--- a/data/monthly_state_ui.xlsx
+++ b/data/monthly_state_ui.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R661"/>
+  <dimension ref="A1:R662"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -4772,43 +4772,43 @@
         <v>28521</v>
       </c>
       <c r="B98">
-        <v>2319209</v>
+        <v>2273261</v>
       </c>
       <c r="D98">
-        <v>1088112</v>
+        <v>1063136</v>
       </c>
       <c r="E98">
-        <v>212712</v>
+        <v>210660</v>
       </c>
       <c r="F98">
-        <v>14034114</v>
+        <v>13886944</v>
       </c>
       <c r="G98">
-        <v>11214108</v>
+        <v>11076378</v>
       </c>
       <c r="H98">
-        <v>919558</v>
+        <v>904867</v>
       </c>
       <c r="I98">
-        <v>84.44</v>
+        <v>84.12</v>
       </c>
       <c r="J98">
-        <v>32.35</v>
+        <v>32.33</v>
       </c>
       <c r="K98">
-        <v>14.28</v>
+        <v>14.31</v>
       </c>
       <c r="L98">
-        <v>79.36</v>
+        <v>79.33</v>
       </c>
       <c r="M98">
-        <v>8657780</v>
+        <v>8643089</v>
       </c>
       <c r="N98">
-        <v>7841696</v>
+        <v>7816720</v>
       </c>
       <c r="O98">
-        <v>2728176</v>
+        <v>2726124</v>
       </c>
       <c r="P98">
         <v>3429</v>
@@ -4846,22 +4846,22 @@
         <v>85.8</v>
       </c>
       <c r="J99">
-        <v>31.67</v>
+        <v>31.64</v>
       </c>
       <c r="K99">
-        <v>14.36</v>
+        <v>14.38</v>
       </c>
       <c r="L99">
-        <v>79.88</v>
+        <v>79.84</v>
       </c>
       <c r="M99">
-        <v>8600867</v>
+        <v>8586176</v>
       </c>
       <c r="N99">
-        <v>7700164</v>
+        <v>7675188</v>
       </c>
       <c r="O99">
-        <v>2660816</v>
+        <v>2658764</v>
       </c>
       <c r="P99">
         <v>3442</v>
@@ -4899,22 +4899,22 @@
         <v>85.48</v>
       </c>
       <c r="J100">
-        <v>30.83</v>
+        <v>30.81</v>
       </c>
       <c r="K100">
-        <v>14.23</v>
+        <v>14.26</v>
       </c>
       <c r="L100">
-        <v>80.52</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="M100">
-        <v>8567240</v>
+        <v>8552549</v>
       </c>
       <c r="N100">
-        <v>7680450</v>
+        <v>7655474</v>
       </c>
       <c r="O100">
-        <v>2571646</v>
+        <v>2569594</v>
       </c>
       <c r="P100">
         <v>3456</v>
@@ -4952,22 +4952,22 @@
         <v>84.33</v>
       </c>
       <c r="J101">
-        <v>30.28</v>
+        <v>30.25</v>
       </c>
       <c r="K101">
-        <v>14.1</v>
+        <v>14.13</v>
       </c>
       <c r="L101">
-        <v>80.98</v>
+        <v>80.95</v>
       </c>
       <c r="M101">
-        <v>8510963</v>
+        <v>8496272</v>
       </c>
       <c r="N101">
-        <v>7655792</v>
+        <v>7630816</v>
       </c>
       <c r="O101">
-        <v>2498762</v>
+        <v>2496710</v>
       </c>
       <c r="P101">
         <v>3472</v>
@@ -5005,22 +5005,22 @@
         <v>82.70999999999999</v>
       </c>
       <c r="J102">
-        <v>30.1</v>
+        <v>30.08</v>
       </c>
       <c r="K102">
-        <v>14.04</v>
+        <v>14.07</v>
       </c>
       <c r="L102">
-        <v>81.38</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="M102">
-        <v>8484666</v>
+        <v>8469975</v>
       </c>
       <c r="N102">
-        <v>7630361</v>
+        <v>7605385</v>
       </c>
       <c r="O102">
-        <v>2449818</v>
+        <v>2447766</v>
       </c>
       <c r="P102">
         <v>3483</v>
@@ -5058,22 +5058,22 @@
         <v>81.7</v>
       </c>
       <c r="J103">
-        <v>29.7</v>
+        <v>29.68</v>
       </c>
       <c r="K103">
-        <v>13.84</v>
+        <v>13.87</v>
       </c>
       <c r="L103">
-        <v>81.78</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="M103">
-        <v>8405004</v>
+        <v>8390313</v>
       </c>
       <c r="N103">
-        <v>7635167</v>
+        <v>7610191</v>
       </c>
       <c r="O103">
-        <v>2371851</v>
+        <v>2369799</v>
       </c>
       <c r="P103">
         <v>3482</v>
@@ -5111,22 +5111,22 @@
         <v>80.67</v>
       </c>
       <c r="J104">
-        <v>29.44</v>
+        <v>29.5</v>
       </c>
       <c r="K104">
-        <v>13.71</v>
+        <v>13.74</v>
       </c>
       <c r="L104">
-        <v>82.15000000000001</v>
+        <v>82.12</v>
       </c>
       <c r="M104">
-        <v>8368430</v>
+        <v>8353739</v>
       </c>
       <c r="N104">
-        <v>7635943</v>
+        <v>7610967</v>
       </c>
       <c r="O104">
-        <v>2308304</v>
+        <v>2306252</v>
       </c>
       <c r="P104">
         <v>3473</v>
@@ -5164,22 +5164,22 @@
         <v>81.40000000000001</v>
       </c>
       <c r="J105">
-        <v>29</v>
+        <v>29.07</v>
       </c>
       <c r="K105">
-        <v>13.54</v>
+        <v>13.57</v>
       </c>
       <c r="L105">
-        <v>82.52</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="M105">
-        <v>8373307</v>
+        <v>8358616</v>
       </c>
       <c r="N105">
-        <v>7702865</v>
+        <v>7677889</v>
       </c>
       <c r="O105">
-        <v>2233017</v>
+        <v>2230965</v>
       </c>
       <c r="P105">
         <v>3475</v>
@@ -5217,22 +5217,22 @@
         <v>81.8</v>
       </c>
       <c r="J106">
-        <v>28.29</v>
+        <v>28.36</v>
       </c>
       <c r="K106">
-        <v>13.5</v>
+        <v>13.52</v>
       </c>
       <c r="L106">
-        <v>82.81999999999999</v>
+        <v>82.78</v>
       </c>
       <c r="M106">
-        <v>8328649</v>
+        <v>8313958</v>
       </c>
       <c r="N106">
-        <v>7661118</v>
+        <v>7636142</v>
       </c>
       <c r="O106">
-        <v>2173075</v>
+        <v>2171023</v>
       </c>
       <c r="P106">
         <v>3484</v>
@@ -5270,22 +5270,22 @@
         <v>83.42</v>
       </c>
       <c r="J107">
-        <v>27.73</v>
+        <v>27.8</v>
       </c>
       <c r="K107">
-        <v>13.45</v>
+        <v>13.48</v>
       </c>
       <c r="L107">
-        <v>83.06999999999999</v>
+        <v>83.03</v>
       </c>
       <c r="M107">
-        <v>8321944</v>
+        <v>8307253</v>
       </c>
       <c r="N107">
-        <v>7658005</v>
+        <v>7633029</v>
       </c>
       <c r="O107">
-        <v>2123303</v>
+        <v>2121251</v>
       </c>
       <c r="P107">
         <v>3488</v>
@@ -5323,22 +5323,22 @@
         <v>83.88</v>
       </c>
       <c r="J108">
-        <v>27.2</v>
+        <v>27.26</v>
       </c>
       <c r="K108">
-        <v>13.39</v>
+        <v>13.42</v>
       </c>
       <c r="L108">
-        <v>83.33</v>
+        <v>83.3</v>
       </c>
       <c r="M108">
-        <v>8278594</v>
+        <v>8263903</v>
       </c>
       <c r="N108">
-        <v>7628569</v>
+        <v>7603593</v>
       </c>
       <c r="O108">
-        <v>2075428</v>
+        <v>2073376</v>
       </c>
       <c r="P108">
         <v>3494</v>
@@ -5376,22 +5376,22 @@
         <v>86.16</v>
       </c>
       <c r="J109">
-        <v>26.62</v>
+        <v>26.68</v>
       </c>
       <c r="K109">
-        <v>13.31</v>
+        <v>13.34</v>
       </c>
       <c r="L109">
-        <v>83.70999999999999</v>
+        <v>83.67</v>
       </c>
       <c r="M109">
-        <v>8226928</v>
+        <v>8212237</v>
       </c>
       <c r="N109">
-        <v>7593286</v>
+        <v>7568310</v>
       </c>
       <c r="O109">
-        <v>2032490</v>
+        <v>2030438</v>
       </c>
       <c r="P109">
         <v>3500</v>
@@ -5429,7 +5429,7 @@
         <v>88.3</v>
       </c>
       <c r="J110">
-        <v>26.24</v>
+        <v>26.32</v>
       </c>
       <c r="K110">
         <v>13.2</v>
@@ -5482,7 +5482,7 @@
         <v>90.31</v>
       </c>
       <c r="J111">
-        <v>25.7</v>
+        <v>25.79</v>
       </c>
       <c r="K111">
         <v>13.26</v>
@@ -5535,7 +5535,7 @@
         <v>90.28</v>
       </c>
       <c r="J112">
-        <v>25.74</v>
+        <v>25.83</v>
       </c>
       <c r="K112">
         <v>13.21</v>
@@ -5588,7 +5588,7 @@
         <v>89.28</v>
       </c>
       <c r="J113">
-        <v>25.66</v>
+        <v>25.75</v>
       </c>
       <c r="K113">
         <v>13.19</v>
@@ -5641,7 +5641,7 @@
         <v>88.37</v>
       </c>
       <c r="J114">
-        <v>25.78</v>
+        <v>25.87</v>
       </c>
       <c r="K114">
         <v>13.19</v>
@@ -5694,7 +5694,7 @@
         <v>87.25</v>
       </c>
       <c r="J115">
-        <v>25.72</v>
+        <v>25.8</v>
       </c>
       <c r="K115">
         <v>13.19</v>
@@ -6589,10 +6589,10 @@
         <v>9516801</v>
       </c>
       <c r="H132">
-        <v>887414</v>
+        <v>935714</v>
       </c>
       <c r="I132">
-        <v>95.63</v>
+        <v>100.73</v>
       </c>
       <c r="J132">
         <v>32.75</v>
@@ -6601,10 +6601,10 @@
         <v>14.67</v>
       </c>
       <c r="L132">
-        <v>98.72</v>
+        <v>99.05</v>
       </c>
       <c r="M132">
-        <v>14018961</v>
+        <v>14067261</v>
       </c>
       <c r="N132">
         <v>9919645</v>
@@ -6654,10 +6654,10 @@
         <v>14.91</v>
       </c>
       <c r="L133">
-        <v>99.20999999999999</v>
+        <v>99.53</v>
       </c>
       <c r="M133">
-        <v>14421413</v>
+        <v>14469713</v>
       </c>
       <c r="N133">
         <v>9992123</v>
@@ -6707,10 +6707,10 @@
         <v>15.02</v>
       </c>
       <c r="L134">
-        <v>99.87</v>
+        <v>100.2</v>
       </c>
       <c r="M134">
-        <v>14557049</v>
+        <v>14605349</v>
       </c>
       <c r="N134">
         <v>9946214</v>
@@ -6760,10 +6760,10 @@
         <v>15.11</v>
       </c>
       <c r="L135">
-        <v>100.4</v>
+        <v>100.72</v>
       </c>
       <c r="M135">
-        <v>14642486</v>
+        <v>14690785</v>
       </c>
       <c r="N135">
         <v>9890722</v>
@@ -6813,10 +6813,10 @@
         <v>15.16</v>
       </c>
       <c r="L136">
-        <v>100.99</v>
+        <v>101.31</v>
       </c>
       <c r="M136">
-        <v>14818945</v>
+        <v>14867245</v>
       </c>
       <c r="N136">
         <v>9919839</v>
@@ -6866,10 +6866,10 @@
         <v>15.27</v>
       </c>
       <c r="L137">
-        <v>101.51</v>
+        <v>101.83</v>
       </c>
       <c r="M137">
-        <v>14813463</v>
+        <v>14861763</v>
       </c>
       <c r="N137">
         <v>9793604</v>
@@ -6919,10 +6919,10 @@
         <v>15.52</v>
       </c>
       <c r="L138">
-        <v>101.92</v>
+        <v>102.25</v>
       </c>
       <c r="M138">
-        <v>14622855</v>
+        <v>14671154</v>
       </c>
       <c r="N138">
         <v>9476838</v>
@@ -6972,10 +6972,10 @@
         <v>15.69</v>
       </c>
       <c r="L139">
-        <v>102.27</v>
+        <v>102.61</v>
       </c>
       <c r="M139">
-        <v>14419080</v>
+        <v>14467379</v>
       </c>
       <c r="N139">
         <v>9214474</v>
@@ -7001,7 +7001,7 @@
         <v>2112151</v>
       </c>
       <c r="D140">
-        <v>815195</v>
+        <v>823652</v>
       </c>
       <c r="E140">
         <v>246909</v>
@@ -7022,16 +7022,16 @@
         <v>32.99</v>
       </c>
       <c r="K140">
-        <v>15.75</v>
+        <v>15.74</v>
       </c>
       <c r="L140">
-        <v>102.73</v>
+        <v>103.08</v>
       </c>
       <c r="M140">
-        <v>14083860</v>
+        <v>14132159</v>
       </c>
       <c r="N140">
-        <v>8927031</v>
+        <v>8935488</v>
       </c>
       <c r="O140">
         <v>3281695</v>
@@ -7075,16 +7075,16 @@
         <v>32.76</v>
       </c>
       <c r="K141">
-        <v>15.68</v>
+        <v>15.66</v>
       </c>
       <c r="L141">
-        <v>103.24</v>
+        <v>103.59</v>
       </c>
       <c r="M141">
-        <v>13846156</v>
+        <v>13894456</v>
       </c>
       <c r="N141">
-        <v>8773546</v>
+        <v>8782003</v>
       </c>
       <c r="O141">
         <v>3240512</v>
@@ -7128,16 +7128,16 @@
         <v>32.19</v>
       </c>
       <c r="K142">
-        <v>15.45</v>
+        <v>15.43</v>
       </c>
       <c r="L142">
-        <v>103.79</v>
+        <v>104.15</v>
       </c>
       <c r="M142">
-        <v>13702063</v>
+        <v>13750363</v>
       </c>
       <c r="N142">
-        <v>8767814</v>
+        <v>8776271</v>
       </c>
       <c r="O142">
         <v>3193123</v>
@@ -7181,16 +7181,16 @@
         <v>31.67</v>
       </c>
       <c r="K143">
-        <v>15.11</v>
+        <v>15.1</v>
       </c>
       <c r="L143">
-        <v>104.39</v>
+        <v>104.75</v>
       </c>
       <c r="M143">
-        <v>13573932</v>
+        <v>13622231</v>
       </c>
       <c r="N143">
-        <v>8828256</v>
+        <v>8836713</v>
       </c>
       <c r="O143">
         <v>3101549</v>
@@ -7234,7 +7234,7 @@
         <v>32.12</v>
       </c>
       <c r="K144">
-        <v>14.83</v>
+        <v>14.81</v>
       </c>
       <c r="L144">
         <v>105.47</v>
@@ -7243,7 +7243,7 @@
         <v>13767328</v>
       </c>
       <c r="N144">
-        <v>9034064</v>
+        <v>9042521</v>
       </c>
       <c r="O144">
         <v>3043526</v>
@@ -7287,7 +7287,7 @@
         <v>32.44</v>
       </c>
       <c r="K145">
-        <v>14.48</v>
+        <v>14.47</v>
       </c>
       <c r="L145">
         <v>106.61</v>
@@ -7296,7 +7296,7 @@
         <v>14113290</v>
       </c>
       <c r="N145">
-        <v>9386684</v>
+        <v>9395141</v>
       </c>
       <c r="O145">
         <v>2989177</v>
@@ -7337,10 +7337,10 @@
         <v>114.95</v>
       </c>
       <c r="J146">
-        <v>32.91</v>
+        <v>32.88</v>
       </c>
       <c r="K146">
-        <v>14.18</v>
+        <v>14.17</v>
       </c>
       <c r="L146">
         <v>107.85</v>
@@ -7349,7 +7349,7 @@
         <v>14458798</v>
       </c>
       <c r="N146">
-        <v>9707548</v>
+        <v>9716005</v>
       </c>
       <c r="O146">
         <v>2937578</v>
@@ -7390,10 +7390,10 @@
         <v>117.46</v>
       </c>
       <c r="J147">
-        <v>33.39</v>
+        <v>33.36</v>
       </c>
       <c r="K147">
-        <v>14.17</v>
+        <v>14.16</v>
       </c>
       <c r="L147">
         <v>109.23</v>
@@ -7402,7 +7402,7 @@
         <v>14926884</v>
       </c>
       <c r="N147">
-        <v>9908379</v>
+        <v>9916836</v>
       </c>
       <c r="O147">
         <v>2929529</v>
@@ -7443,10 +7443,10 @@
         <v>117.44</v>
       </c>
       <c r="J148">
-        <v>33.99</v>
+        <v>33.95</v>
       </c>
       <c r="K148">
-        <v>14.26</v>
+        <v>14.25</v>
       </c>
       <c r="L148">
         <v>110.6</v>
@@ -7455,7 +7455,7 @@
         <v>15607688</v>
       </c>
       <c r="N148">
-        <v>10168012</v>
+        <v>10176469</v>
       </c>
       <c r="O148">
         <v>2979966</v>
@@ -7496,10 +7496,10 @@
         <v>117.9</v>
       </c>
       <c r="J149">
-        <v>34.58</v>
+        <v>34.55</v>
       </c>
       <c r="K149">
-        <v>14.36</v>
+        <v>14.35</v>
       </c>
       <c r="L149">
         <v>111.76</v>
@@ -7508,7 +7508,7 @@
         <v>16230878</v>
       </c>
       <c r="N149">
-        <v>10393593</v>
+        <v>10402050</v>
       </c>
       <c r="O149">
         <v>3052828</v>
@@ -7549,10 +7549,10 @@
         <v>118.33</v>
       </c>
       <c r="J150">
-        <v>34.81</v>
+        <v>34.78</v>
       </c>
       <c r="K150">
-        <v>14.47</v>
+        <v>14.46</v>
       </c>
       <c r="L150">
         <v>112.75</v>
@@ -7561,7 +7561,7 @@
         <v>16798094</v>
       </c>
       <c r="N150">
-        <v>10577993</v>
+        <v>10586450</v>
       </c>
       <c r="O150">
         <v>3145040</v>
@@ -7602,10 +7602,10 @@
         <v>118.32</v>
       </c>
       <c r="J151">
-        <v>34.93</v>
+        <v>34.9</v>
       </c>
       <c r="K151">
-        <v>14.62</v>
+        <v>14.61</v>
       </c>
       <c r="L151">
         <v>113.8</v>
@@ -7614,7 +7614,7 @@
         <v>17524614</v>
       </c>
       <c r="N151">
-        <v>10825906</v>
+        <v>10834363</v>
       </c>
       <c r="O151">
         <v>3279005</v>
@@ -7655,7 +7655,7 @@
         <v>117.67</v>
       </c>
       <c r="J152">
-        <v>34.94</v>
+        <v>34.91</v>
       </c>
       <c r="K152">
         <v>14.74</v>
@@ -7708,7 +7708,7 @@
         <v>119.22</v>
       </c>
       <c r="J153">
-        <v>35.74</v>
+        <v>35.71</v>
       </c>
       <c r="K153">
         <v>14.94</v>
@@ -7761,7 +7761,7 @@
         <v>121.03</v>
       </c>
       <c r="J154">
-        <v>36.25</v>
+        <v>36.22</v>
       </c>
       <c r="K154">
         <v>15.13</v>
@@ -7814,7 +7814,7 @@
         <v>122.9</v>
       </c>
       <c r="J155">
-        <v>36.88</v>
+        <v>36.85</v>
       </c>
       <c r="K155">
         <v>15.32</v>
@@ -7867,7 +7867,7 @@
         <v>123.46</v>
       </c>
       <c r="J156">
-        <v>37.97</v>
+        <v>37.94</v>
       </c>
       <c r="K156">
         <v>15.57</v>
@@ -7920,7 +7920,7 @@
         <v>123.55</v>
       </c>
       <c r="J157">
-        <v>38.56</v>
+        <v>38.53</v>
       </c>
       <c r="K157">
         <v>15.92</v>
@@ -9439,7 +9439,7 @@
         <v>1488338</v>
       </c>
       <c r="D186">
-        <v>554334</v>
+        <v>590442</v>
       </c>
       <c r="E186">
         <v>232183</v>
@@ -9448,28 +9448,28 @@
         <v>10937527</v>
       </c>
       <c r="G186">
-        <v>9089505</v>
+        <v>9817589</v>
       </c>
       <c r="H186">
-        <v>1123128</v>
+        <v>1208666</v>
       </c>
       <c r="I186">
-        <v>127.67</v>
+        <v>127.34</v>
       </c>
       <c r="J186">
         <v>32.49</v>
       </c>
       <c r="K186">
-        <v>13.94</v>
+        <v>13.96</v>
       </c>
       <c r="L186">
-        <v>125.19</v>
+        <v>125.18</v>
       </c>
       <c r="M186">
-        <v>13803918</v>
+        <v>13889456</v>
       </c>
       <c r="N186">
-        <v>8175139</v>
+        <v>8211247</v>
       </c>
       <c r="O186">
         <v>2510371</v>
@@ -9495,7 +9495,7 @@
         <v>498855</v>
       </c>
       <c r="E187">
-        <v>196723</v>
+        <v>194076</v>
       </c>
       <c r="F187">
         <v>9421892</v>
@@ -9510,22 +9510,22 @@
         <v>126.49</v>
       </c>
       <c r="J187">
-        <v>32.41</v>
+        <v>32.38</v>
       </c>
       <c r="K187">
-        <v>13.94</v>
+        <v>13.97</v>
       </c>
       <c r="L187">
-        <v>125.49</v>
+        <v>125.48</v>
       </c>
       <c r="M187">
-        <v>13880151</v>
+        <v>13965689</v>
       </c>
       <c r="N187">
-        <v>8195130</v>
+        <v>8231238</v>
       </c>
       <c r="O187">
-        <v>2509458</v>
+        <v>2506811</v>
       </c>
       <c r="P187">
         <v>3825</v>
@@ -9563,22 +9563,22 @@
         <v>125.79</v>
       </c>
       <c r="J188">
-        <v>32</v>
+        <v>31.96</v>
       </c>
       <c r="K188">
-        <v>13.98</v>
+        <v>14.01</v>
       </c>
       <c r="L188">
-        <v>125.91</v>
+        <v>125.89</v>
       </c>
       <c r="M188">
-        <v>14091384</v>
+        <v>14176922</v>
       </c>
       <c r="N188">
-        <v>8274916</v>
+        <v>8311024</v>
       </c>
       <c r="O188">
-        <v>2531056</v>
+        <v>2528409</v>
       </c>
       <c r="P188">
         <v>3837</v>
@@ -9601,7 +9601,7 @@
         <v>631919</v>
       </c>
       <c r="E189">
-        <v>207353</v>
+        <v>204866</v>
       </c>
       <c r="F189">
         <v>10180433</v>
@@ -9616,22 +9616,22 @@
         <v>126.88</v>
       </c>
       <c r="J189">
-        <v>31.56</v>
+        <v>31.5</v>
       </c>
       <c r="K189">
-        <v>14.01</v>
+        <v>14.03</v>
       </c>
       <c r="L189">
-        <v>126.39</v>
+        <v>126.37</v>
       </c>
       <c r="M189">
-        <v>14174692</v>
+        <v>14260230</v>
       </c>
       <c r="N189">
-        <v>8279276</v>
+        <v>8315384</v>
       </c>
       <c r="O189">
-        <v>2526585</v>
+        <v>2521451</v>
       </c>
       <c r="P189">
         <v>3841</v>
@@ -9651,10 +9651,10 @@
         <v>1343308</v>
       </c>
       <c r="D190">
-        <v>510005</v>
+        <v>509987</v>
       </c>
       <c r="E190">
-        <v>184062</v>
+        <v>181941</v>
       </c>
       <c r="F190">
         <v>9164177</v>
@@ -9669,22 +9669,22 @@
         <v>128.7</v>
       </c>
       <c r="J190">
-        <v>31.56</v>
+        <v>31.47</v>
       </c>
       <c r="K190">
-        <v>14.03</v>
+        <v>14.06</v>
       </c>
       <c r="L190">
-        <v>126.81</v>
+        <v>126.78</v>
       </c>
       <c r="M190">
-        <v>14337019</v>
+        <v>14422557</v>
       </c>
       <c r="N190">
-        <v>8334875</v>
+        <v>8370965</v>
       </c>
       <c r="O190">
-        <v>2547309</v>
+        <v>2540054</v>
       </c>
       <c r="P190">
         <v>3855</v>
@@ -9704,40 +9704,40 @@
         <v>1667576</v>
       </c>
       <c r="D191">
-        <v>633431</v>
+        <v>573571</v>
       </c>
       <c r="E191">
-        <v>234627</v>
+        <v>207667</v>
       </c>
       <c r="F191">
         <v>9966680</v>
       </c>
       <c r="G191">
-        <v>9984867</v>
+        <v>8670742</v>
       </c>
       <c r="H191">
-        <v>1652804</v>
+        <v>1073136</v>
       </c>
       <c r="I191">
-        <v>170.59</v>
+        <v>128.6</v>
       </c>
       <c r="J191">
-        <v>31.71</v>
+        <v>31.29</v>
       </c>
       <c r="K191">
-        <v>14.16</v>
+        <v>14.13</v>
       </c>
       <c r="L191">
-        <v>130.66</v>
+        <v>127.14</v>
       </c>
       <c r="M191">
-        <v>15021920</v>
+        <v>14527790</v>
       </c>
       <c r="N191">
-        <v>8392280</v>
+        <v>8368510</v>
       </c>
       <c r="O191">
-        <v>2585292</v>
+        <v>2551077</v>
       </c>
       <c r="P191">
         <v>3864</v>
@@ -9775,22 +9775,22 @@
         <v>130.9</v>
       </c>
       <c r="J192">
-        <v>31.58</v>
+        <v>31.03</v>
       </c>
       <c r="K192">
-        <v>14.25</v>
+        <v>14.22</v>
       </c>
       <c r="L192">
-        <v>131.12</v>
+        <v>127.59</v>
       </c>
       <c r="M192">
-        <v>15026695</v>
+        <v>14532564</v>
       </c>
       <c r="N192">
-        <v>8313854</v>
+        <v>8290084</v>
       </c>
       <c r="O192">
-        <v>2581914</v>
+        <v>2547699</v>
       </c>
       <c r="P192">
         <v>3867</v>
@@ -9828,22 +9828,22 @@
         <v>132.24</v>
       </c>
       <c r="J193">
-        <v>31.81</v>
+        <v>31.25</v>
       </c>
       <c r="K193">
-        <v>14.29</v>
+        <v>14.26</v>
       </c>
       <c r="L193">
-        <v>131.63</v>
+        <v>128.13</v>
       </c>
       <c r="M193">
-        <v>15255218</v>
+        <v>14761088</v>
       </c>
       <c r="N193">
-        <v>8388946</v>
+        <v>8365176</v>
       </c>
       <c r="O193">
-        <v>2606562</v>
+        <v>2572347</v>
       </c>
       <c r="P193">
         <v>3862</v>
@@ -9869,7 +9869,7 @@
         <v>235008</v>
       </c>
       <c r="F194">
-        <v>14727910</v>
+        <v>14729040</v>
       </c>
       <c r="G194">
         <v>13027499</v>
@@ -9881,22 +9881,22 @@
         <v>133.57</v>
       </c>
       <c r="J194">
-        <v>31.47</v>
+        <v>30.92</v>
       </c>
       <c r="K194">
-        <v>14.26</v>
+        <v>14.23</v>
       </c>
       <c r="L194">
-        <v>132.37</v>
+        <v>128.88</v>
       </c>
       <c r="M194">
-        <v>15337899</v>
+        <v>14843769</v>
       </c>
       <c r="N194">
-        <v>8411833</v>
+        <v>8388063</v>
       </c>
       <c r="O194">
-        <v>2604362</v>
+        <v>2570147</v>
       </c>
       <c r="P194">
         <v>3869</v>
@@ -9934,22 +9934,22 @@
         <v>135</v>
       </c>
       <c r="J195">
-        <v>31.47</v>
+        <v>30.92</v>
       </c>
       <c r="K195">
-        <v>14.34</v>
+        <v>14.31</v>
       </c>
       <c r="L195">
-        <v>133.03</v>
+        <v>129.54</v>
       </c>
       <c r="M195">
-        <v>15382830</v>
+        <v>14888699</v>
       </c>
       <c r="N195">
-        <v>8349305</v>
+        <v>8325535</v>
       </c>
       <c r="O195">
-        <v>2605251</v>
+        <v>2571036</v>
       </c>
       <c r="P195">
         <v>3875</v>
@@ -9975,7 +9975,7 @@
         <v>219934</v>
       </c>
       <c r="F196">
-        <v>13101136</v>
+        <v>13097746</v>
       </c>
       <c r="G196">
         <v>11730221</v>
@@ -9987,22 +9987,22 @@
         <v>134.8</v>
       </c>
       <c r="J196">
-        <v>31.16</v>
+        <v>30.62</v>
       </c>
       <c r="K196">
-        <v>14.35</v>
+        <v>14.32</v>
       </c>
       <c r="L196">
-        <v>133.69</v>
+        <v>130.19</v>
       </c>
       <c r="M196">
-        <v>15461511</v>
+        <v>14967381</v>
       </c>
       <c r="N196">
-        <v>8343801</v>
+        <v>8320031</v>
       </c>
       <c r="O196">
-        <v>2597325</v>
+        <v>2563110</v>
       </c>
       <c r="P196">
         <v>3873</v>
@@ -10040,22 +10040,22 @@
         <v>135.23</v>
       </c>
       <c r="J197">
-        <v>30.99</v>
+        <v>30.67</v>
       </c>
       <c r="K197">
-        <v>14.36</v>
+        <v>14.33</v>
       </c>
       <c r="L197">
-        <v>134.34</v>
+        <v>130.86</v>
       </c>
       <c r="M197">
-        <v>15583656</v>
+        <v>15089525</v>
       </c>
       <c r="N197">
-        <v>8365265</v>
+        <v>8341495</v>
       </c>
       <c r="O197">
-        <v>2600780</v>
+        <v>2566565</v>
       </c>
       <c r="P197">
         <v>3878</v>
@@ -10078,7 +10078,7 @@
         <v>579278</v>
       </c>
       <c r="E198">
-        <v>235346</v>
+        <v>232984</v>
       </c>
       <c r="F198">
         <v>10732540</v>
@@ -10093,22 +10093,22 @@
         <v>135.78</v>
       </c>
       <c r="J198">
-        <v>31.32</v>
+        <v>30.97</v>
       </c>
       <c r="K198">
-        <v>14.38</v>
+        <v>14.33</v>
       </c>
       <c r="L198">
-        <v>134.96</v>
+        <v>131.55</v>
       </c>
       <c r="M198">
-        <v>15721253</v>
+        <v>15141584</v>
       </c>
       <c r="N198">
-        <v>8390209</v>
+        <v>8330331</v>
       </c>
       <c r="O198">
-        <v>2603943</v>
+        <v>2567366</v>
       </c>
       <c r="P198">
         <v>3884</v>
@@ -10131,10 +10131,10 @@
         <v>525103</v>
       </c>
       <c r="E199">
-        <v>216966</v>
+        <v>214626</v>
       </c>
       <c r="F199">
-        <v>10183519</v>
+        <v>10187280</v>
       </c>
       <c r="G199">
         <v>9028611</v>
@@ -10146,22 +10146,22 @@
         <v>135.39</v>
       </c>
       <c r="J199">
-        <v>31.28</v>
+        <v>30.94</v>
       </c>
       <c r="K199">
-        <v>14.43</v>
+        <v>14.37</v>
       </c>
       <c r="L199">
-        <v>135.57</v>
+        <v>132.19</v>
       </c>
       <c r="M199">
-        <v>15888796</v>
+        <v>15309128</v>
       </c>
       <c r="N199">
-        <v>8416457</v>
+        <v>8356579</v>
       </c>
       <c r="O199">
-        <v>2624186</v>
+        <v>2587916</v>
       </c>
       <c r="P199">
         <v>3887</v>
@@ -10184,7 +10184,7 @@
         <v>735606</v>
       </c>
       <c r="E200">
-        <v>249256</v>
+        <v>247048</v>
       </c>
       <c r="F200">
         <v>11601024</v>
@@ -10199,22 +10199,22 @@
         <v>134.13</v>
       </c>
       <c r="J200">
-        <v>31.37</v>
+        <v>31</v>
       </c>
       <c r="K200">
-        <v>14.48</v>
+        <v>14.43</v>
       </c>
       <c r="L200">
-        <v>136.23</v>
+        <v>132.87</v>
       </c>
       <c r="M200">
-        <v>16020406</v>
+        <v>15440738</v>
       </c>
       <c r="N200">
-        <v>8410476</v>
+        <v>8350598</v>
       </c>
       <c r="O200">
-        <v>2638444</v>
+        <v>2599966</v>
       </c>
       <c r="P200">
         <v>3886</v>
@@ -10237,7 +10237,7 @@
         <v>649662</v>
       </c>
       <c r="E201">
-        <v>212491</v>
+        <v>210438</v>
       </c>
       <c r="F201">
         <v>10189513</v>
@@ -10252,22 +10252,22 @@
         <v>135.05</v>
       </c>
       <c r="J201">
-        <v>31.66</v>
+        <v>31.3</v>
       </c>
       <c r="K201">
-        <v>14.45</v>
+        <v>14.4</v>
       </c>
       <c r="L201">
-        <v>136.84</v>
+        <v>133.49</v>
       </c>
       <c r="M201">
-        <v>16090180</v>
+        <v>15510512</v>
       </c>
       <c r="N201">
-        <v>8428219</v>
+        <v>8368341</v>
       </c>
       <c r="O201">
-        <v>2643582</v>
+        <v>2605538</v>
       </c>
       <c r="P201">
         <v>3887</v>
@@ -10293,7 +10293,7 @@
         <v>211859</v>
       </c>
       <c r="F202">
-        <v>10101688</v>
+        <v>10071131</v>
       </c>
       <c r="G202">
         <v>8724780</v>
@@ -10305,22 +10305,22 @@
         <v>136.9</v>
       </c>
       <c r="J202">
-        <v>32.02</v>
+        <v>31.68</v>
       </c>
       <c r="K202">
-        <v>14.51</v>
+        <v>14.46</v>
       </c>
       <c r="L202">
-        <v>137.37</v>
+        <v>134.05</v>
       </c>
       <c r="M202">
-        <v>16253490</v>
+        <v>15673822</v>
       </c>
       <c r="N202">
-        <v>8441758</v>
+        <v>8381898</v>
       </c>
       <c r="O202">
-        <v>2671379</v>
+        <v>2635456</v>
       </c>
       <c r="P202">
         <v>3895</v>
@@ -10346,7 +10346,7 @@
         <v>223173</v>
       </c>
       <c r="F203">
-        <v>9887040</v>
+        <v>9851199</v>
       </c>
       <c r="G203">
         <v>8695175</v>
@@ -10358,7 +10358,7 @@
         <v>138.01</v>
       </c>
       <c r="J203">
-        <v>31.8</v>
+        <v>31.78</v>
       </c>
       <c r="K203">
         <v>14.47</v>
@@ -10373,7 +10373,7 @@
         <v>8380544</v>
       </c>
       <c r="O203">
-        <v>2659925</v>
+        <v>2650962</v>
       </c>
       <c r="P203">
         <v>3915</v>
@@ -10411,7 +10411,7 @@
         <v>137.51</v>
       </c>
       <c r="J204">
-        <v>31.8</v>
+        <v>31.92</v>
       </c>
       <c r="K204">
         <v>14.52</v>
@@ -10426,7 +10426,7 @@
         <v>8330361</v>
       </c>
       <c r="O204">
-        <v>2667747</v>
+        <v>2658784</v>
       </c>
       <c r="P204">
         <v>3927</v>
@@ -10464,7 +10464,7 @@
         <v>137.95</v>
       </c>
       <c r="J205">
-        <v>32.04</v>
+        <v>32.16</v>
       </c>
       <c r="K205">
         <v>14.52</v>
@@ -10479,7 +10479,7 @@
         <v>8360752</v>
       </c>
       <c r="O205">
-        <v>2696296</v>
+        <v>2687333</v>
       </c>
       <c r="P205">
         <v>3938</v>
@@ -10517,7 +10517,7 @@
         <v>138.97</v>
       </c>
       <c r="J206">
-        <v>32</v>
+        <v>32.12</v>
       </c>
       <c r="K206">
         <v>14.65</v>
@@ -10532,7 +10532,7 @@
         <v>8190399</v>
       </c>
       <c r="O206">
-        <v>2691350</v>
+        <v>2682387</v>
       </c>
       <c r="P206">
         <v>3943</v>
@@ -10570,7 +10570,7 @@
         <v>140.64</v>
       </c>
       <c r="J207">
-        <v>32.08</v>
+        <v>32.2</v>
       </c>
       <c r="K207">
         <v>14.64</v>
@@ -10585,7 +10585,7 @@
         <v>8167954</v>
       </c>
       <c r="O207">
-        <v>2703701</v>
+        <v>2694738</v>
       </c>
       <c r="P207">
         <v>3943</v>
@@ -10623,7 +10623,7 @@
         <v>140.76</v>
       </c>
       <c r="J208">
-        <v>32.32</v>
+        <v>32.44</v>
       </c>
       <c r="K208">
         <v>14.7</v>
@@ -10638,7 +10638,7 @@
         <v>8133267</v>
       </c>
       <c r="O208">
-        <v>2728284</v>
+        <v>2719321</v>
       </c>
       <c r="P208">
         <v>3945</v>
@@ -10676,7 +10676,7 @@
         <v>140.62</v>
       </c>
       <c r="J209">
-        <v>32.42</v>
+        <v>32.31</v>
       </c>
       <c r="K209">
         <v>14.74</v>
@@ -10691,7 +10691,7 @@
         <v>8038963</v>
       </c>
       <c r="O209">
-        <v>2716726</v>
+        <v>2707763</v>
       </c>
       <c r="P209">
         <v>3954</v>
@@ -10729,7 +10729,7 @@
         <v>140.5</v>
       </c>
       <c r="J210">
-        <v>32.25</v>
+        <v>32.18</v>
       </c>
       <c r="K210">
         <v>14.77</v>
@@ -10744,7 +10744,7 @@
         <v>7908330</v>
       </c>
       <c r="O210">
-        <v>2686929</v>
+        <v>2680328</v>
       </c>
       <c r="P210">
         <v>3955</v>
@@ -10782,7 +10782,7 @@
         <v>140.32</v>
       </c>
       <c r="J211">
-        <v>32.01</v>
+        <v>31.96</v>
       </c>
       <c r="K211">
         <v>14.74</v>
@@ -10797,7 +10797,7 @@
         <v>7873641</v>
       </c>
       <c r="O211">
-        <v>2676231</v>
+        <v>2671970</v>
       </c>
       <c r="P211">
         <v>3950</v>
@@ -10835,7 +10835,7 @@
         <v>139.1</v>
       </c>
       <c r="J212">
-        <v>32.22</v>
+        <v>32.2</v>
       </c>
       <c r="K212">
         <v>14.7</v>
@@ -10850,7 +10850,7 @@
         <v>7781838</v>
       </c>
       <c r="O212">
-        <v>2639284</v>
+        <v>2637231</v>
       </c>
       <c r="P212">
         <v>3967</v>
@@ -11874,7 +11874,7 @@
         <v>32598</v>
       </c>
       <c r="B232">
-        <v>1367669</v>
+        <v>1361144</v>
       </c>
       <c r="D232">
         <v>652549</v>
@@ -11883,7 +11883,7 @@
         <v>176192</v>
       </c>
       <c r="F232">
-        <v>11714703</v>
+        <v>11588960</v>
       </c>
       <c r="G232">
         <v>10451849</v>
@@ -32210,10 +32210,10 @@
         <v>1753952</v>
       </c>
       <c r="P602">
-        <v>5270</v>
+        <v>5262</v>
       </c>
       <c r="Q602">
-        <v>14666</v>
+        <v>14664</v>
       </c>
       <c r="R602">
         <v>341963</v>
@@ -32266,10 +32266,10 @@
         <v>1757299</v>
       </c>
       <c r="P603">
-        <v>5319</v>
+        <v>5308</v>
       </c>
       <c r="Q603">
-        <v>14697</v>
+        <v>14692</v>
       </c>
       <c r="R603">
         <v>343097</v>
@@ -32322,10 +32322,10 @@
         <v>1773952</v>
       </c>
       <c r="P604">
-        <v>5266</v>
+        <v>5263</v>
       </c>
       <c r="Q604">
-        <v>14692</v>
+        <v>14688</v>
       </c>
       <c r="R604">
         <v>346286</v>
@@ -32378,10 +32378,10 @@
         <v>1812574</v>
       </c>
       <c r="P605">
-        <v>5115</v>
+        <v>5113</v>
       </c>
       <c r="Q605">
-        <v>13925</v>
+        <v>13921</v>
       </c>
       <c r="R605">
         <v>337598</v>
@@ -32434,10 +32434,10 @@
         <v>1924685</v>
       </c>
       <c r="P606">
-        <v>5057</v>
+        <v>5059</v>
       </c>
       <c r="Q606">
-        <v>13460</v>
+        <v>13458</v>
       </c>
       <c r="R606">
         <v>346584</v>
@@ -32490,10 +32490,10 @@
         <v>2392117</v>
       </c>
       <c r="P607">
-        <v>5059</v>
+        <v>5069</v>
       </c>
       <c r="Q607">
-        <v>13485</v>
+        <v>13460</v>
       </c>
       <c r="R607">
         <v>342378</v>
@@ -32546,10 +32546,10 @@
         <v>3183893</v>
       </c>
       <c r="P608">
-        <v>5070</v>
+        <v>5080</v>
       </c>
       <c r="Q608">
-        <v>13559</v>
+        <v>13526</v>
       </c>
       <c r="R608">
         <v>336713</v>
@@ -32602,10 +32602,10 @@
         <v>4115659</v>
       </c>
       <c r="P609">
-        <v>5115</v>
+        <v>5120</v>
       </c>
       <c r="Q609">
-        <v>13715</v>
+        <v>13724</v>
       </c>
       <c r="R609">
         <v>335100</v>
@@ -32658,10 +32658,10 @@
         <v>7059486</v>
       </c>
       <c r="P610">
-        <v>5096</v>
+        <v>5091</v>
       </c>
       <c r="Q610">
-        <v>13718</v>
+        <v>13715</v>
       </c>
       <c r="R610">
         <v>334831</v>
@@ -32717,7 +32717,7 @@
         <v>5074</v>
       </c>
       <c r="Q611">
-        <v>13710</v>
+        <v>13750</v>
       </c>
       <c r="R611">
         <v>337476</v>
@@ -32770,10 +32770,10 @@
         <v>10553541</v>
       </c>
       <c r="P612">
-        <v>5077</v>
+        <v>5074</v>
       </c>
       <c r="Q612">
-        <v>13711</v>
+        <v>13717</v>
       </c>
       <c r="R612">
         <v>343612</v>
@@ -32882,10 +32882,10 @@
         <v>12105826</v>
       </c>
       <c r="P614">
-        <v>5159</v>
+        <v>5150</v>
       </c>
       <c r="Q614">
-        <v>13746</v>
+        <v>13743</v>
       </c>
       <c r="R614">
         <v>345096</v>
@@ -32938,10 +32938,10 @@
         <v>12600385</v>
       </c>
       <c r="P615">
-        <v>5166</v>
+        <v>5154</v>
       </c>
       <c r="Q615">
-        <v>13733</v>
+        <v>13728</v>
       </c>
       <c r="R615">
         <v>336315</v>
@@ -32994,10 +32994,10 @@
         <v>13044263</v>
       </c>
       <c r="P616">
-        <v>5196</v>
+        <v>5192</v>
       </c>
       <c r="Q616">
-        <v>13781</v>
+        <v>13779</v>
       </c>
       <c r="R616">
         <v>336681</v>
@@ -33050,10 +33050,10 @@
         <v>13246975</v>
       </c>
       <c r="P617">
-        <v>5189</v>
+        <v>5187</v>
       </c>
       <c r="Q617">
-        <v>13830</v>
+        <v>13827</v>
       </c>
       <c r="R617">
         <v>334978</v>
@@ -33109,7 +33109,7 @@
         <v>5174</v>
       </c>
       <c r="Q618">
-        <v>13854</v>
+        <v>13849</v>
       </c>
       <c r="R618">
         <v>337801</v>
@@ -33162,10 +33162,10 @@
         <v>13081161</v>
       </c>
       <c r="P619">
-        <v>5188</v>
+        <v>5199</v>
       </c>
       <c r="Q619">
-        <v>13941</v>
+        <v>13917</v>
       </c>
       <c r="R619">
         <v>328950</v>
@@ -33218,10 +33218,10 @@
         <v>12415951</v>
       </c>
       <c r="P620">
-        <v>5164</v>
+        <v>5177</v>
       </c>
       <c r="Q620">
-        <v>14023</v>
+        <v>13990</v>
       </c>
       <c r="R620">
         <v>329615</v>
@@ -33274,10 +33274,10 @@
         <v>11621754</v>
       </c>
       <c r="P621">
-        <v>5150</v>
+        <v>5155</v>
       </c>
       <c r="Q621">
-        <v>14053</v>
+        <v>14057</v>
       </c>
       <c r="R621">
         <v>334864</v>
@@ -33330,10 +33330,10 @@
         <v>8844302</v>
       </c>
       <c r="P622">
-        <v>5141</v>
+        <v>5139</v>
       </c>
       <c r="Q622">
-        <v>14047</v>
+        <v>14055</v>
       </c>
       <c r="R622">
         <v>326687</v>
@@ -33386,10 +33386,10 @@
         <v>6715937</v>
       </c>
       <c r="P623">
-        <v>5136</v>
+        <v>5132</v>
       </c>
       <c r="Q623">
-        <v>14022</v>
+        <v>14035</v>
       </c>
       <c r="R623">
         <v>326597</v>
@@ -33442,10 +33442,10 @@
         <v>5597086</v>
       </c>
       <c r="P624">
-        <v>5123</v>
+        <v>5121</v>
       </c>
       <c r="Q624">
-        <v>14028</v>
+        <v>14035</v>
       </c>
       <c r="R624">
         <v>331859</v>
@@ -33498,10 +33498,10 @@
         <v>4737483</v>
       </c>
       <c r="P625">
-        <v>5121</v>
+        <v>5122</v>
       </c>
       <c r="Q625">
-        <v>14063</v>
+        <v>14071</v>
       </c>
       <c r="R625">
         <v>331023</v>
@@ -33554,10 +33554,10 @@
         <v>4093250</v>
       </c>
       <c r="P626">
-        <v>5094</v>
+        <v>5087</v>
       </c>
       <c r="Q626">
-        <v>14084</v>
+        <v>14091</v>
       </c>
       <c r="R626">
         <v>336477</v>
@@ -33610,10 +33610,10 @@
         <v>3599110</v>
       </c>
       <c r="P627">
-        <v>5083</v>
+        <v>5070</v>
       </c>
       <c r="Q627">
-        <v>14099</v>
+        <v>14097</v>
       </c>
       <c r="R627">
         <v>342490</v>
@@ -33666,10 +33666,10 @@
         <v>3158708</v>
       </c>
       <c r="P628">
-        <v>5065</v>
+        <v>5057</v>
       </c>
       <c r="Q628">
-        <v>14118</v>
+        <v>14116</v>
       </c>
       <c r="R628">
         <v>342356</v>
@@ -33722,10 +33722,10 @@
         <v>2875209</v>
       </c>
       <c r="P629">
-        <v>5080</v>
+        <v>5075</v>
       </c>
       <c r="Q629">
-        <v>14140</v>
+        <v>14137</v>
       </c>
       <c r="R629">
         <v>348326</v>
@@ -33778,10 +33778,10 @@
         <v>2630539</v>
       </c>
       <c r="P630">
-        <v>5096</v>
+        <v>5095</v>
       </c>
       <c r="Q630">
-        <v>14153</v>
+        <v>14145</v>
       </c>
       <c r="R630">
         <v>343789</v>
@@ -33834,10 +33834,10 @@
         <v>2403701</v>
       </c>
       <c r="P631">
-        <v>5103</v>
+        <v>5104</v>
       </c>
       <c r="Q631">
-        <v>14161</v>
+        <v>14168</v>
       </c>
       <c r="R631">
         <v>347954</v>
@@ -33890,10 +33890,10 @@
         <v>2232430</v>
       </c>
       <c r="P632">
-        <v>5129</v>
+        <v>5140</v>
       </c>
       <c r="Q632">
-        <v>14272</v>
+        <v>14280</v>
       </c>
       <c r="R632">
         <v>359534</v>
@@ -33946,10 +33946,10 @@
         <v>2077437</v>
       </c>
       <c r="P633">
-        <v>5139</v>
+        <v>5146</v>
       </c>
       <c r="Q633">
-        <v>14266</v>
+        <v>14264</v>
       </c>
       <c r="R633">
         <v>361704</v>
@@ -34005,7 +34005,7 @@
         <v>5148</v>
       </c>
       <c r="Q634">
-        <v>14260</v>
+        <v>14269</v>
       </c>
       <c r="R634">
         <v>366800</v>
@@ -34058,10 +34058,10 @@
         <v>1683239</v>
       </c>
       <c r="P635">
-        <v>5143</v>
+        <v>5139</v>
       </c>
       <c r="Q635">
-        <v>14287</v>
+        <v>14301</v>
       </c>
       <c r="R635">
         <v>366024</v>
@@ -34114,10 +34114,10 @@
         <v>1584571</v>
       </c>
       <c r="P636">
-        <v>5161</v>
+        <v>5162</v>
       </c>
       <c r="Q636">
-        <v>14328</v>
+        <v>14337</v>
       </c>
       <c r="R636">
         <v>367116</v>
@@ -34170,10 +34170,10 @@
         <v>1517282</v>
       </c>
       <c r="P637">
-        <v>5131</v>
+        <v>5136</v>
       </c>
       <c r="Q637">
-        <v>14360</v>
+        <v>14364</v>
       </c>
       <c r="R637">
         <v>372938</v>
@@ -34226,10 +34226,10 @@
         <v>1480064</v>
       </c>
       <c r="P638">
-        <v>5206</v>
+        <v>5199</v>
       </c>
       <c r="Q638">
-        <v>14402</v>
+        <v>14411</v>
       </c>
       <c r="R638">
         <v>378357</v>
@@ -34282,10 +34282,10 @@
         <v>1459645</v>
       </c>
       <c r="P639">
-        <v>5229</v>
+        <v>5219</v>
       </c>
       <c r="Q639">
-        <v>14430</v>
+        <v>14439</v>
       </c>
       <c r="R639">
         <v>387772</v>
@@ -34338,10 +34338,10 @@
         <v>1421710</v>
       </c>
       <c r="P640">
-        <v>5249</v>
+        <v>5235</v>
       </c>
       <c r="Q640">
-        <v>14457</v>
+        <v>14453</v>
       </c>
       <c r="R640">
         <v>394738</v>
@@ -34394,10 +34394,10 @@
         <v>1445207</v>
       </c>
       <c r="P641">
-        <v>5263</v>
+        <v>5251</v>
       </c>
       <c r="Q641">
-        <v>14482</v>
+        <v>14478</v>
       </c>
       <c r="R641">
         <v>403577</v>
@@ -34450,10 +34450,10 @@
         <v>1475556</v>
       </c>
       <c r="P642">
-        <v>5280</v>
+        <v>5272</v>
       </c>
       <c r="Q642">
-        <v>14508</v>
+        <v>14509</v>
       </c>
       <c r="R642">
         <v>411117</v>
@@ -34506,10 +34506,10 @@
         <v>1504960</v>
       </c>
       <c r="P643">
-        <v>5301</v>
+        <v>5294</v>
       </c>
       <c r="Q643">
-        <v>14536</v>
+        <v>14565</v>
       </c>
       <c r="R643">
         <v>418667</v>
@@ -34562,10 +34562,10 @@
         <v>1556991</v>
       </c>
       <c r="P644">
-        <v>5301</v>
+        <v>5303</v>
       </c>
       <c r="Q644">
-        <v>14564</v>
+        <v>14589</v>
       </c>
       <c r="R644">
         <v>417761</v>
@@ -34618,10 +34618,10 @@
         <v>1594594</v>
       </c>
       <c r="P645">
-        <v>5329</v>
+        <v>5324</v>
       </c>
       <c r="Q645">
-        <v>14585</v>
+        <v>14603</v>
       </c>
       <c r="R645">
         <v>420853</v>
@@ -34674,10 +34674,10 @@
         <v>1632935</v>
       </c>
       <c r="P646">
-        <v>5346</v>
+        <v>5337</v>
       </c>
       <c r="Q646">
-        <v>14612</v>
+        <v>14653</v>
       </c>
       <c r="R646">
         <v>429575</v>
@@ -34730,10 +34730,10 @@
         <v>1688430</v>
       </c>
       <c r="P647">
-        <v>5375</v>
+        <v>5359</v>
       </c>
       <c r="Q647">
-        <v>14642</v>
+        <v>14693</v>
       </c>
       <c r="R647">
         <v>440206</v>
@@ -34786,10 +34786,10 @@
         <v>1727451</v>
       </c>
       <c r="P648">
-        <v>5383</v>
+        <v>5366</v>
       </c>
       <c r="Q648">
-        <v>14665</v>
+        <v>14728</v>
       </c>
       <c r="R648">
         <v>445839</v>
@@ -34842,10 +34842,10 @@
         <v>1772185</v>
       </c>
       <c r="P649">
-        <v>5404</v>
+        <v>5378</v>
       </c>
       <c r="Q649">
-        <v>14711</v>
+        <v>14763</v>
       </c>
       <c r="R649">
         <v>446422</v>
@@ -34898,10 +34898,10 @@
         <v>1816373</v>
       </c>
       <c r="P650">
-        <v>5420</v>
+        <v>5390</v>
       </c>
       <c r="Q650">
-        <v>14742</v>
+        <v>14786</v>
       </c>
       <c r="R650">
         <v>442338</v>
@@ -34954,10 +34954,10 @@
         <v>1855195</v>
       </c>
       <c r="P651">
-        <v>5434</v>
+        <v>5404</v>
       </c>
       <c r="Q651">
-        <v>14776</v>
+        <v>14835</v>
       </c>
       <c r="R651">
         <v>445503</v>
@@ -35010,10 +35010,10 @@
         <v>1888538</v>
       </c>
       <c r="P652">
-        <v>5444</v>
+        <v>5414</v>
       </c>
       <c r="Q652">
-        <v>14832</v>
+        <v>14890</v>
       </c>
       <c r="R652">
         <v>450173</v>
@@ -35024,7 +35024,7 @@
         <v>45412</v>
       </c>
       <c r="B653">
-        <v>901499</v>
+        <v>901545</v>
       </c>
       <c r="C653">
         <v>1807.6</v>
@@ -35036,7 +35036,7 @@
         <v>185615</v>
       </c>
       <c r="F653">
-        <v>7953125</v>
+        <v>7953210</v>
       </c>
       <c r="G653">
         <v>7093323</v>
@@ -35066,10 +35066,10 @@
         <v>1925423</v>
       </c>
       <c r="P653">
-        <v>5448</v>
+        <v>5418</v>
       </c>
       <c r="Q653">
-        <v>14828</v>
+        <v>14877</v>
       </c>
       <c r="R653">
         <v>450938</v>
@@ -35080,7 +35080,7 @@
         <v>45443</v>
       </c>
       <c r="B654">
-        <v>879489</v>
+        <v>879370</v>
       </c>
       <c r="C654">
         <v>1650</v>
@@ -35092,7 +35092,7 @@
         <v>168510</v>
       </c>
       <c r="F654">
-        <v>7049042</v>
+        <v>7049151</v>
       </c>
       <c r="G654">
         <v>6013043</v>
@@ -35122,10 +35122,10 @@
         <v>1938241</v>
       </c>
       <c r="P654">
-        <v>5429</v>
+        <v>5420</v>
       </c>
       <c r="Q654">
-        <v>14856</v>
+        <v>14905</v>
       </c>
       <c r="R654">
         <v>450559</v>
@@ -35136,7 +35136,7 @@
         <v>45473</v>
       </c>
       <c r="B655">
-        <v>968764</v>
+        <v>968522</v>
       </c>
       <c r="C655">
         <v>1736.8</v>
@@ -35148,7 +35148,7 @@
         <v>159554</v>
       </c>
       <c r="F655">
-        <v>7674226</v>
+        <v>7674321</v>
       </c>
       <c r="G655">
         <v>6015491</v>
@@ -35178,10 +35178,10 @@
         <v>1962179</v>
       </c>
       <c r="P655">
-        <v>5436</v>
+        <v>5429</v>
       </c>
       <c r="Q655">
-        <v>14868</v>
+        <v>14915</v>
       </c>
       <c r="R655">
         <v>452201</v>
@@ -35192,7 +35192,7 @@
         <v>45504</v>
       </c>
       <c r="B656">
-        <v>1066057</v>
+        <v>1065985</v>
       </c>
       <c r="C656">
         <v>1901</v>
@@ -35204,7 +35204,7 @@
         <v>181829</v>
       </c>
       <c r="F656">
-        <v>8487700</v>
+        <v>8487804</v>
       </c>
       <c r="G656">
         <v>7347349</v>
@@ -35234,10 +35234,10 @@
         <v>1978634</v>
       </c>
       <c r="P656">
-        <v>5459</v>
+        <v>5444</v>
       </c>
       <c r="Q656">
-        <v>14890</v>
+        <v>14946</v>
       </c>
       <c r="R656">
         <v>456588</v>
@@ -35248,7 +35248,7 @@
         <v>45535</v>
       </c>
       <c r="B657">
-        <v>848669</v>
+        <v>848460</v>
       </c>
       <c r="C657">
         <v>1817.9</v>
@@ -35260,7 +35260,7 @@
         <v>164528</v>
       </c>
       <c r="F657">
-        <v>7586001</v>
+        <v>7586180</v>
       </c>
       <c r="G657">
         <v>6466287</v>
@@ -35290,10 +35290,10 @@
         <v>1987040</v>
       </c>
       <c r="P657">
-        <v>5473</v>
+        <v>5453</v>
       </c>
       <c r="Q657">
-        <v>14916</v>
+        <v>14973</v>
       </c>
       <c r="R657">
         <v>458308</v>
@@ -35304,7 +35304,7 @@
         <v>45565</v>
       </c>
       <c r="B658">
-        <v>792215</v>
+        <v>792151</v>
       </c>
       <c r="C658">
         <v>1615.9</v>
@@ -35316,7 +35316,7 @@
         <v>169526</v>
       </c>
       <c r="F658">
-        <v>7613585</v>
+        <v>7613704</v>
       </c>
       <c r="G658">
         <v>6230313</v>
@@ -35346,10 +35346,10 @@
         <v>2015409</v>
       </c>
       <c r="P658">
-        <v>5495</v>
+        <v>5468</v>
       </c>
       <c r="Q658">
-        <v>14923</v>
+        <v>14986</v>
       </c>
       <c r="R658">
         <v>466887</v>
@@ -35360,7 +35360,7 @@
         <v>45596</v>
       </c>
       <c r="B659">
-        <v>976845</v>
+        <v>976745</v>
       </c>
       <c r="C659">
         <v>1620.6</v>
@@ -35372,7 +35372,7 @@
         <v>165272</v>
       </c>
       <c r="F659">
-        <v>6904022</v>
+        <v>6904139</v>
       </c>
       <c r="G659">
         <v>5923759</v>
@@ -35402,13 +35402,13 @@
         <v>2010972</v>
       </c>
       <c r="P659">
-        <v>5508</v>
+        <v>5484</v>
       </c>
       <c r="Q659">
-        <v>14941</v>
+        <v>15012</v>
       </c>
       <c r="R659">
-        <v>465683</v>
+        <v>468844</v>
       </c>
     </row>
     <row r="660">
@@ -35416,7 +35416,7 @@
         <v>45626</v>
       </c>
       <c r="B660">
-        <v>941073</v>
+        <v>940818</v>
       </c>
       <c r="C660">
         <v>1681.3</v>
@@ -35428,7 +35428,7 @@
         <v>155499</v>
       </c>
       <c r="F660">
-        <v>6728016</v>
+        <v>6728220</v>
       </c>
       <c r="G660">
         <v>5563175</v>
@@ -35458,13 +35458,13 @@
         <v>2015372</v>
       </c>
       <c r="P660">
-        <v>5521</v>
+        <v>5493</v>
       </c>
       <c r="Q660">
-        <v>14958</v>
+        <v>15022</v>
       </c>
       <c r="R660">
-        <v>465284</v>
+        <v>468508</v>
       </c>
     </row>
     <row r="661">
@@ -35472,7 +35472,7 @@
         <v>45657</v>
       </c>
       <c r="B661">
-        <v>1286585</v>
+        <v>1286331</v>
       </c>
       <c r="C661">
         <v>1926.7</v>
@@ -35484,7 +35484,7 @@
         <v>194345</v>
       </c>
       <c r="F661">
-        <v>9204439</v>
+        <v>9204571</v>
       </c>
       <c r="G661">
         <v>7721352</v>
@@ -35514,10 +35514,66 @@
         <v>2050424</v>
       </c>
       <c r="P661">
-        <v>5531</v>
+        <v>5504</v>
       </c>
       <c r="Q661">
-        <v>14975</v>
+        <v>15039</v>
+      </c>
+      <c r="R661">
+        <v>466031</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="2">
+        <v>45688</v>
+      </c>
+      <c r="B662">
+        <v>1262560</v>
+      </c>
+      <c r="C662">
+        <v>2144.7</v>
+      </c>
+      <c r="D662">
+        <v>702980</v>
+      </c>
+      <c r="E662">
+        <v>174717</v>
+      </c>
+      <c r="F662">
+        <v>9260875</v>
+      </c>
+      <c r="G662">
+        <v>7846406</v>
+      </c>
+      <c r="H662">
+        <v>3602761</v>
+      </c>
+      <c r="I662">
+        <v>468.4</v>
+      </c>
+      <c r="J662">
+        <v>38.81</v>
+      </c>
+      <c r="K662">
+        <v>15.11</v>
+      </c>
+      <c r="L662">
+        <v>454.68</v>
+      </c>
+      <c r="M662">
+        <v>36132972</v>
+      </c>
+      <c r="N662">
+        <v>5355542</v>
+      </c>
+      <c r="O662">
+        <v>2040637</v>
+      </c>
+      <c r="P662">
+        <v>5506</v>
+      </c>
+      <c r="Q662">
+        <v>15060</v>
       </c>
     </row>
   </sheetData>

--- a/data/monthly_state_ui.xlsx
+++ b/data/monthly_state_ui.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R662"/>
+  <dimension ref="A1:R663"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -4781,7 +4781,7 @@
         <v>210660</v>
       </c>
       <c r="F98">
-        <v>13886944</v>
+        <v>13886945</v>
       </c>
       <c r="G98">
         <v>11076378</v>
@@ -4961,7 +4961,7 @@
         <v>80.95</v>
       </c>
       <c r="M101">
-        <v>8496272</v>
+        <v>8496273</v>
       </c>
       <c r="N101">
         <v>7630816</v>
@@ -5067,7 +5067,7 @@
         <v>81.73999999999999</v>
       </c>
       <c r="M103">
-        <v>8390313</v>
+        <v>8390314</v>
       </c>
       <c r="N103">
         <v>7610191</v>
@@ -6589,7 +6589,7 @@
         <v>9516801</v>
       </c>
       <c r="H132">
-        <v>935714</v>
+        <v>935650</v>
       </c>
       <c r="I132">
         <v>100.73</v>
@@ -6604,7 +6604,7 @@
         <v>99.05</v>
       </c>
       <c r="M132">
-        <v>14067261</v>
+        <v>14067197</v>
       </c>
       <c r="N132">
         <v>9919645</v>
@@ -6657,7 +6657,7 @@
         <v>99.53</v>
       </c>
       <c r="M133">
-        <v>14469713</v>
+        <v>14469649</v>
       </c>
       <c r="N133">
         <v>9992123</v>
@@ -6710,7 +6710,7 @@
         <v>100.2</v>
       </c>
       <c r="M134">
-        <v>14605349</v>
+        <v>14605285</v>
       </c>
       <c r="N134">
         <v>9946214</v>
@@ -6763,7 +6763,7 @@
         <v>100.72</v>
       </c>
       <c r="M135">
-        <v>14690785</v>
+        <v>14690721</v>
       </c>
       <c r="N135">
         <v>9890722</v>
@@ -6816,7 +6816,7 @@
         <v>101.31</v>
       </c>
       <c r="M136">
-        <v>14867245</v>
+        <v>14867181</v>
       </c>
       <c r="N136">
         <v>9919839</v>
@@ -6869,7 +6869,7 @@
         <v>101.83</v>
       </c>
       <c r="M137">
-        <v>14861763</v>
+        <v>14861699</v>
       </c>
       <c r="N137">
         <v>9793604</v>
@@ -6922,7 +6922,7 @@
         <v>102.25</v>
       </c>
       <c r="M138">
-        <v>14671154</v>
+        <v>14671090</v>
       </c>
       <c r="N138">
         <v>9476838</v>
@@ -6975,7 +6975,7 @@
         <v>102.61</v>
       </c>
       <c r="M139">
-        <v>14467379</v>
+        <v>14467316</v>
       </c>
       <c r="N139">
         <v>9214474</v>
@@ -7001,7 +7001,7 @@
         <v>2112151</v>
       </c>
       <c r="D140">
-        <v>823652</v>
+        <v>823657</v>
       </c>
       <c r="E140">
         <v>246909</v>
@@ -7028,10 +7028,10 @@
         <v>103.08</v>
       </c>
       <c r="M140">
-        <v>14132159</v>
+        <v>14132095</v>
       </c>
       <c r="N140">
-        <v>8935488</v>
+        <v>8935493</v>
       </c>
       <c r="O140">
         <v>3281695</v>
@@ -7081,10 +7081,10 @@
         <v>103.59</v>
       </c>
       <c r="M141">
-        <v>13894456</v>
+        <v>13894392</v>
       </c>
       <c r="N141">
-        <v>8782003</v>
+        <v>8782008</v>
       </c>
       <c r="O141">
         <v>3240512</v>
@@ -7131,13 +7131,13 @@
         <v>15.43</v>
       </c>
       <c r="L142">
-        <v>104.15</v>
+        <v>104.14</v>
       </c>
       <c r="M142">
-        <v>13750363</v>
+        <v>13750299</v>
       </c>
       <c r="N142">
-        <v>8776271</v>
+        <v>8776276</v>
       </c>
       <c r="O142">
         <v>3193123</v>
@@ -7187,10 +7187,10 @@
         <v>104.75</v>
       </c>
       <c r="M143">
-        <v>13622231</v>
+        <v>13622167</v>
       </c>
       <c r="N143">
-        <v>8836713</v>
+        <v>8836718</v>
       </c>
       <c r="O143">
         <v>3101549</v>
@@ -7243,7 +7243,7 @@
         <v>13767328</v>
       </c>
       <c r="N144">
-        <v>9042521</v>
+        <v>9042526</v>
       </c>
       <c r="O144">
         <v>3043526</v>
@@ -7296,7 +7296,7 @@
         <v>14113290</v>
       </c>
       <c r="N145">
-        <v>9395141</v>
+        <v>9395146</v>
       </c>
       <c r="O145">
         <v>2989177</v>
@@ -7349,7 +7349,7 @@
         <v>14458798</v>
       </c>
       <c r="N146">
-        <v>9716005</v>
+        <v>9716010</v>
       </c>
       <c r="O146">
         <v>2937578</v>
@@ -7402,7 +7402,7 @@
         <v>14926884</v>
       </c>
       <c r="N147">
-        <v>9916836</v>
+        <v>9916841</v>
       </c>
       <c r="O147">
         <v>2929529</v>
@@ -7455,7 +7455,7 @@
         <v>15607688</v>
       </c>
       <c r="N148">
-        <v>10176469</v>
+        <v>10176474</v>
       </c>
       <c r="O148">
         <v>2979966</v>
@@ -7508,7 +7508,7 @@
         <v>16230878</v>
       </c>
       <c r="N149">
-        <v>10402050</v>
+        <v>10402055</v>
       </c>
       <c r="O149">
         <v>3052828</v>
@@ -7561,7 +7561,7 @@
         <v>16798094</v>
       </c>
       <c r="N150">
-        <v>10586450</v>
+        <v>10586455</v>
       </c>
       <c r="O150">
         <v>3145040</v>
@@ -7614,7 +7614,7 @@
         <v>17524614</v>
       </c>
       <c r="N151">
-        <v>10834363</v>
+        <v>10834368</v>
       </c>
       <c r="O151">
         <v>3279005</v>
@@ -9439,7 +9439,7 @@
         <v>1488338</v>
       </c>
       <c r="D186">
-        <v>590442</v>
+        <v>590447</v>
       </c>
       <c r="E186">
         <v>232183</v>
@@ -9448,13 +9448,13 @@
         <v>10937527</v>
       </c>
       <c r="G186">
-        <v>9817589</v>
+        <v>9817707</v>
       </c>
       <c r="H186">
-        <v>1208666</v>
+        <v>1208631</v>
       </c>
       <c r="I186">
-        <v>127.34</v>
+        <v>127.33</v>
       </c>
       <c r="J186">
         <v>32.49</v>
@@ -9466,10 +9466,10 @@
         <v>125.18</v>
       </c>
       <c r="M186">
-        <v>13889456</v>
+        <v>13889421</v>
       </c>
       <c r="N186">
-        <v>8211247</v>
+        <v>8211252</v>
       </c>
       <c r="O186">
         <v>2510371</v>
@@ -9519,10 +9519,10 @@
         <v>125.48</v>
       </c>
       <c r="M187">
-        <v>13965689</v>
+        <v>13965654</v>
       </c>
       <c r="N187">
-        <v>8231238</v>
+        <v>8231243</v>
       </c>
       <c r="O187">
         <v>2506811</v>
@@ -9572,10 +9572,10 @@
         <v>125.89</v>
       </c>
       <c r="M188">
-        <v>14176922</v>
+        <v>14176887</v>
       </c>
       <c r="N188">
-        <v>8311024</v>
+        <v>8311029</v>
       </c>
       <c r="O188">
         <v>2528409</v>
@@ -9625,10 +9625,10 @@
         <v>126.37</v>
       </c>
       <c r="M189">
-        <v>14260230</v>
+        <v>14260195</v>
       </c>
       <c r="N189">
-        <v>8315384</v>
+        <v>8315389</v>
       </c>
       <c r="O189">
         <v>2521451</v>
@@ -9678,10 +9678,10 @@
         <v>126.78</v>
       </c>
       <c r="M190">
-        <v>14422557</v>
+        <v>14422522</v>
       </c>
       <c r="N190">
-        <v>8370965</v>
+        <v>8370970</v>
       </c>
       <c r="O190">
         <v>2540054</v>
@@ -9704,22 +9704,22 @@
         <v>1667576</v>
       </c>
       <c r="D191">
-        <v>573571</v>
+        <v>573573</v>
       </c>
       <c r="E191">
-        <v>207667</v>
+        <v>207668</v>
       </c>
       <c r="F191">
         <v>9966680</v>
       </c>
       <c r="G191">
-        <v>8670742</v>
+        <v>8670779</v>
       </c>
       <c r="H191">
-        <v>1073136</v>
+        <v>1073133</v>
       </c>
       <c r="I191">
-        <v>128.6</v>
+        <v>128.59</v>
       </c>
       <c r="J191">
         <v>31.29</v>
@@ -9731,13 +9731,13 @@
         <v>127.14</v>
       </c>
       <c r="M191">
-        <v>14527790</v>
+        <v>14527752</v>
       </c>
       <c r="N191">
-        <v>8368510</v>
+        <v>8368517</v>
       </c>
       <c r="O191">
-        <v>2551077</v>
+        <v>2551078</v>
       </c>
       <c r="P191">
         <v>3864</v>
@@ -9784,13 +9784,13 @@
         <v>127.59</v>
       </c>
       <c r="M192">
-        <v>14532564</v>
+        <v>14532527</v>
       </c>
       <c r="N192">
-        <v>8290084</v>
+        <v>8290091</v>
       </c>
       <c r="O192">
-        <v>2547699</v>
+        <v>2547700</v>
       </c>
       <c r="P192">
         <v>3867</v>
@@ -9837,13 +9837,13 @@
         <v>128.13</v>
       </c>
       <c r="M193">
-        <v>14761088</v>
+        <v>14761050</v>
       </c>
       <c r="N193">
-        <v>8365176</v>
+        <v>8365183</v>
       </c>
       <c r="O193">
-        <v>2572347</v>
+        <v>2572348</v>
       </c>
       <c r="P193">
         <v>3862</v>
@@ -9869,7 +9869,7 @@
         <v>235008</v>
       </c>
       <c r="F194">
-        <v>14729040</v>
+        <v>14729043</v>
       </c>
       <c r="G194">
         <v>13027499</v>
@@ -9890,13 +9890,13 @@
         <v>128.88</v>
       </c>
       <c r="M194">
-        <v>14843769</v>
+        <v>14843731</v>
       </c>
       <c r="N194">
-        <v>8388063</v>
+        <v>8388070</v>
       </c>
       <c r="O194">
-        <v>2570147</v>
+        <v>2570148</v>
       </c>
       <c r="P194">
         <v>3869</v>
@@ -9943,13 +9943,13 @@
         <v>129.54</v>
       </c>
       <c r="M195">
-        <v>14888699</v>
+        <v>14888662</v>
       </c>
       <c r="N195">
-        <v>8325535</v>
+        <v>8325542</v>
       </c>
       <c r="O195">
-        <v>2571036</v>
+        <v>2571037</v>
       </c>
       <c r="P195">
         <v>3875</v>
@@ -9975,7 +9975,7 @@
         <v>219934</v>
       </c>
       <c r="F196">
-        <v>13097746</v>
+        <v>13097747</v>
       </c>
       <c r="G196">
         <v>11730221</v>
@@ -9996,13 +9996,13 @@
         <v>130.19</v>
       </c>
       <c r="M196">
-        <v>14967381</v>
+        <v>14967343</v>
       </c>
       <c r="N196">
-        <v>8320031</v>
+        <v>8320038</v>
       </c>
       <c r="O196">
-        <v>2563110</v>
+        <v>2563111</v>
       </c>
       <c r="P196">
         <v>3873</v>
@@ -10049,13 +10049,13 @@
         <v>130.86</v>
       </c>
       <c r="M197">
-        <v>15089525</v>
+        <v>15089488</v>
       </c>
       <c r="N197">
-        <v>8341495</v>
+        <v>8341502</v>
       </c>
       <c r="O197">
-        <v>2566565</v>
+        <v>2566566</v>
       </c>
       <c r="P197">
         <v>3878</v>
@@ -10102,13 +10102,13 @@
         <v>131.55</v>
       </c>
       <c r="M198">
-        <v>15141584</v>
+        <v>15141581</v>
       </c>
       <c r="N198">
-        <v>8330331</v>
+        <v>8330333</v>
       </c>
       <c r="O198">
-        <v>2567366</v>
+        <v>2567367</v>
       </c>
       <c r="P198">
         <v>3884</v>
@@ -10134,7 +10134,7 @@
         <v>214626</v>
       </c>
       <c r="F199">
-        <v>10187280</v>
+        <v>10187281</v>
       </c>
       <c r="G199">
         <v>9028611</v>
@@ -10155,13 +10155,13 @@
         <v>132.19</v>
       </c>
       <c r="M199">
-        <v>15309128</v>
+        <v>15309125</v>
       </c>
       <c r="N199">
-        <v>8356579</v>
+        <v>8356581</v>
       </c>
       <c r="O199">
-        <v>2587916</v>
+        <v>2587917</v>
       </c>
       <c r="P199">
         <v>3887</v>
@@ -10208,13 +10208,13 @@
         <v>132.87</v>
       </c>
       <c r="M200">
-        <v>15440738</v>
+        <v>15440735</v>
       </c>
       <c r="N200">
-        <v>8350598</v>
+        <v>8350600</v>
       </c>
       <c r="O200">
-        <v>2599966</v>
+        <v>2599967</v>
       </c>
       <c r="P200">
         <v>3886</v>
@@ -10237,7 +10237,7 @@
         <v>649662</v>
       </c>
       <c r="E201">
-        <v>210438</v>
+        <v>210437</v>
       </c>
       <c r="F201">
         <v>10189513</v>
@@ -10261,10 +10261,10 @@
         <v>133.49</v>
       </c>
       <c r="M201">
-        <v>15510512</v>
+        <v>15510509</v>
       </c>
       <c r="N201">
-        <v>8368341</v>
+        <v>8368343</v>
       </c>
       <c r="O201">
         <v>2605538</v>
@@ -10293,7 +10293,7 @@
         <v>211859</v>
       </c>
       <c r="F202">
-        <v>10071131</v>
+        <v>10071148</v>
       </c>
       <c r="G202">
         <v>8724780</v>
@@ -10314,10 +10314,10 @@
         <v>134.05</v>
       </c>
       <c r="M202">
-        <v>15673822</v>
+        <v>15673819</v>
       </c>
       <c r="N202">
-        <v>8381898</v>
+        <v>8381900</v>
       </c>
       <c r="O202">
         <v>2635456</v>
@@ -10346,7 +10346,7 @@
         <v>223173</v>
       </c>
       <c r="F203">
-        <v>9851199</v>
+        <v>9851206</v>
       </c>
       <c r="G203">
         <v>8695175</v>
@@ -10373,7 +10373,7 @@
         <v>8380544</v>
       </c>
       <c r="O203">
-        <v>2650962</v>
+        <v>2650961</v>
       </c>
       <c r="P203">
         <v>3915</v>
@@ -10426,7 +10426,7 @@
         <v>8330361</v>
       </c>
       <c r="O204">
-        <v>2658784</v>
+        <v>2658783</v>
       </c>
       <c r="P204">
         <v>3927</v>
@@ -10479,7 +10479,7 @@
         <v>8360752</v>
       </c>
       <c r="O205">
-        <v>2687333</v>
+        <v>2687332</v>
       </c>
       <c r="P205">
         <v>3938</v>
@@ -10532,7 +10532,7 @@
         <v>8190399</v>
       </c>
       <c r="O206">
-        <v>2682387</v>
+        <v>2682386</v>
       </c>
       <c r="P206">
         <v>3943</v>
@@ -10585,7 +10585,7 @@
         <v>8167954</v>
       </c>
       <c r="O207">
-        <v>2694738</v>
+        <v>2694737</v>
       </c>
       <c r="P207">
         <v>3943</v>
@@ -10638,7 +10638,7 @@
         <v>8133267</v>
       </c>
       <c r="O208">
-        <v>2719321</v>
+        <v>2719320</v>
       </c>
       <c r="P208">
         <v>3945</v>
@@ -10691,7 +10691,7 @@
         <v>8038963</v>
       </c>
       <c r="O209">
-        <v>2707763</v>
+        <v>2707762</v>
       </c>
       <c r="P209">
         <v>3954</v>
@@ -10744,7 +10744,7 @@
         <v>7908330</v>
       </c>
       <c r="O210">
-        <v>2680328</v>
+        <v>2680327</v>
       </c>
       <c r="P210">
         <v>3955</v>
@@ -10797,7 +10797,7 @@
         <v>7873641</v>
       </c>
       <c r="O211">
-        <v>2671970</v>
+        <v>2671969</v>
       </c>
       <c r="P211">
         <v>3950</v>
@@ -10850,7 +10850,7 @@
         <v>7781838</v>
       </c>
       <c r="O212">
-        <v>2637231</v>
+        <v>2637230</v>
       </c>
       <c r="P212">
         <v>3967</v>
@@ -11883,7 +11883,7 @@
         <v>176192</v>
       </c>
       <c r="F232">
-        <v>11588960</v>
+        <v>11588959</v>
       </c>
       <c r="G232">
         <v>10451849</v>
@@ -35360,25 +35360,25 @@
         <v>45596</v>
       </c>
       <c r="B659">
-        <v>976745</v>
+        <v>976719</v>
       </c>
       <c r="C659">
         <v>1620.6</v>
       </c>
       <c r="D659">
-        <v>392516</v>
+        <v>392515</v>
       </c>
       <c r="E659">
-        <v>165272</v>
+        <v>165270</v>
       </c>
       <c r="F659">
-        <v>6904139</v>
+        <v>6904002</v>
       </c>
       <c r="G659">
-        <v>5923759</v>
+        <v>5923756</v>
       </c>
       <c r="H659">
-        <v>2667050</v>
+        <v>2667049</v>
       </c>
       <c r="I659">
         <v>458.86</v>
@@ -35393,13 +35393,13 @@
         <v>452.16</v>
       </c>
       <c r="M659">
-        <v>35640460</v>
+        <v>35640459</v>
       </c>
       <c r="N659">
-        <v>5281068</v>
+        <v>5281067</v>
       </c>
       <c r="O659">
-        <v>2010972</v>
+        <v>2010970</v>
       </c>
       <c r="P659">
         <v>5484</v>
@@ -35416,25 +35416,25 @@
         <v>45626</v>
       </c>
       <c r="B660">
-        <v>940818</v>
+        <v>940793</v>
       </c>
       <c r="C660">
         <v>1681.3</v>
       </c>
       <c r="D660">
-        <v>368899</v>
+        <v>368900</v>
       </c>
       <c r="E660">
         <v>155499</v>
       </c>
       <c r="F660">
-        <v>6728220</v>
+        <v>6728140</v>
       </c>
       <c r="G660">
-        <v>5563175</v>
+        <v>5563171</v>
       </c>
       <c r="H660">
-        <v>2513668</v>
+        <v>2513669</v>
       </c>
       <c r="I660">
         <v>460.95</v>
@@ -35455,7 +35455,7 @@
         <v>5256639</v>
       </c>
       <c r="O660">
-        <v>2015372</v>
+        <v>2015370</v>
       </c>
       <c r="P660">
         <v>5493</v>
@@ -35464,7 +35464,7 @@
         <v>15022</v>
       </c>
       <c r="R660">
-        <v>468508</v>
+        <v>469357</v>
       </c>
     </row>
     <row r="661">
@@ -35472,7 +35472,7 @@
         <v>45657</v>
       </c>
       <c r="B661">
-        <v>1286331</v>
+        <v>1286291</v>
       </c>
       <c r="C661">
         <v>1926.7</v>
@@ -35481,16 +35481,16 @@
         <v>541871</v>
       </c>
       <c r="E661">
-        <v>194345</v>
+        <v>194340</v>
       </c>
       <c r="F661">
-        <v>9204571</v>
+        <v>9204459</v>
       </c>
       <c r="G661">
-        <v>7721352</v>
+        <v>7721346</v>
       </c>
       <c r="H661">
-        <v>3511565</v>
+        <v>3511562</v>
       </c>
       <c r="I661">
         <v>463.66</v>
@@ -35505,22 +35505,22 @@
         <v>453.85</v>
       </c>
       <c r="M661">
-        <v>36307411</v>
+        <v>36307408</v>
       </c>
       <c r="N661">
         <v>5333071</v>
       </c>
       <c r="O661">
-        <v>2050424</v>
+        <v>2050417</v>
       </c>
       <c r="P661">
-        <v>5504</v>
+        <v>5512</v>
       </c>
       <c r="Q661">
-        <v>15039</v>
+        <v>15036</v>
       </c>
       <c r="R661">
-        <v>466031</v>
+        <v>469232</v>
       </c>
     </row>
     <row r="662">
@@ -35528,52 +35528,108 @@
         <v>45688</v>
       </c>
       <c r="B662">
-        <v>1262560</v>
+        <v>1230480</v>
       </c>
       <c r="C662">
         <v>2144.7</v>
       </c>
       <c r="D662">
-        <v>702980</v>
+        <v>689057</v>
       </c>
       <c r="E662">
-        <v>174717</v>
+        <v>180879</v>
       </c>
       <c r="F662">
-        <v>9260875</v>
+        <v>9272720</v>
       </c>
       <c r="G662">
-        <v>7846406</v>
+        <v>7923862</v>
       </c>
       <c r="H662">
-        <v>3602761</v>
+        <v>3653058</v>
       </c>
       <c r="I662">
-        <v>468.4</v>
+        <v>470.47</v>
       </c>
       <c r="J662">
-        <v>38.81</v>
+        <v>38.92</v>
       </c>
       <c r="K662">
-        <v>15.11</v>
+        <v>15.17</v>
       </c>
       <c r="L662">
-        <v>454.68</v>
+        <v>454.89</v>
       </c>
       <c r="M662">
-        <v>36132972</v>
+        <v>36183265</v>
       </c>
       <c r="N662">
-        <v>5355542</v>
+        <v>5341619</v>
       </c>
       <c r="O662">
-        <v>2040637</v>
+        <v>2046793</v>
       </c>
       <c r="P662">
-        <v>5506</v>
+        <v>5531</v>
       </c>
       <c r="Q662">
-        <v>15060</v>
+        <v>15056</v>
+      </c>
+      <c r="R662">
+        <v>468748</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="2">
+        <v>45716</v>
+      </c>
+      <c r="B663">
+        <v>937358</v>
+      </c>
+      <c r="C663">
+        <v>2141</v>
+      </c>
+      <c r="D663">
+        <v>492916</v>
+      </c>
+      <c r="E663">
+        <v>169403</v>
+      </c>
+      <c r="F663">
+        <v>8640604</v>
+      </c>
+      <c r="G663">
+        <v>7485551</v>
+      </c>
+      <c r="H663">
+        <v>3446546</v>
+      </c>
+      <c r="I663">
+        <v>468.44</v>
+      </c>
+      <c r="J663">
+        <v>39.28</v>
+      </c>
+      <c r="K663">
+        <v>15.18</v>
+      </c>
+      <c r="L663">
+        <v>455.71</v>
+      </c>
+      <c r="M663">
+        <v>36290736</v>
+      </c>
+      <c r="N663">
+        <v>5343979</v>
+      </c>
+      <c r="O663">
+        <v>2058727</v>
+      </c>
+      <c r="P663">
+        <v>5532</v>
+      </c>
+      <c r="Q663">
+        <v>15076</v>
       </c>
     </row>
   </sheetData>

--- a/data/monthly_state_ui.xlsx
+++ b/data/monthly_state_ui.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R663"/>
+  <dimension ref="A1:R664"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -4784,7 +4784,7 @@
         <v>13886945</v>
       </c>
       <c r="G98">
-        <v>11076378</v>
+        <v>11076379</v>
       </c>
       <c r="H98">
         <v>904867</v>
@@ -5226,7 +5226,7 @@
         <v>82.78</v>
       </c>
       <c r="M106">
-        <v>8313958</v>
+        <v>8313959</v>
       </c>
       <c r="N106">
         <v>7636142</v>
@@ -5279,7 +5279,7 @@
         <v>83.03</v>
       </c>
       <c r="M107">
-        <v>8307253</v>
+        <v>8307254</v>
       </c>
       <c r="N107">
         <v>7633029</v>
@@ -6589,10 +6589,10 @@
         <v>9516801</v>
       </c>
       <c r="H132">
-        <v>935650</v>
+        <v>935554</v>
       </c>
       <c r="I132">
-        <v>100.73</v>
+        <v>100.72</v>
       </c>
       <c r="J132">
         <v>32.75</v>
@@ -6604,7 +6604,7 @@
         <v>99.05</v>
       </c>
       <c r="M132">
-        <v>14067197</v>
+        <v>14067101</v>
       </c>
       <c r="N132">
         <v>9919645</v>
@@ -6657,7 +6657,7 @@
         <v>99.53</v>
       </c>
       <c r="M133">
-        <v>14469649</v>
+        <v>14469554</v>
       </c>
       <c r="N133">
         <v>9992123</v>
@@ -6710,7 +6710,7 @@
         <v>100.2</v>
       </c>
       <c r="M134">
-        <v>14605285</v>
+        <v>14605189</v>
       </c>
       <c r="N134">
         <v>9946214</v>
@@ -6763,7 +6763,7 @@
         <v>100.72</v>
       </c>
       <c r="M135">
-        <v>14690721</v>
+        <v>14690626</v>
       </c>
       <c r="N135">
         <v>9890722</v>
@@ -6816,7 +6816,7 @@
         <v>101.31</v>
       </c>
       <c r="M136">
-        <v>14867181</v>
+        <v>14867085</v>
       </c>
       <c r="N136">
         <v>9919839</v>
@@ -6869,7 +6869,7 @@
         <v>101.83</v>
       </c>
       <c r="M137">
-        <v>14861699</v>
+        <v>14861603</v>
       </c>
       <c r="N137">
         <v>9793604</v>
@@ -6922,7 +6922,7 @@
         <v>102.25</v>
       </c>
       <c r="M138">
-        <v>14671090</v>
+        <v>14670995</v>
       </c>
       <c r="N138">
         <v>9476838</v>
@@ -6975,7 +6975,7 @@
         <v>102.61</v>
       </c>
       <c r="M139">
-        <v>14467316</v>
+        <v>14467220</v>
       </c>
       <c r="N139">
         <v>9214474</v>
@@ -7001,7 +7001,7 @@
         <v>2112151</v>
       </c>
       <c r="D140">
-        <v>823657</v>
+        <v>823661</v>
       </c>
       <c r="E140">
         <v>246909</v>
@@ -7028,10 +7028,10 @@
         <v>103.08</v>
       </c>
       <c r="M140">
-        <v>14132095</v>
+        <v>14132000</v>
       </c>
       <c r="N140">
-        <v>8935493</v>
+        <v>8935497</v>
       </c>
       <c r="O140">
         <v>3281695</v>
@@ -7081,10 +7081,10 @@
         <v>103.59</v>
       </c>
       <c r="M141">
-        <v>13894392</v>
+        <v>13894296</v>
       </c>
       <c r="N141">
-        <v>8782008</v>
+        <v>8782012</v>
       </c>
       <c r="O141">
         <v>3240512</v>
@@ -7134,10 +7134,10 @@
         <v>104.14</v>
       </c>
       <c r="M142">
-        <v>13750299</v>
+        <v>13750203</v>
       </c>
       <c r="N142">
-        <v>8776276</v>
+        <v>8776280</v>
       </c>
       <c r="O142">
         <v>3193123</v>
@@ -7187,10 +7187,10 @@
         <v>104.75</v>
       </c>
       <c r="M143">
-        <v>13622167</v>
+        <v>13622072</v>
       </c>
       <c r="N143">
-        <v>8836718</v>
+        <v>8836722</v>
       </c>
       <c r="O143">
         <v>3101549</v>
@@ -7243,7 +7243,7 @@
         <v>13767328</v>
       </c>
       <c r="N144">
-        <v>9042526</v>
+        <v>9042530</v>
       </c>
       <c r="O144">
         <v>3043526</v>
@@ -7296,7 +7296,7 @@
         <v>14113290</v>
       </c>
       <c r="N145">
-        <v>9395146</v>
+        <v>9395150</v>
       </c>
       <c r="O145">
         <v>2989177</v>
@@ -7349,7 +7349,7 @@
         <v>14458798</v>
       </c>
       <c r="N146">
-        <v>9716010</v>
+        <v>9716014</v>
       </c>
       <c r="O146">
         <v>2937578</v>
@@ -7402,7 +7402,7 @@
         <v>14926884</v>
       </c>
       <c r="N147">
-        <v>9916841</v>
+        <v>9916845</v>
       </c>
       <c r="O147">
         <v>2929529</v>
@@ -7455,7 +7455,7 @@
         <v>15607688</v>
       </c>
       <c r="N148">
-        <v>10176474</v>
+        <v>10176478</v>
       </c>
       <c r="O148">
         <v>2979966</v>
@@ -7508,7 +7508,7 @@
         <v>16230878</v>
       </c>
       <c r="N149">
-        <v>10402055</v>
+        <v>10402059</v>
       </c>
       <c r="O149">
         <v>3052828</v>
@@ -7561,7 +7561,7 @@
         <v>16798094</v>
       </c>
       <c r="N150">
-        <v>10586455</v>
+        <v>10586459</v>
       </c>
       <c r="O150">
         <v>3145040</v>
@@ -7614,7 +7614,7 @@
         <v>17524614</v>
       </c>
       <c r="N151">
-        <v>10834368</v>
+        <v>10834372</v>
       </c>
       <c r="O151">
         <v>3279005</v>
@@ -9439,7 +9439,7 @@
         <v>1488338</v>
       </c>
       <c r="D186">
-        <v>590447</v>
+        <v>590453</v>
       </c>
       <c r="E186">
         <v>232183</v>
@@ -9448,10 +9448,10 @@
         <v>10937527</v>
       </c>
       <c r="G186">
-        <v>9817707</v>
+        <v>9817786</v>
       </c>
       <c r="H186">
-        <v>1208631</v>
+        <v>1208592</v>
       </c>
       <c r="I186">
         <v>127.33</v>
@@ -9466,10 +9466,10 @@
         <v>125.18</v>
       </c>
       <c r="M186">
-        <v>13889421</v>
+        <v>13889382</v>
       </c>
       <c r="N186">
-        <v>8211252</v>
+        <v>8211258</v>
       </c>
       <c r="O186">
         <v>2510371</v>
@@ -9519,10 +9519,10 @@
         <v>125.48</v>
       </c>
       <c r="M187">
-        <v>13965654</v>
+        <v>13965615</v>
       </c>
       <c r="N187">
-        <v>8231243</v>
+        <v>8231249</v>
       </c>
       <c r="O187">
         <v>2506811</v>
@@ -9572,10 +9572,10 @@
         <v>125.89</v>
       </c>
       <c r="M188">
-        <v>14176887</v>
+        <v>14176848</v>
       </c>
       <c r="N188">
-        <v>8311029</v>
+        <v>8311035</v>
       </c>
       <c r="O188">
         <v>2528409</v>
@@ -9625,10 +9625,10 @@
         <v>126.37</v>
       </c>
       <c r="M189">
-        <v>14260195</v>
+        <v>14260156</v>
       </c>
       <c r="N189">
-        <v>8315389</v>
+        <v>8315395</v>
       </c>
       <c r="O189">
         <v>2521451</v>
@@ -9678,10 +9678,10 @@
         <v>126.78</v>
       </c>
       <c r="M190">
-        <v>14422522</v>
+        <v>14422483</v>
       </c>
       <c r="N190">
-        <v>8370970</v>
+        <v>8370976</v>
       </c>
       <c r="O190">
         <v>2540054</v>
@@ -9704,7 +9704,7 @@
         <v>1667576</v>
       </c>
       <c r="D191">
-        <v>573573</v>
+        <v>573576</v>
       </c>
       <c r="E191">
         <v>207668</v>
@@ -9713,10 +9713,10 @@
         <v>9966680</v>
       </c>
       <c r="G191">
-        <v>8670779</v>
+        <v>8670809</v>
       </c>
       <c r="H191">
-        <v>1073133</v>
+        <v>1073127</v>
       </c>
       <c r="I191">
         <v>128.59</v>
@@ -9731,10 +9731,10 @@
         <v>127.14</v>
       </c>
       <c r="M191">
-        <v>14527752</v>
+        <v>14527707</v>
       </c>
       <c r="N191">
-        <v>8368517</v>
+        <v>8368526</v>
       </c>
       <c r="O191">
         <v>2551078</v>
@@ -9784,10 +9784,10 @@
         <v>127.59</v>
       </c>
       <c r="M192">
-        <v>14532527</v>
+        <v>14532482</v>
       </c>
       <c r="N192">
-        <v>8290091</v>
+        <v>8290100</v>
       </c>
       <c r="O192">
         <v>2547700</v>
@@ -9837,10 +9837,10 @@
         <v>128.13</v>
       </c>
       <c r="M193">
-        <v>14761050</v>
+        <v>14761005</v>
       </c>
       <c r="N193">
-        <v>8365183</v>
+        <v>8365192</v>
       </c>
       <c r="O193">
         <v>2572348</v>
@@ -9869,7 +9869,7 @@
         <v>235008</v>
       </c>
       <c r="F194">
-        <v>14729043</v>
+        <v>14729046</v>
       </c>
       <c r="G194">
         <v>13027499</v>
@@ -9890,10 +9890,10 @@
         <v>128.88</v>
       </c>
       <c r="M194">
-        <v>14843731</v>
+        <v>14843686</v>
       </c>
       <c r="N194">
-        <v>8388070</v>
+        <v>8388079</v>
       </c>
       <c r="O194">
         <v>2570148</v>
@@ -9943,10 +9943,10 @@
         <v>129.54</v>
       </c>
       <c r="M195">
-        <v>14888662</v>
+        <v>14888617</v>
       </c>
       <c r="N195">
-        <v>8325542</v>
+        <v>8325551</v>
       </c>
       <c r="O195">
         <v>2571037</v>
@@ -9975,7 +9975,7 @@
         <v>219934</v>
       </c>
       <c r="F196">
-        <v>13097747</v>
+        <v>13097708</v>
       </c>
       <c r="G196">
         <v>11730221</v>
@@ -9996,10 +9996,10 @@
         <v>130.19</v>
       </c>
       <c r="M196">
-        <v>14967343</v>
+        <v>14967298</v>
       </c>
       <c r="N196">
-        <v>8320038</v>
+        <v>8320047</v>
       </c>
       <c r="O196">
         <v>2563111</v>
@@ -10049,10 +10049,10 @@
         <v>130.86</v>
       </c>
       <c r="M197">
-        <v>15089488</v>
+        <v>15089443</v>
       </c>
       <c r="N197">
-        <v>8341502</v>
+        <v>8341511</v>
       </c>
       <c r="O197">
         <v>2566566</v>
@@ -10102,10 +10102,10 @@
         <v>131.55</v>
       </c>
       <c r="M198">
-        <v>15141581</v>
+        <v>15141575</v>
       </c>
       <c r="N198">
-        <v>8330333</v>
+        <v>8330336</v>
       </c>
       <c r="O198">
         <v>2567367</v>
@@ -10134,7 +10134,7 @@
         <v>214626</v>
       </c>
       <c r="F199">
-        <v>10187281</v>
+        <v>10187282</v>
       </c>
       <c r="G199">
         <v>9028611</v>
@@ -10155,10 +10155,10 @@
         <v>132.19</v>
       </c>
       <c r="M199">
-        <v>15309125</v>
+        <v>15309119</v>
       </c>
       <c r="N199">
-        <v>8356581</v>
+        <v>8356584</v>
       </c>
       <c r="O199">
         <v>2587917</v>
@@ -10208,10 +10208,10 @@
         <v>132.87</v>
       </c>
       <c r="M200">
-        <v>15440735</v>
+        <v>15440729</v>
       </c>
       <c r="N200">
-        <v>8350600</v>
+        <v>8350603</v>
       </c>
       <c r="O200">
         <v>2599967</v>
@@ -10261,10 +10261,10 @@
         <v>133.49</v>
       </c>
       <c r="M201">
-        <v>15510509</v>
+        <v>15510503</v>
       </c>
       <c r="N201">
-        <v>8368343</v>
+        <v>8368346</v>
       </c>
       <c r="O201">
         <v>2605538</v>
@@ -10293,7 +10293,7 @@
         <v>211859</v>
       </c>
       <c r="F202">
-        <v>10071148</v>
+        <v>10071152</v>
       </c>
       <c r="G202">
         <v>8724780</v>
@@ -10311,13 +10311,13 @@
         <v>14.46</v>
       </c>
       <c r="L202">
-        <v>134.05</v>
+        <v>134.04</v>
       </c>
       <c r="M202">
-        <v>15673819</v>
+        <v>15673813</v>
       </c>
       <c r="N202">
-        <v>8381900</v>
+        <v>8381903</v>
       </c>
       <c r="O202">
         <v>2635456</v>
@@ -10346,7 +10346,7 @@
         <v>223173</v>
       </c>
       <c r="F203">
-        <v>9851206</v>
+        <v>9851212</v>
       </c>
       <c r="G203">
         <v>8695175</v>
@@ -11874,7 +11874,7 @@
         <v>32598</v>
       </c>
       <c r="B232">
-        <v>1361144</v>
+        <v>1361121</v>
       </c>
       <c r="D232">
         <v>652549</v>
@@ -11883,7 +11883,7 @@
         <v>176192</v>
       </c>
       <c r="F232">
-        <v>11588959</v>
+        <v>11588939</v>
       </c>
       <c r="G232">
         <v>10451849</v>
@@ -35192,7 +35192,7 @@
         <v>45504</v>
       </c>
       <c r="B656">
-        <v>1065985</v>
+        <v>1065996</v>
       </c>
       <c r="C656">
         <v>1901</v>
@@ -35204,7 +35204,7 @@
         <v>181829</v>
       </c>
       <c r="F656">
-        <v>8487804</v>
+        <v>8487876</v>
       </c>
       <c r="G656">
         <v>7347349</v>
@@ -35316,13 +35316,13 @@
         <v>169526</v>
       </c>
       <c r="F658">
-        <v>7613704</v>
+        <v>7613775</v>
       </c>
       <c r="G658">
         <v>6230313</v>
       </c>
       <c r="H658">
-        <v>2752859</v>
+        <v>2752870</v>
       </c>
       <c r="I658">
         <v>450.94</v>
@@ -35337,7 +35337,7 @@
         <v>451.22</v>
       </c>
       <c r="M658">
-        <v>35651687</v>
+        <v>35651697</v>
       </c>
       <c r="N658">
         <v>5255969</v>
@@ -35393,7 +35393,7 @@
         <v>452.16</v>
       </c>
       <c r="M659">
-        <v>35640459</v>
+        <v>35640470</v>
       </c>
       <c r="N659">
         <v>5281067</v>
@@ -35449,7 +35449,7 @@
         <v>452.81</v>
       </c>
       <c r="M660">
-        <v>35645417</v>
+        <v>35645428</v>
       </c>
       <c r="N660">
         <v>5256639</v>
@@ -35472,28 +35472,28 @@
         <v>45657</v>
       </c>
       <c r="B661">
-        <v>1286291</v>
+        <v>1286671</v>
       </c>
       <c r="C661">
         <v>1926.7</v>
       </c>
       <c r="D661">
-        <v>541871</v>
+        <v>541872</v>
       </c>
       <c r="E661">
-        <v>194340</v>
+        <v>194341</v>
       </c>
       <c r="F661">
-        <v>9204459</v>
+        <v>9204452</v>
       </c>
       <c r="G661">
-        <v>7721346</v>
+        <v>7721373</v>
       </c>
       <c r="H661">
-        <v>3511562</v>
+        <v>3513259</v>
       </c>
       <c r="I661">
-        <v>463.66</v>
+        <v>463.85</v>
       </c>
       <c r="J661">
         <v>39.38</v>
@@ -35502,16 +35502,16 @@
         <v>15.27</v>
       </c>
       <c r="L661">
-        <v>453.85</v>
+        <v>453.87</v>
       </c>
       <c r="M661">
-        <v>36307408</v>
+        <v>36309115</v>
       </c>
       <c r="N661">
-        <v>5333071</v>
+        <v>5333072</v>
       </c>
       <c r="O661">
-        <v>2050417</v>
+        <v>2050418</v>
       </c>
       <c r="P661">
         <v>5512</v>
@@ -35520,7 +35520,7 @@
         <v>15036</v>
       </c>
       <c r="R661">
-        <v>469232</v>
+        <v>470075</v>
       </c>
     </row>
     <row r="662">
@@ -35549,7 +35549,7 @@
         <v>3653058</v>
       </c>
       <c r="I662">
-        <v>470.47</v>
+        <v>469.31</v>
       </c>
       <c r="J662">
         <v>38.92</v>
@@ -35558,25 +35558,25 @@
         <v>15.17</v>
       </c>
       <c r="L662">
-        <v>454.89</v>
+        <v>454.8</v>
       </c>
       <c r="M662">
-        <v>36183265</v>
+        <v>36184973</v>
       </c>
       <c r="N662">
-        <v>5341619</v>
+        <v>5341620</v>
       </c>
       <c r="O662">
-        <v>2046793</v>
+        <v>2046794</v>
       </c>
       <c r="P662">
-        <v>5531</v>
+        <v>5524</v>
       </c>
       <c r="Q662">
-        <v>15056</v>
+        <v>15053</v>
       </c>
       <c r="R662">
-        <v>468748</v>
+        <v>470274</v>
       </c>
     </row>
     <row r="663">
@@ -35584,52 +35584,108 @@
         <v>45716</v>
       </c>
       <c r="B663">
-        <v>937358</v>
+        <v>905084</v>
       </c>
       <c r="C663">
         <v>2141</v>
       </c>
       <c r="D663">
-        <v>492916</v>
+        <v>483723</v>
       </c>
       <c r="E663">
-        <v>169403</v>
+        <v>165056</v>
       </c>
       <c r="F663">
-        <v>8640604</v>
+        <v>8661513</v>
       </c>
       <c r="G663">
-        <v>7485551</v>
+        <v>7509946</v>
       </c>
       <c r="H663">
-        <v>3446546</v>
+        <v>3480178</v>
       </c>
       <c r="I663">
-        <v>468.44</v>
+        <v>471.52</v>
       </c>
       <c r="J663">
-        <v>39.28</v>
+        <v>39.2</v>
       </c>
       <c r="K663">
-        <v>15.18</v>
+        <v>15.21</v>
       </c>
       <c r="L663">
-        <v>455.71</v>
+        <v>455.91</v>
       </c>
       <c r="M663">
-        <v>36290736</v>
+        <v>36326076</v>
       </c>
       <c r="N663">
-        <v>5343979</v>
+        <v>5334786</v>
       </c>
       <c r="O663">
-        <v>2058727</v>
+        <v>2054381</v>
       </c>
       <c r="P663">
-        <v>5532</v>
+        <v>5520</v>
       </c>
       <c r="Q663">
-        <v>15076</v>
+        <v>15069</v>
+      </c>
+      <c r="R663">
+        <v>472115</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="2">
+        <v>45747</v>
+      </c>
+      <c r="B664">
+        <v>890794</v>
+      </c>
+      <c r="C664">
+        <v>2065.1</v>
+      </c>
+      <c r="D664">
+        <v>431634</v>
+      </c>
+      <c r="E664">
+        <v>188320</v>
+      </c>
+      <c r="F664">
+        <v>9620921</v>
+      </c>
+      <c r="G664">
+        <v>8149650</v>
+      </c>
+      <c r="H664">
+        <v>3743494</v>
+      </c>
+      <c r="I664">
+        <v>467.75</v>
+      </c>
+      <c r="J664">
+        <v>39.55</v>
+      </c>
+      <c r="K664">
+        <v>15.3</v>
+      </c>
+      <c r="L664">
+        <v>457.08</v>
+      </c>
+      <c r="M664">
+        <v>36781593</v>
+      </c>
+      <c r="N664">
+        <v>5357361</v>
+      </c>
+      <c r="O664">
+        <v>2078927</v>
+      </c>
+      <c r="P664">
+        <v>5526</v>
+      </c>
+      <c r="Q664">
+        <v>15086</v>
       </c>
     </row>
   </sheetData>

--- a/data/monthly_state_ui.xlsx
+++ b/data/monthly_state_ui.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R664"/>
+  <dimension ref="A1:R665"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -35576,7 +35576,7 @@
         <v>15053</v>
       </c>
       <c r="R662">
-        <v>470274</v>
+        <v>471070</v>
       </c>
     </row>
     <row r="663">
@@ -35626,13 +35626,13 @@
         <v>2054381</v>
       </c>
       <c r="P663">
-        <v>5520</v>
+        <v>5514</v>
       </c>
       <c r="Q663">
-        <v>15069</v>
+        <v>15071</v>
       </c>
       <c r="R663">
-        <v>472115</v>
+        <v>472141</v>
       </c>
     </row>
     <row r="664">
@@ -35682,10 +35682,24 @@
         <v>2078927</v>
       </c>
       <c r="P664">
-        <v>5526</v>
+        <v>5516</v>
       </c>
       <c r="Q664">
-        <v>15086</v>
+        <v>15088</v>
+      </c>
+      <c r="R664">
+        <v>471183</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="2">
+        <v>45777</v>
+      </c>
+      <c r="P665">
+        <v>5522</v>
+      </c>
+      <c r="Q665">
+        <v>15101</v>
       </c>
     </row>
   </sheetData>

--- a/data/monthly_state_ui.xlsx
+++ b/data/monthly_state_ui.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R665"/>
+  <dimension ref="A1:R666"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -35632,7 +35632,7 @@
         <v>15071</v>
       </c>
       <c r="R663">
-        <v>472141</v>
+        <v>474386</v>
       </c>
     </row>
     <row r="664">
@@ -35682,24 +35682,41 @@
         <v>2078927</v>
       </c>
       <c r="P664">
-        <v>5516</v>
+        <v>5515</v>
       </c>
       <c r="Q664">
-        <v>15088</v>
+        <v>15087</v>
       </c>
       <c r="R664">
-        <v>471183</v>
+        <v>474713</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" s="2">
         <v>45777</v>
       </c>
+      <c r="C665">
+        <v>1877</v>
+      </c>
       <c r="P665">
-        <v>5522</v>
+        <v>5518</v>
       </c>
       <c r="Q665">
-        <v>15101</v>
+        <v>15098</v>
+      </c>
+      <c r="R665">
+        <v>475961</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="2">
+        <v>45808</v>
+      </c>
+      <c r="P666">
+        <v>5518</v>
+      </c>
+      <c r="Q666">
+        <v>15119</v>
       </c>
     </row>
   </sheetData>

--- a/data/monthly_state_ui.xlsx
+++ b/data/monthly_state_ui.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R666"/>
+  <dimension ref="A1:R667"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -626,10 +626,10 @@
         <v>25964</v>
       </c>
       <c r="B14">
-        <v>1756023</v>
+        <v>1756033</v>
       </c>
       <c r="D14">
-        <v>873722</v>
+        <v>873822</v>
       </c>
       <c r="E14">
         <v>162257</v>
@@ -3238,7 +3238,7 @@
         <v>1566361</v>
       </c>
       <c r="D69">
-        <v>748977</v>
+        <v>749343</v>
       </c>
       <c r="E69">
         <v>412513</v>
@@ -3268,7 +3268,7 @@
         <v>10944048</v>
       </c>
       <c r="N69">
-        <v>11449206</v>
+        <v>11449572</v>
       </c>
       <c r="O69">
         <v>3486140</v>
@@ -3291,7 +3291,7 @@
         <v>1521549</v>
       </c>
       <c r="D70">
-        <v>563952</v>
+        <v>564426</v>
       </c>
       <c r="E70">
         <v>369764</v>
@@ -3321,7 +3321,7 @@
         <v>11340205</v>
       </c>
       <c r="N70">
-        <v>11578759</v>
+        <v>11579599</v>
       </c>
       <c r="O70">
         <v>3710861</v>
@@ -3344,7 +3344,7 @@
         <v>1676391</v>
       </c>
       <c r="D71">
-        <v>578811</v>
+        <v>578891</v>
       </c>
       <c r="E71">
         <v>350072</v>
@@ -3374,7 +3374,7 @@
         <v>11655813</v>
       </c>
       <c r="N71">
-        <v>11606700</v>
+        <v>11607620</v>
       </c>
       <c r="O71">
         <v>3906188</v>
@@ -3397,7 +3397,7 @@
         <v>1620082</v>
       </c>
       <c r="D72">
-        <v>545377</v>
+        <v>545054</v>
       </c>
       <c r="E72">
         <v>290799</v>
@@ -3427,7 +3427,7 @@
         <v>11847509</v>
       </c>
       <c r="N72">
-        <v>11490904</v>
+        <v>11491501</v>
       </c>
       <c r="O72">
         <v>4044850</v>
@@ -3450,7 +3450,7 @@
         <v>2419835</v>
       </c>
       <c r="D73">
-        <v>806063</v>
+        <v>804560</v>
       </c>
       <c r="E73">
         <v>335676</v>
@@ -3480,7 +3480,7 @@
         <v>11995329</v>
       </c>
       <c r="N73">
-        <v>11160948</v>
+        <v>11160042</v>
       </c>
       <c r="O73">
         <v>4195023</v>
@@ -3524,7 +3524,7 @@
         <v>37.99</v>
       </c>
       <c r="K74">
-        <v>16.43</v>
+        <v>16.44</v>
       </c>
       <c r="L74">
         <v>70.81999999999999</v>
@@ -3533,7 +3533,7 @@
         <v>11885516</v>
       </c>
       <c r="N74">
-        <v>10476340</v>
+        <v>10475434</v>
       </c>
       <c r="O74">
         <v>4298599</v>
@@ -3577,7 +3577,7 @@
         <v>38.11</v>
       </c>
       <c r="K75">
-        <v>17.01</v>
+        <v>17.02</v>
       </c>
       <c r="L75">
         <v>71.41</v>
@@ -3586,7 +3586,7 @@
         <v>11666118</v>
       </c>
       <c r="N75">
-        <v>9846698</v>
+        <v>9845792</v>
       </c>
       <c r="O75">
         <v>4363238</v>
@@ -3627,7 +3627,7 @@
         <v>75.70999999999999</v>
       </c>
       <c r="J76">
-        <v>38.1</v>
+        <v>38.09</v>
       </c>
       <c r="K76">
         <v>17.24</v>
@@ -3639,7 +3639,7 @@
         <v>11397450</v>
       </c>
       <c r="N76">
-        <v>9405330</v>
+        <v>9404424</v>
       </c>
       <c r="O76">
         <v>4411077</v>
@@ -3692,7 +3692,7 @@
         <v>10956621</v>
       </c>
       <c r="N77">
-        <v>9012904</v>
+        <v>9011998</v>
       </c>
       <c r="O77">
         <v>4347024</v>
@@ -3745,7 +3745,7 @@
         <v>10503070</v>
       </c>
       <c r="N78">
-        <v>8739521</v>
+        <v>8738615</v>
       </c>
       <c r="O78">
         <v>4214920</v>
@@ -3798,7 +3798,7 @@
         <v>10233113</v>
       </c>
       <c r="N79">
-        <v>8641629</v>
+        <v>8640723</v>
       </c>
       <c r="O79">
         <v>4058873</v>
@@ -3851,7 +3851,7 @@
         <v>9920954</v>
       </c>
       <c r="N80">
-        <v>8546567</v>
+        <v>8545661</v>
       </c>
       <c r="O80">
         <v>3835154</v>
@@ -3904,7 +3904,7 @@
         <v>9743000</v>
       </c>
       <c r="N81">
-        <v>8493629</v>
+        <v>8492357</v>
       </c>
       <c r="O81">
         <v>3676265</v>
@@ -3945,7 +3945,7 @@
         <v>74.34999999999999</v>
       </c>
       <c r="J82">
-        <v>37.69</v>
+        <v>37.7</v>
       </c>
       <c r="K82">
         <v>15.63</v>
@@ -3957,7 +3957,7 @@
         <v>9599242</v>
       </c>
       <c r="N82">
-        <v>8453410</v>
+        <v>8451664</v>
       </c>
       <c r="O82">
         <v>3545180</v>
@@ -4001,7 +4001,7 @@
         <v>37.81</v>
       </c>
       <c r="K83">
-        <v>15.37</v>
+        <v>15.38</v>
       </c>
       <c r="L83">
         <v>74.63</v>
@@ -4010,7 +4010,7 @@
         <v>9431518</v>
       </c>
       <c r="N83">
-        <v>8419354</v>
+        <v>8417528</v>
       </c>
       <c r="O83">
         <v>3407332</v>
@@ -4063,7 +4063,7 @@
         <v>9420670</v>
       </c>
       <c r="N84">
-        <v>8507985</v>
+        <v>8506482</v>
       </c>
       <c r="O84">
         <v>3347085</v>
@@ -4157,7 +4157,7 @@
         <v>78.61</v>
       </c>
       <c r="J86">
-        <v>37.33</v>
+        <v>37.34</v>
       </c>
       <c r="K86">
         <v>14.68</v>
@@ -4210,7 +4210,7 @@
         <v>80.48</v>
       </c>
       <c r="J87">
-        <v>37.05</v>
+        <v>37.06</v>
       </c>
       <c r="K87">
         <v>14.41</v>
@@ -4263,7 +4263,7 @@
         <v>79.63</v>
       </c>
       <c r="J88">
-        <v>36.8</v>
+        <v>36.81</v>
       </c>
       <c r="K88">
         <v>14.39</v>
@@ -4316,7 +4316,7 @@
         <v>78.83</v>
       </c>
       <c r="J89">
-        <v>36.48</v>
+        <v>36.49</v>
       </c>
       <c r="K89">
         <v>14.31</v>
@@ -4778,16 +4778,16 @@
         <v>1063136</v>
       </c>
       <c r="E98">
-        <v>210660</v>
+        <v>210645</v>
       </c>
       <c r="F98">
-        <v>13886945</v>
+        <v>13886572</v>
       </c>
       <c r="G98">
-        <v>11076379</v>
+        <v>11076319</v>
       </c>
       <c r="H98">
-        <v>904867</v>
+        <v>904856</v>
       </c>
       <c r="I98">
         <v>84.12</v>
@@ -4802,13 +4802,13 @@
         <v>79.33</v>
       </c>
       <c r="M98">
-        <v>8643089</v>
+        <v>8643078</v>
       </c>
       <c r="N98">
         <v>7816720</v>
       </c>
       <c r="O98">
-        <v>2726124</v>
+        <v>2726109</v>
       </c>
       <c r="P98">
         <v>3429</v>
@@ -4855,13 +4855,13 @@
         <v>79.84</v>
       </c>
       <c r="M99">
-        <v>8586176</v>
+        <v>8586165</v>
       </c>
       <c r="N99">
         <v>7675188</v>
       </c>
       <c r="O99">
-        <v>2658764</v>
+        <v>2658749</v>
       </c>
       <c r="P99">
         <v>3442</v>
@@ -4908,13 +4908,13 @@
         <v>80.48999999999999</v>
       </c>
       <c r="M100">
-        <v>8552549</v>
+        <v>8552538</v>
       </c>
       <c r="N100">
         <v>7655474</v>
       </c>
       <c r="O100">
-        <v>2569594</v>
+        <v>2569579</v>
       </c>
       <c r="P100">
         <v>3456</v>
@@ -4958,16 +4958,16 @@
         <v>14.13</v>
       </c>
       <c r="L101">
-        <v>80.95</v>
+        <v>80.94</v>
       </c>
       <c r="M101">
-        <v>8496273</v>
+        <v>8496261</v>
       </c>
       <c r="N101">
         <v>7630816</v>
       </c>
       <c r="O101">
-        <v>2496710</v>
+        <v>2496695</v>
       </c>
       <c r="P101">
         <v>3472</v>
@@ -5014,13 +5014,13 @@
         <v>81.34999999999999</v>
       </c>
       <c r="M102">
-        <v>8469975</v>
+        <v>8469964</v>
       </c>
       <c r="N102">
         <v>7605385</v>
       </c>
       <c r="O102">
-        <v>2447766</v>
+        <v>2447751</v>
       </c>
       <c r="P102">
         <v>3483</v>
@@ -5067,13 +5067,13 @@
         <v>81.73999999999999</v>
       </c>
       <c r="M103">
-        <v>8390314</v>
+        <v>8390302</v>
       </c>
       <c r="N103">
         <v>7610191</v>
       </c>
       <c r="O103">
-        <v>2369799</v>
+        <v>2369784</v>
       </c>
       <c r="P103">
         <v>3482</v>
@@ -5120,13 +5120,13 @@
         <v>82.12</v>
       </c>
       <c r="M104">
-        <v>8353739</v>
+        <v>8353728</v>
       </c>
       <c r="N104">
         <v>7610967</v>
       </c>
       <c r="O104">
-        <v>2306252</v>
+        <v>2306237</v>
       </c>
       <c r="P104">
         <v>3473</v>
@@ -5170,16 +5170,16 @@
         <v>13.57</v>
       </c>
       <c r="L105">
-        <v>82.48999999999999</v>
+        <v>82.48</v>
       </c>
       <c r="M105">
-        <v>8358616</v>
+        <v>8358605</v>
       </c>
       <c r="N105">
         <v>7677889</v>
       </c>
       <c r="O105">
-        <v>2230965</v>
+        <v>2230950</v>
       </c>
       <c r="P105">
         <v>3475</v>
@@ -5226,13 +5226,13 @@
         <v>82.78</v>
       </c>
       <c r="M106">
-        <v>8313959</v>
+        <v>8313947</v>
       </c>
       <c r="N106">
         <v>7636142</v>
       </c>
       <c r="O106">
-        <v>2171023</v>
+        <v>2171008</v>
       </c>
       <c r="P106">
         <v>3484</v>
@@ -5279,13 +5279,13 @@
         <v>83.03</v>
       </c>
       <c r="M107">
-        <v>8307254</v>
+        <v>8307242</v>
       </c>
       <c r="N107">
         <v>7633029</v>
       </c>
       <c r="O107">
-        <v>2121251</v>
+        <v>2121236</v>
       </c>
       <c r="P107">
         <v>3488</v>
@@ -5332,13 +5332,13 @@
         <v>83.3</v>
       </c>
       <c r="M108">
-        <v>8263903</v>
+        <v>8263892</v>
       </c>
       <c r="N108">
         <v>7603593</v>
       </c>
       <c r="O108">
-        <v>2073376</v>
+        <v>2073361</v>
       </c>
       <c r="P108">
         <v>3494</v>
@@ -5385,13 +5385,13 @@
         <v>83.67</v>
       </c>
       <c r="M109">
-        <v>8212237</v>
+        <v>8212226</v>
       </c>
       <c r="N109">
         <v>7568310</v>
       </c>
       <c r="O109">
-        <v>2030438</v>
+        <v>2030423</v>
       </c>
       <c r="P109">
         <v>3500</v>
@@ -5941,7 +5941,7 @@
         <v>1826171</v>
       </c>
       <c r="D120">
-        <v>612750</v>
+        <v>613421</v>
       </c>
       <c r="E120">
         <v>158640</v>
@@ -5962,7 +5962,7 @@
         <v>26.54</v>
       </c>
       <c r="K120">
-        <v>13.08</v>
+        <v>13.07</v>
       </c>
       <c r="L120">
         <v>88.98999999999999</v>
@@ -5971,7 +5971,7 @@
         <v>9066829</v>
       </c>
       <c r="N120">
-        <v>8008042</v>
+        <v>8008713</v>
       </c>
       <c r="O120">
         <v>2023729</v>
@@ -6024,7 +6024,7 @@
         <v>9261079</v>
       </c>
       <c r="N121">
-        <v>8075003</v>
+        <v>8075674</v>
       </c>
       <c r="O121">
         <v>2037095</v>
@@ -6077,7 +6077,7 @@
         <v>9572200</v>
       </c>
       <c r="N122">
-        <v>8257441</v>
+        <v>8258112</v>
       </c>
       <c r="O122">
         <v>2068668</v>
@@ -6130,7 +6130,7 @@
         <v>9886931</v>
       </c>
       <c r="N123">
-        <v>8354782</v>
+        <v>8355453</v>
       </c>
       <c r="O123">
         <v>2110168</v>
@@ -6183,7 +6183,7 @@
         <v>10129520</v>
       </c>
       <c r="N124">
-        <v>8345649</v>
+        <v>8346320</v>
       </c>
       <c r="O124">
         <v>2137290</v>
@@ -6236,7 +6236,7 @@
         <v>10583994</v>
       </c>
       <c r="N125">
-        <v>8554140</v>
+        <v>8554811</v>
       </c>
       <c r="O125">
         <v>2211148</v>
@@ -6289,7 +6289,7 @@
         <v>11055601</v>
       </c>
       <c r="N126">
-        <v>8900019</v>
+        <v>8900690</v>
       </c>
       <c r="O126">
         <v>2267224</v>
@@ -6342,7 +6342,7 @@
         <v>11658927</v>
       </c>
       <c r="N127">
-        <v>9253751</v>
+        <v>9254422</v>
       </c>
       <c r="O127">
         <v>2351002</v>
@@ -6395,7 +6395,7 @@
         <v>12390483</v>
       </c>
       <c r="N128">
-        <v>9651194</v>
+        <v>9651865</v>
       </c>
       <c r="O128">
         <v>2480122</v>
@@ -6448,7 +6448,7 @@
         <v>12869773</v>
       </c>
       <c r="N129">
-        <v>9753674</v>
+        <v>9754345</v>
       </c>
       <c r="O129">
         <v>2569988</v>
@@ -6501,7 +6501,7 @@
         <v>13408748</v>
       </c>
       <c r="N130">
-        <v>9902903</v>
+        <v>9903574</v>
       </c>
       <c r="O130">
         <v>2683996</v>
@@ -6521,7 +6521,7 @@
         <v>29525</v>
       </c>
       <c r="B131">
-        <v>1807850</v>
+        <v>1807852</v>
       </c>
       <c r="D131">
         <v>633181</v>
@@ -6545,7 +6545,7 @@
         <v>32.9</v>
       </c>
       <c r="K131">
-        <v>14.43</v>
+        <v>14.42</v>
       </c>
       <c r="L131">
         <v>98.56999999999999</v>
@@ -6554,7 +6554,7 @@
         <v>13860671</v>
       </c>
       <c r="N131">
-        <v>9990095</v>
+        <v>9990766</v>
       </c>
       <c r="O131">
         <v>2814590</v>
@@ -6589,10 +6589,10 @@
         <v>9516801</v>
       </c>
       <c r="H132">
-        <v>935554</v>
+        <v>866493</v>
       </c>
       <c r="I132">
-        <v>100.72</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="J132">
         <v>32.75</v>
@@ -6601,10 +6601,10 @@
         <v>14.67</v>
       </c>
       <c r="L132">
-        <v>99.05</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="M132">
-        <v>14067101</v>
+        <v>13998040</v>
       </c>
       <c r="N132">
         <v>9919645</v>
@@ -6648,16 +6648,16 @@
         <v>101.51</v>
       </c>
       <c r="J133">
-        <v>33.2</v>
+        <v>33.19</v>
       </c>
       <c r="K133">
         <v>14.91</v>
       </c>
       <c r="L133">
-        <v>99.53</v>
+        <v>99.06</v>
       </c>
       <c r="M133">
-        <v>14469554</v>
+        <v>14400492</v>
       </c>
       <c r="N133">
         <v>9992123</v>
@@ -6707,10 +6707,10 @@
         <v>15.02</v>
       </c>
       <c r="L134">
-        <v>100.2</v>
+        <v>99.73</v>
       </c>
       <c r="M134">
-        <v>14605189</v>
+        <v>14536128</v>
       </c>
       <c r="N134">
         <v>9946214</v>
@@ -6754,16 +6754,16 @@
         <v>104.48</v>
       </c>
       <c r="J135">
-        <v>33.22</v>
+        <v>33.21</v>
       </c>
       <c r="K135">
         <v>15.11</v>
       </c>
       <c r="L135">
-        <v>100.72</v>
+        <v>100.26</v>
       </c>
       <c r="M135">
-        <v>14690626</v>
+        <v>14621565</v>
       </c>
       <c r="N135">
         <v>9890722</v>
@@ -6813,10 +6813,10 @@
         <v>15.16</v>
       </c>
       <c r="L136">
-        <v>101.31</v>
+        <v>100.84</v>
       </c>
       <c r="M136">
-        <v>14867085</v>
+        <v>14798024</v>
       </c>
       <c r="N136">
         <v>9919839</v>
@@ -6866,10 +6866,10 @@
         <v>15.27</v>
       </c>
       <c r="L137">
-        <v>101.83</v>
+        <v>101.36</v>
       </c>
       <c r="M137">
-        <v>14861603</v>
+        <v>14792542</v>
       </c>
       <c r="N137">
         <v>9793604</v>
@@ -6919,10 +6919,10 @@
         <v>15.52</v>
       </c>
       <c r="L138">
-        <v>102.25</v>
+        <v>101.77</v>
       </c>
       <c r="M138">
-        <v>14670995</v>
+        <v>14601934</v>
       </c>
       <c r="N138">
         <v>9476838</v>
@@ -6972,10 +6972,10 @@
         <v>15.69</v>
       </c>
       <c r="L139">
-        <v>102.61</v>
+        <v>102.13</v>
       </c>
       <c r="M139">
-        <v>14467220</v>
+        <v>14398159</v>
       </c>
       <c r="N139">
         <v>9214474</v>
@@ -7001,7 +7001,7 @@
         <v>2112151</v>
       </c>
       <c r="D140">
-        <v>823661</v>
+        <v>813167</v>
       </c>
       <c r="E140">
         <v>246909</v>
@@ -7022,16 +7022,16 @@
         <v>32.99</v>
       </c>
       <c r="K140">
-        <v>15.74</v>
+        <v>15.76</v>
       </c>
       <c r="L140">
-        <v>103.08</v>
+        <v>102.58</v>
       </c>
       <c r="M140">
-        <v>14132000</v>
+        <v>14062939</v>
       </c>
       <c r="N140">
-        <v>8935497</v>
+        <v>8925003</v>
       </c>
       <c r="O140">
         <v>3281695</v>
@@ -7075,16 +7075,16 @@
         <v>32.76</v>
       </c>
       <c r="K141">
-        <v>15.66</v>
+        <v>15.68</v>
       </c>
       <c r="L141">
-        <v>103.59</v>
+        <v>103.08</v>
       </c>
       <c r="M141">
-        <v>13894296</v>
+        <v>13825235</v>
       </c>
       <c r="N141">
-        <v>8782012</v>
+        <v>8771518</v>
       </c>
       <c r="O141">
         <v>3240512</v>
@@ -7128,16 +7128,16 @@
         <v>32.19</v>
       </c>
       <c r="K142">
-        <v>15.43</v>
+        <v>15.45</v>
       </c>
       <c r="L142">
-        <v>104.14</v>
+        <v>103.63</v>
       </c>
       <c r="M142">
-        <v>13750203</v>
+        <v>13681142</v>
       </c>
       <c r="N142">
-        <v>8776280</v>
+        <v>8765786</v>
       </c>
       <c r="O142">
         <v>3193123</v>
@@ -7181,16 +7181,16 @@
         <v>31.67</v>
       </c>
       <c r="K143">
-        <v>15.1</v>
+        <v>15.12</v>
       </c>
       <c r="L143">
-        <v>104.75</v>
+        <v>104.23</v>
       </c>
       <c r="M143">
-        <v>13622072</v>
+        <v>13553011</v>
       </c>
       <c r="N143">
-        <v>8836722</v>
+        <v>8826228</v>
       </c>
       <c r="O143">
         <v>3101549</v>
@@ -7234,7 +7234,7 @@
         <v>32.12</v>
       </c>
       <c r="K144">
-        <v>14.81</v>
+        <v>14.83</v>
       </c>
       <c r="L144">
         <v>105.47</v>
@@ -7243,7 +7243,7 @@
         <v>13767328</v>
       </c>
       <c r="N144">
-        <v>9042530</v>
+        <v>9032036</v>
       </c>
       <c r="O144">
         <v>3043526</v>
@@ -7287,7 +7287,7 @@
         <v>32.44</v>
       </c>
       <c r="K145">
-        <v>14.47</v>
+        <v>14.48</v>
       </c>
       <c r="L145">
         <v>106.61</v>
@@ -7296,7 +7296,7 @@
         <v>14113290</v>
       </c>
       <c r="N145">
-        <v>9395150</v>
+        <v>9384656</v>
       </c>
       <c r="O145">
         <v>2989177</v>
@@ -7337,10 +7337,10 @@
         <v>114.95</v>
       </c>
       <c r="J146">
-        <v>32.88</v>
+        <v>32.91</v>
       </c>
       <c r="K146">
-        <v>14.17</v>
+        <v>14.19</v>
       </c>
       <c r="L146">
         <v>107.85</v>
@@ -7349,7 +7349,7 @@
         <v>14458798</v>
       </c>
       <c r="N146">
-        <v>9716014</v>
+        <v>9705520</v>
       </c>
       <c r="O146">
         <v>2937578</v>
@@ -7390,10 +7390,10 @@
         <v>117.46</v>
       </c>
       <c r="J147">
-        <v>33.36</v>
+        <v>33.4</v>
       </c>
       <c r="K147">
-        <v>14.16</v>
+        <v>14.17</v>
       </c>
       <c r="L147">
         <v>109.23</v>
@@ -7402,7 +7402,7 @@
         <v>14926884</v>
       </c>
       <c r="N147">
-        <v>9916845</v>
+        <v>9906351</v>
       </c>
       <c r="O147">
         <v>2929529</v>
@@ -7443,10 +7443,10 @@
         <v>117.44</v>
       </c>
       <c r="J148">
-        <v>33.95</v>
+        <v>34</v>
       </c>
       <c r="K148">
-        <v>14.25</v>
+        <v>14.26</v>
       </c>
       <c r="L148">
         <v>110.6</v>
@@ -7455,7 +7455,7 @@
         <v>15607688</v>
       </c>
       <c r="N148">
-        <v>10176478</v>
+        <v>10165984</v>
       </c>
       <c r="O148">
         <v>2979966</v>
@@ -7496,10 +7496,10 @@
         <v>117.9</v>
       </c>
       <c r="J149">
-        <v>34.55</v>
+        <v>34.59</v>
       </c>
       <c r="K149">
-        <v>14.35</v>
+        <v>14.36</v>
       </c>
       <c r="L149">
         <v>111.76</v>
@@ -7508,7 +7508,7 @@
         <v>16230878</v>
       </c>
       <c r="N149">
-        <v>10402059</v>
+        <v>10391565</v>
       </c>
       <c r="O149">
         <v>3052828</v>
@@ -7549,10 +7549,10 @@
         <v>118.33</v>
       </c>
       <c r="J150">
-        <v>34.78</v>
+        <v>34.82</v>
       </c>
       <c r="K150">
-        <v>14.46</v>
+        <v>14.48</v>
       </c>
       <c r="L150">
         <v>112.75</v>
@@ -7561,7 +7561,7 @@
         <v>16798094</v>
       </c>
       <c r="N150">
-        <v>10586459</v>
+        <v>10575965</v>
       </c>
       <c r="O150">
         <v>3145040</v>
@@ -7602,10 +7602,10 @@
         <v>118.32</v>
       </c>
       <c r="J151">
-        <v>34.9</v>
+        <v>34.94</v>
       </c>
       <c r="K151">
-        <v>14.61</v>
+        <v>14.62</v>
       </c>
       <c r="L151">
         <v>113.8</v>
@@ -7614,7 +7614,7 @@
         <v>17524614</v>
       </c>
       <c r="N151">
-        <v>10834372</v>
+        <v>10823878</v>
       </c>
       <c r="O151">
         <v>3279005</v>
@@ -7655,7 +7655,7 @@
         <v>117.67</v>
       </c>
       <c r="J152">
-        <v>34.91</v>
+        <v>34.95</v>
       </c>
       <c r="K152">
         <v>14.74</v>
@@ -7708,7 +7708,7 @@
         <v>119.22</v>
       </c>
       <c r="J153">
-        <v>35.71</v>
+        <v>35.75</v>
       </c>
       <c r="K153">
         <v>14.94</v>
@@ -7761,7 +7761,7 @@
         <v>121.03</v>
       </c>
       <c r="J154">
-        <v>36.22</v>
+        <v>36.26</v>
       </c>
       <c r="K154">
         <v>15.13</v>
@@ -7793,7 +7793,7 @@
         <v>30255</v>
       </c>
       <c r="B155">
-        <v>2442779</v>
+        <v>2442719</v>
       </c>
       <c r="D155">
         <v>830491</v>
@@ -7814,7 +7814,7 @@
         <v>122.9</v>
       </c>
       <c r="J155">
-        <v>36.85</v>
+        <v>36.88</v>
       </c>
       <c r="K155">
         <v>15.32</v>
@@ -7867,7 +7867,7 @@
         <v>123.46</v>
       </c>
       <c r="J156">
-        <v>37.94</v>
+        <v>37.97</v>
       </c>
       <c r="K156">
         <v>15.57</v>
@@ -7920,7 +7920,7 @@
         <v>123.55</v>
       </c>
       <c r="J157">
-        <v>38.53</v>
+        <v>38.57</v>
       </c>
       <c r="K157">
         <v>15.92</v>
@@ -8058,7 +8058,7 @@
         <v>30406</v>
       </c>
       <c r="B160">
-        <v>2075814</v>
+        <v>2074814</v>
       </c>
       <c r="D160">
         <v>905581</v>
@@ -8217,7 +8217,7 @@
         <v>30497</v>
       </c>
       <c r="B163">
-        <v>1739030</v>
+        <v>1739042</v>
       </c>
       <c r="D163">
         <v>610343</v>
@@ -8323,7 +8323,7 @@
         <v>30559</v>
       </c>
       <c r="B165">
-        <v>1666862</v>
+        <v>1666892</v>
       </c>
       <c r="D165">
         <v>640922</v>
@@ -8432,7 +8432,7 @@
         <v>1521621</v>
       </c>
       <c r="D167">
-        <v>498870</v>
+        <v>498930</v>
       </c>
       <c r="E167">
         <v>244243</v>
@@ -8462,7 +8462,7 @@
         <v>20303133</v>
       </c>
       <c r="N167">
-        <v>9634596</v>
+        <v>9634656</v>
       </c>
       <c r="O167">
         <v>4490183</v>
@@ -8515,7 +8515,7 @@
         <v>19582898</v>
       </c>
       <c r="N168">
-        <v>9326533</v>
+        <v>9326593</v>
       </c>
       <c r="O168">
         <v>4354932</v>
@@ -8568,7 +8568,7 @@
         <v>18648417</v>
       </c>
       <c r="N169">
-        <v>8907190</v>
+        <v>8907250</v>
       </c>
       <c r="O169">
         <v>4179622</v>
@@ -8621,7 +8621,7 @@
         <v>17900798</v>
       </c>
       <c r="N170">
-        <v>8536282</v>
+        <v>8536342</v>
       </c>
       <c r="O170">
         <v>4027489</v>
@@ -8644,7 +8644,7 @@
         <v>1527822</v>
       </c>
       <c r="D171">
-        <v>770220</v>
+        <v>770420</v>
       </c>
       <c r="E171">
         <v>244709</v>
@@ -8665,7 +8665,7 @@
         <v>37.73</v>
       </c>
       <c r="K171">
-        <v>17.39</v>
+        <v>17.38</v>
       </c>
       <c r="L171">
         <v>123.45</v>
@@ -8674,7 +8674,7 @@
         <v>17248271</v>
       </c>
       <c r="N171">
-        <v>8290309</v>
+        <v>8290569</v>
       </c>
       <c r="O171">
         <v>3877939</v>
@@ -8727,7 +8727,7 @@
         <v>16245547</v>
       </c>
       <c r="N172">
-        <v>7988864</v>
+        <v>7989124</v>
       </c>
       <c r="O172">
         <v>3658592</v>
@@ -8780,7 +8780,7 @@
         <v>15588841</v>
       </c>
       <c r="N173">
-        <v>7830082</v>
+        <v>7830342</v>
       </c>
       <c r="O173">
         <v>3473175</v>
@@ -8833,7 +8833,7 @@
         <v>15099983</v>
       </c>
       <c r="N174">
-        <v>7759328</v>
+        <v>7759588</v>
       </c>
       <c r="O174">
         <v>3318135</v>
@@ -8886,7 +8886,7 @@
         <v>14497327</v>
       </c>
       <c r="N175">
-        <v>7627849</v>
+        <v>7628109</v>
       </c>
       <c r="O175">
         <v>3132741</v>
@@ -8939,7 +8939,7 @@
         <v>14172974</v>
       </c>
       <c r="N176">
-        <v>7609502</v>
+        <v>7609762</v>
       </c>
       <c r="O176">
         <v>3010054</v>
@@ -8992,7 +8992,7 @@
         <v>13819521</v>
       </c>
       <c r="N177">
-        <v>7596139</v>
+        <v>7596399</v>
       </c>
       <c r="O177">
         <v>2881068</v>
@@ -9045,7 +9045,7 @@
         <v>13541997</v>
       </c>
       <c r="N178">
-        <v>7566133</v>
+        <v>7566393</v>
       </c>
       <c r="O178">
         <v>2780419</v>
@@ -9098,7 +9098,7 @@
         <v>13507868</v>
       </c>
       <c r="N179">
-        <v>7643289</v>
+        <v>7643489</v>
       </c>
       <c r="O179">
         <v>2732820</v>
@@ -9151,7 +9151,7 @@
         <v>13417997</v>
       </c>
       <c r="N180">
-        <v>7726050</v>
+        <v>7726250</v>
       </c>
       <c r="O180">
         <v>2666642</v>
@@ -9204,7 +9204,7 @@
         <v>13328187</v>
       </c>
       <c r="N181">
-        <v>7742547</v>
+        <v>7742747</v>
       </c>
       <c r="O181">
         <v>2606145</v>
@@ -9257,7 +9257,7 @@
         <v>13450137</v>
       </c>
       <c r="N182">
-        <v>7910090</v>
+        <v>7910290</v>
       </c>
       <c r="O182">
         <v>2574533</v>
@@ -9298,7 +9298,7 @@
         <v>128.2</v>
       </c>
       <c r="J183">
-        <v>33.4</v>
+        <v>33.39</v>
       </c>
       <c r="K183">
         <v>14.04</v>
@@ -9439,7 +9439,7 @@
         <v>1488338</v>
       </c>
       <c r="D186">
-        <v>590453</v>
+        <v>550342</v>
       </c>
       <c r="E186">
         <v>232183</v>
@@ -9448,28 +9448,28 @@
         <v>10937527</v>
       </c>
       <c r="G186">
-        <v>9817786</v>
+        <v>9028657</v>
       </c>
       <c r="H186">
-        <v>1208592</v>
+        <v>1106890</v>
       </c>
       <c r="I186">
-        <v>127.33</v>
+        <v>126.67</v>
       </c>
       <c r="J186">
         <v>32.49</v>
       </c>
       <c r="K186">
-        <v>13.96</v>
+        <v>13.93</v>
       </c>
       <c r="L186">
-        <v>125.18</v>
+        <v>125.11</v>
       </c>
       <c r="M186">
-        <v>13889382</v>
+        <v>13787679</v>
       </c>
       <c r="N186">
-        <v>8211258</v>
+        <v>8171147</v>
       </c>
       <c r="O186">
         <v>2510371</v>
@@ -9513,16 +9513,16 @@
         <v>32.38</v>
       </c>
       <c r="K187">
-        <v>13.97</v>
+        <v>13.94</v>
       </c>
       <c r="L187">
-        <v>125.48</v>
+        <v>125.41</v>
       </c>
       <c r="M187">
-        <v>13965615</v>
+        <v>13863912</v>
       </c>
       <c r="N187">
-        <v>8231249</v>
+        <v>8191138</v>
       </c>
       <c r="O187">
         <v>2506811</v>
@@ -9566,16 +9566,16 @@
         <v>31.96</v>
       </c>
       <c r="K188">
-        <v>14.01</v>
+        <v>13.98</v>
       </c>
       <c r="L188">
-        <v>125.89</v>
+        <v>125.83</v>
       </c>
       <c r="M188">
-        <v>14176848</v>
+        <v>14075145</v>
       </c>
       <c r="N188">
-        <v>8311035</v>
+        <v>8270924</v>
       </c>
       <c r="O188">
         <v>2528409</v>
@@ -9601,7 +9601,7 @@
         <v>631919</v>
       </c>
       <c r="E189">
-        <v>204866</v>
+        <v>204810</v>
       </c>
       <c r="F189">
         <v>10180433</v>
@@ -9619,19 +9619,19 @@
         <v>31.5</v>
       </c>
       <c r="K189">
-        <v>14.03</v>
+        <v>14.01</v>
       </c>
       <c r="L189">
-        <v>126.37</v>
+        <v>126.31</v>
       </c>
       <c r="M189">
-        <v>14260156</v>
+        <v>14158453</v>
       </c>
       <c r="N189">
-        <v>8315395</v>
+        <v>8275284</v>
       </c>
       <c r="O189">
-        <v>2521451</v>
+        <v>2521395</v>
       </c>
       <c r="P189">
         <v>3841</v>
@@ -9651,10 +9651,10 @@
         <v>1343308</v>
       </c>
       <c r="D190">
-        <v>509987</v>
+        <v>509923</v>
       </c>
       <c r="E190">
-        <v>181941</v>
+        <v>181637</v>
       </c>
       <c r="F190">
         <v>9164177</v>
@@ -9669,22 +9669,22 @@
         <v>128.7</v>
       </c>
       <c r="J190">
-        <v>31.47</v>
+        <v>31.46</v>
       </c>
       <c r="K190">
-        <v>14.06</v>
+        <v>14.03</v>
       </c>
       <c r="L190">
-        <v>126.78</v>
+        <v>126.73</v>
       </c>
       <c r="M190">
-        <v>14422483</v>
+        <v>14320780</v>
       </c>
       <c r="N190">
-        <v>8370976</v>
+        <v>8330801</v>
       </c>
       <c r="O190">
-        <v>2540054</v>
+        <v>2539694</v>
       </c>
       <c r="P190">
         <v>3855</v>
@@ -9704,40 +9704,40 @@
         <v>1667576</v>
       </c>
       <c r="D191">
-        <v>573576</v>
+        <v>565804</v>
       </c>
       <c r="E191">
-        <v>207668</v>
+        <v>205478</v>
       </c>
       <c r="F191">
         <v>9966680</v>
       </c>
       <c r="G191">
-        <v>8670809</v>
+        <v>8568198</v>
       </c>
       <c r="H191">
-        <v>1073127</v>
+        <v>1059755</v>
       </c>
       <c r="I191">
-        <v>128.59</v>
+        <v>128.56</v>
       </c>
       <c r="J191">
-        <v>31.29</v>
+        <v>31.26</v>
       </c>
       <c r="K191">
-        <v>14.13</v>
+        <v>14.1</v>
       </c>
       <c r="L191">
-        <v>127.14</v>
+        <v>127.08</v>
       </c>
       <c r="M191">
-        <v>14527707</v>
+        <v>14412633</v>
       </c>
       <c r="N191">
-        <v>8368526</v>
+        <v>8320579</v>
       </c>
       <c r="O191">
-        <v>2551078</v>
+        <v>2548528</v>
       </c>
       <c r="P191">
         <v>3864</v>
@@ -9775,22 +9775,22 @@
         <v>130.9</v>
       </c>
       <c r="J192">
-        <v>31.03</v>
+        <v>31.15</v>
       </c>
       <c r="K192">
-        <v>14.22</v>
+        <v>14.19</v>
       </c>
       <c r="L192">
-        <v>127.59</v>
+        <v>127.53</v>
       </c>
       <c r="M192">
-        <v>14532482</v>
+        <v>14417407</v>
       </c>
       <c r="N192">
-        <v>8290100</v>
+        <v>8242153</v>
       </c>
       <c r="O192">
-        <v>2547700</v>
+        <v>2545150</v>
       </c>
       <c r="P192">
         <v>3867</v>
@@ -9828,22 +9828,22 @@
         <v>132.24</v>
       </c>
       <c r="J193">
-        <v>31.25</v>
+        <v>31.37</v>
       </c>
       <c r="K193">
-        <v>14.26</v>
+        <v>14.23</v>
       </c>
       <c r="L193">
-        <v>128.13</v>
+        <v>128.09</v>
       </c>
       <c r="M193">
-        <v>14761005</v>
+        <v>14645931</v>
       </c>
       <c r="N193">
-        <v>8365192</v>
+        <v>8317245</v>
       </c>
       <c r="O193">
-        <v>2572348</v>
+        <v>2569798</v>
       </c>
       <c r="P193">
         <v>3862</v>
@@ -9863,13 +9863,13 @@
         <v>2447240</v>
       </c>
       <c r="D194">
-        <v>1315030</v>
+        <v>1277139</v>
       </c>
       <c r="E194">
         <v>235008</v>
       </c>
       <c r="F194">
-        <v>14729046</v>
+        <v>14582389</v>
       </c>
       <c r="G194">
         <v>13027499</v>
@@ -9881,22 +9881,22 @@
         <v>133.57</v>
       </c>
       <c r="J194">
-        <v>30.92</v>
+        <v>31.04</v>
       </c>
       <c r="K194">
-        <v>14.23</v>
+        <v>14.27</v>
       </c>
       <c r="L194">
-        <v>128.88</v>
+        <v>128.83</v>
       </c>
       <c r="M194">
-        <v>14843686</v>
+        <v>14728612</v>
       </c>
       <c r="N194">
-        <v>8388079</v>
+        <v>8302241</v>
       </c>
       <c r="O194">
-        <v>2570148</v>
+        <v>2567598</v>
       </c>
       <c r="P194">
         <v>3869</v>
@@ -9934,22 +9934,22 @@
         <v>135</v>
       </c>
       <c r="J195">
-        <v>30.92</v>
+        <v>31.04</v>
       </c>
       <c r="K195">
-        <v>14.31</v>
+        <v>14.35</v>
       </c>
       <c r="L195">
-        <v>129.54</v>
+        <v>129.5</v>
       </c>
       <c r="M195">
-        <v>14888617</v>
+        <v>14773542</v>
       </c>
       <c r="N195">
-        <v>8325551</v>
+        <v>8239713</v>
       </c>
       <c r="O195">
-        <v>2571037</v>
+        <v>2568487</v>
       </c>
       <c r="P195">
         <v>3875</v>
@@ -9975,7 +9975,7 @@
         <v>219934</v>
       </c>
       <c r="F196">
-        <v>13097708</v>
+        <v>12935633</v>
       </c>
       <c r="G196">
         <v>11730221</v>
@@ -9987,22 +9987,22 @@
         <v>134.8</v>
       </c>
       <c r="J196">
-        <v>30.62</v>
+        <v>30.74</v>
       </c>
       <c r="K196">
-        <v>14.32</v>
+        <v>14.36</v>
       </c>
       <c r="L196">
-        <v>130.19</v>
+        <v>130.16</v>
       </c>
       <c r="M196">
-        <v>14967298</v>
+        <v>14852224</v>
       </c>
       <c r="N196">
-        <v>8320047</v>
+        <v>8234209</v>
       </c>
       <c r="O196">
-        <v>2563111</v>
+        <v>2560561</v>
       </c>
       <c r="P196">
         <v>3873</v>
@@ -10040,22 +10040,22 @@
         <v>135.23</v>
       </c>
       <c r="J197">
-        <v>30.67</v>
+        <v>30.82</v>
       </c>
       <c r="K197">
-        <v>14.33</v>
+        <v>14.37</v>
       </c>
       <c r="L197">
-        <v>130.86</v>
+        <v>130.83</v>
       </c>
       <c r="M197">
-        <v>15089443</v>
+        <v>14974368</v>
       </c>
       <c r="N197">
-        <v>8341511</v>
+        <v>8255673</v>
       </c>
       <c r="O197">
-        <v>2566566</v>
+        <v>2564016</v>
       </c>
       <c r="P197">
         <v>3878</v>
@@ -10093,22 +10093,22 @@
         <v>135.78</v>
       </c>
       <c r="J198">
-        <v>30.97</v>
+        <v>31.12</v>
       </c>
       <c r="K198">
-        <v>14.33</v>
+        <v>14.39</v>
       </c>
       <c r="L198">
         <v>131.55</v>
       </c>
       <c r="M198">
-        <v>15141575</v>
+        <v>15128204</v>
       </c>
       <c r="N198">
-        <v>8330336</v>
+        <v>8284609</v>
       </c>
       <c r="O198">
-        <v>2567367</v>
+        <v>2564817</v>
       </c>
       <c r="P198">
         <v>3884</v>
@@ -10131,10 +10131,10 @@
         <v>525103</v>
       </c>
       <c r="E199">
-        <v>214626</v>
+        <v>212380</v>
       </c>
       <c r="F199">
-        <v>10187282</v>
+        <v>10143793</v>
       </c>
       <c r="G199">
         <v>9028611</v>
@@ -10146,22 +10146,22 @@
         <v>135.39</v>
       </c>
       <c r="J199">
-        <v>30.94</v>
+        <v>31.06</v>
       </c>
       <c r="K199">
-        <v>14.37</v>
+        <v>14.44</v>
       </c>
       <c r="L199">
         <v>132.19</v>
       </c>
       <c r="M199">
-        <v>15309119</v>
+        <v>15295747</v>
       </c>
       <c r="N199">
-        <v>8356584</v>
+        <v>8310857</v>
       </c>
       <c r="O199">
-        <v>2587917</v>
+        <v>2583121</v>
       </c>
       <c r="P199">
         <v>3887</v>
@@ -10184,7 +10184,7 @@
         <v>735606</v>
       </c>
       <c r="E200">
-        <v>247048</v>
+        <v>247004</v>
       </c>
       <c r="F200">
         <v>11601024</v>
@@ -10199,22 +10199,22 @@
         <v>134.13</v>
       </c>
       <c r="J200">
-        <v>31</v>
+        <v>31.26</v>
       </c>
       <c r="K200">
-        <v>14.43</v>
+        <v>14.5</v>
       </c>
       <c r="L200">
         <v>132.87</v>
       </c>
       <c r="M200">
-        <v>15440729</v>
+        <v>15427357</v>
       </c>
       <c r="N200">
-        <v>8350603</v>
+        <v>8304876</v>
       </c>
       <c r="O200">
-        <v>2599967</v>
+        <v>2595127</v>
       </c>
       <c r="P200">
         <v>3886</v>
@@ -10237,7 +10237,7 @@
         <v>649662</v>
       </c>
       <c r="E201">
-        <v>210437</v>
+        <v>210292</v>
       </c>
       <c r="F201">
         <v>10189513</v>
@@ -10252,22 +10252,22 @@
         <v>135.05</v>
       </c>
       <c r="J201">
-        <v>31.3</v>
+        <v>31.56</v>
       </c>
       <c r="K201">
-        <v>14.4</v>
+        <v>14.46</v>
       </c>
       <c r="L201">
         <v>133.49</v>
       </c>
       <c r="M201">
-        <v>15510503</v>
+        <v>15497132</v>
       </c>
       <c r="N201">
-        <v>8368346</v>
+        <v>8322619</v>
       </c>
       <c r="O201">
-        <v>2605538</v>
+        <v>2600609</v>
       </c>
       <c r="P201">
         <v>3887</v>
@@ -10293,7 +10293,7 @@
         <v>211859</v>
       </c>
       <c r="F202">
-        <v>10071152</v>
+        <v>9577738</v>
       </c>
       <c r="G202">
         <v>8724780</v>
@@ -10305,22 +10305,22 @@
         <v>136.9</v>
       </c>
       <c r="J202">
-        <v>31.68</v>
+        <v>31.95</v>
       </c>
       <c r="K202">
-        <v>14.46</v>
+        <v>14.53</v>
       </c>
       <c r="L202">
-        <v>134.04</v>
+        <v>134.05</v>
       </c>
       <c r="M202">
-        <v>15673813</v>
+        <v>15660442</v>
       </c>
       <c r="N202">
-        <v>8381903</v>
+        <v>8336240</v>
       </c>
       <c r="O202">
-        <v>2635456</v>
+        <v>2630831</v>
       </c>
       <c r="P202">
         <v>3895</v>
@@ -10346,7 +10346,7 @@
         <v>223173</v>
       </c>
       <c r="F203">
-        <v>9851212</v>
+        <v>9570267</v>
       </c>
       <c r="G203">
         <v>8695175</v>
@@ -10358,10 +10358,10 @@
         <v>138.01</v>
       </c>
       <c r="J203">
-        <v>31.78</v>
+        <v>32.08</v>
       </c>
       <c r="K203">
-        <v>14.47</v>
+        <v>14.53</v>
       </c>
       <c r="L203">
         <v>134.72</v>
@@ -10370,10 +10370,10 @@
         <v>15757689</v>
       </c>
       <c r="N203">
-        <v>8380544</v>
+        <v>8342653</v>
       </c>
       <c r="O203">
-        <v>2650961</v>
+        <v>2648526</v>
       </c>
       <c r="P203">
         <v>3915</v>
@@ -10411,10 +10411,10 @@
         <v>137.51</v>
       </c>
       <c r="J204">
-        <v>31.92</v>
+        <v>32.06</v>
       </c>
       <c r="K204">
-        <v>14.52</v>
+        <v>14.58</v>
       </c>
       <c r="L204">
         <v>135.15</v>
@@ -10423,10 +10423,10 @@
         <v>15773575</v>
       </c>
       <c r="N204">
-        <v>8330361</v>
+        <v>8292470</v>
       </c>
       <c r="O204">
-        <v>2658783</v>
+        <v>2656348</v>
       </c>
       <c r="P204">
         <v>3927</v>
@@ -10464,10 +10464,10 @@
         <v>137.95</v>
       </c>
       <c r="J205">
-        <v>32.16</v>
+        <v>32.31</v>
       </c>
       <c r="K205">
-        <v>14.52</v>
+        <v>14.59</v>
       </c>
       <c r="L205">
         <v>135.65</v>
@@ -10476,10 +10476,10 @@
         <v>15898070</v>
       </c>
       <c r="N205">
-        <v>8360752</v>
+        <v>8322861</v>
       </c>
       <c r="O205">
-        <v>2687332</v>
+        <v>2684897</v>
       </c>
       <c r="P205">
         <v>3938</v>
@@ -10517,7 +10517,7 @@
         <v>138.97</v>
       </c>
       <c r="J206">
-        <v>32.12</v>
+        <v>32.27</v>
       </c>
       <c r="K206">
         <v>14.65</v>
@@ -10532,7 +10532,7 @@
         <v>8190399</v>
       </c>
       <c r="O206">
-        <v>2682386</v>
+        <v>2679951</v>
       </c>
       <c r="P206">
         <v>3943</v>
@@ -10570,7 +10570,7 @@
         <v>140.64</v>
       </c>
       <c r="J207">
-        <v>32.2</v>
+        <v>32.35</v>
       </c>
       <c r="K207">
         <v>14.64</v>
@@ -10585,7 +10585,7 @@
         <v>8167954</v>
       </c>
       <c r="O207">
-        <v>2694737</v>
+        <v>2692302</v>
       </c>
       <c r="P207">
         <v>3943</v>
@@ -10623,7 +10623,7 @@
         <v>140.76</v>
       </c>
       <c r="J208">
-        <v>32.44</v>
+        <v>32.59</v>
       </c>
       <c r="K208">
         <v>14.7</v>
@@ -10638,7 +10638,7 @@
         <v>8133267</v>
       </c>
       <c r="O208">
-        <v>2719320</v>
+        <v>2716885</v>
       </c>
       <c r="P208">
         <v>3945</v>
@@ -10676,7 +10676,7 @@
         <v>140.62</v>
       </c>
       <c r="J209">
-        <v>32.31</v>
+        <v>32.43</v>
       </c>
       <c r="K209">
         <v>14.74</v>
@@ -10691,7 +10691,7 @@
         <v>8038963</v>
       </c>
       <c r="O209">
-        <v>2707762</v>
+        <v>2705327</v>
       </c>
       <c r="P209">
         <v>3954</v>
@@ -10729,7 +10729,7 @@
         <v>140.5</v>
       </c>
       <c r="J210">
-        <v>32.18</v>
+        <v>32.29</v>
       </c>
       <c r="K210">
         <v>14.77</v>
@@ -10744,7 +10744,7 @@
         <v>7908330</v>
       </c>
       <c r="O210">
-        <v>2680327</v>
+        <v>2677892</v>
       </c>
       <c r="P210">
         <v>3955</v>
@@ -10782,7 +10782,7 @@
         <v>140.32</v>
       </c>
       <c r="J211">
-        <v>31.96</v>
+        <v>32.1</v>
       </c>
       <c r="K211">
         <v>14.74</v>
@@ -10797,7 +10797,7 @@
         <v>7873641</v>
       </c>
       <c r="O211">
-        <v>2671969</v>
+        <v>2671780</v>
       </c>
       <c r="P211">
         <v>3950</v>
@@ -10850,7 +10850,7 @@
         <v>7781838</v>
       </c>
       <c r="O212">
-        <v>2637230</v>
+        <v>2637085</v>
       </c>
       <c r="P212">
         <v>3967</v>
@@ -11874,16 +11874,16 @@
         <v>32598</v>
       </c>
       <c r="B232">
-        <v>1361121</v>
+        <v>1356063</v>
       </c>
       <c r="D232">
-        <v>652549</v>
+        <v>647549</v>
       </c>
       <c r="E232">
         <v>176192</v>
       </c>
       <c r="F232">
-        <v>11588939</v>
+        <v>11519378</v>
       </c>
       <c r="G232">
         <v>10451849</v>
@@ -11898,7 +11898,7 @@
         <v>27.8</v>
       </c>
       <c r="K232">
-        <v>13.62</v>
+        <v>13.63</v>
       </c>
       <c r="L232">
         <v>145.74</v>
@@ -11907,7 +11907,7 @@
         <v>13112231</v>
       </c>
       <c r="N232">
-        <v>6838131</v>
+        <v>6833131</v>
       </c>
       <c r="O232">
         <v>1926636</v>
@@ -11927,7 +11927,7 @@
         <v>32628</v>
       </c>
       <c r="B233">
-        <v>1116786</v>
+        <v>1116846</v>
       </c>
       <c r="D233">
         <v>468631</v>
@@ -11951,7 +11951,7 @@
         <v>27.67</v>
       </c>
       <c r="K233">
-        <v>13.61</v>
+        <v>13.62</v>
       </c>
       <c r="L233">
         <v>146.13</v>
@@ -11960,7 +11960,7 @@
         <v>13134026</v>
       </c>
       <c r="N233">
-        <v>6838696</v>
+        <v>6833696</v>
       </c>
       <c r="O233">
         <v>1912217</v>
@@ -12004,7 +12004,7 @@
         <v>27.52</v>
       </c>
       <c r="K234">
-        <v>13.61</v>
+        <v>13.62</v>
       </c>
       <c r="L234">
         <v>146.66</v>
@@ -12013,7 +12013,7 @@
         <v>13258873</v>
       </c>
       <c r="N234">
-        <v>6876100</v>
+        <v>6871100</v>
       </c>
       <c r="O234">
         <v>1912025</v>
@@ -12057,7 +12057,7 @@
         <v>27.74</v>
       </c>
       <c r="K235">
-        <v>13.53</v>
+        <v>13.54</v>
       </c>
       <c r="L235">
         <v>147.25</v>
@@ -12066,7 +12066,7 @@
         <v>13315210</v>
       </c>
       <c r="N235">
-        <v>6918759</v>
+        <v>6913759</v>
       </c>
       <c r="O235">
         <v>1902946</v>
@@ -12119,7 +12119,7 @@
         <v>13452236</v>
       </c>
       <c r="N236">
-        <v>6993441</v>
+        <v>6988441</v>
       </c>
       <c r="O236">
         <v>1904158</v>
@@ -12139,7 +12139,7 @@
         <v>32751</v>
       </c>
       <c r="B237">
-        <v>1266305</v>
+        <v>1266285</v>
       </c>
       <c r="D237">
         <v>627549</v>
@@ -12163,7 +12163,7 @@
         <v>28.08</v>
       </c>
       <c r="K237">
-        <v>13.41</v>
+        <v>13.42</v>
       </c>
       <c r="L237">
         <v>148.51</v>
@@ -12172,7 +12172,7 @@
         <v>13574992</v>
       </c>
       <c r="N237">
-        <v>7057325</v>
+        <v>7052325</v>
       </c>
       <c r="O237">
         <v>1907438</v>
@@ -12192,7 +12192,7 @@
         <v>32781</v>
       </c>
       <c r="B238">
-        <v>1081622</v>
+        <v>1081620</v>
       </c>
       <c r="D238">
         <v>432172</v>
@@ -12213,10 +12213,10 @@
         <v>152.18</v>
       </c>
       <c r="J238">
-        <v>27.99</v>
+        <v>28.01</v>
       </c>
       <c r="K238">
-        <v>13.37</v>
+        <v>13.38</v>
       </c>
       <c r="L238">
         <v>149.09</v>
@@ -12225,7 +12225,7 @@
         <v>13656326</v>
       </c>
       <c r="N238">
-        <v>7089977</v>
+        <v>7084977</v>
       </c>
       <c r="O238">
         <v>1913937</v>
@@ -12266,10 +12266,10 @@
         <v>155.56</v>
       </c>
       <c r="J239">
-        <v>28.18</v>
+        <v>28.2</v>
       </c>
       <c r="K239">
-        <v>13.29</v>
+        <v>13.3</v>
       </c>
       <c r="L239">
         <v>149.86</v>
@@ -12278,7 +12278,7 @@
         <v>13906989</v>
       </c>
       <c r="N239">
-        <v>7227337</v>
+        <v>7222337</v>
       </c>
       <c r="O239">
         <v>1927110</v>
@@ -12319,10 +12319,10 @@
         <v>154.36</v>
       </c>
       <c r="J240">
-        <v>28.14</v>
+        <v>28.16</v>
       </c>
       <c r="K240">
-        <v>13.26</v>
+        <v>13.27</v>
       </c>
       <c r="L240">
         <v>150.61</v>
@@ -12331,7 +12331,7 @@
         <v>14117140</v>
       </c>
       <c r="N240">
-        <v>7315643</v>
+        <v>7310643</v>
       </c>
       <c r="O240">
         <v>1935214</v>
@@ -12354,7 +12354,7 @@
         <v>1971875</v>
       </c>
       <c r="D241">
-        <v>692431</v>
+        <v>692731</v>
       </c>
       <c r="E241">
         <v>153622</v>
@@ -12372,10 +12372,10 @@
         <v>155.45</v>
       </c>
       <c r="J241">
-        <v>28.05</v>
+        <v>28.07</v>
       </c>
       <c r="K241">
-        <v>13.27</v>
+        <v>13.28</v>
       </c>
       <c r="L241">
         <v>151.43</v>
@@ -12384,7 +12384,7 @@
         <v>14303157</v>
       </c>
       <c r="N241">
-        <v>7368766</v>
+        <v>7364066</v>
       </c>
       <c r="O241">
         <v>1940390</v>
@@ -12425,7 +12425,7 @@
         <v>158.21</v>
       </c>
       <c r="J242">
-        <v>28.24</v>
+        <v>28.26</v>
       </c>
       <c r="K242">
         <v>13.13</v>
@@ -12437,7 +12437,7 @@
         <v>14733543</v>
       </c>
       <c r="N242">
-        <v>7619704</v>
+        <v>7615004</v>
       </c>
       <c r="O242">
         <v>1975023</v>
@@ -12478,10 +12478,10 @@
         <v>160.08</v>
       </c>
       <c r="J243">
-        <v>28.25</v>
+        <v>28.27</v>
       </c>
       <c r="K243">
-        <v>13.16</v>
+        <v>13.17</v>
       </c>
       <c r="L243">
         <v>153.58</v>
@@ -12490,7 +12490,7 @@
         <v>15034027</v>
       </c>
       <c r="N243">
-        <v>7707749</v>
+        <v>7703049</v>
       </c>
       <c r="O243">
         <v>1993665</v>
@@ -12531,7 +12531,7 @@
         <v>159.24</v>
       </c>
       <c r="J244">
-        <v>28.33</v>
+        <v>28.35</v>
       </c>
       <c r="K244">
         <v>13.22</v>
@@ -12543,7 +12543,7 @@
         <v>15228048</v>
       </c>
       <c r="N244">
-        <v>7727606</v>
+        <v>7727906</v>
       </c>
       <c r="O244">
         <v>2008393</v>
@@ -12584,7 +12584,7 @@
         <v>161.65</v>
       </c>
       <c r="J245">
-        <v>28.21</v>
+        <v>28.23</v>
       </c>
       <c r="K245">
         <v>13.28</v>
@@ -12596,7 +12596,7 @@
         <v>15568195</v>
       </c>
       <c r="N245">
-        <v>7813295</v>
+        <v>7813595</v>
       </c>
       <c r="O245">
         <v>2038889</v>
@@ -12637,7 +12637,7 @@
         <v>161.65</v>
       </c>
       <c r="J246">
-        <v>28.34</v>
+        <v>28.36</v>
       </c>
       <c r="K246">
         <v>13.38</v>
@@ -12649,7 +12649,7 @@
         <v>15897264</v>
       </c>
       <c r="N246">
-        <v>7880459</v>
+        <v>7880759</v>
       </c>
       <c r="O246">
         <v>2073202</v>
@@ -12669,7 +12669,7 @@
         <v>33054</v>
       </c>
       <c r="B247">
-        <v>1333281</v>
+        <v>1333284</v>
       </c>
       <c r="D247">
         <v>508177</v>
@@ -12690,7 +12690,7 @@
         <v>161.53</v>
       </c>
       <c r="J247">
-        <v>28.43</v>
+        <v>28.45</v>
       </c>
       <c r="K247">
         <v>13.45</v>
@@ -12702,7 +12702,7 @@
         <v>16086472</v>
       </c>
       <c r="N247">
-        <v>7893499</v>
+        <v>7893799</v>
       </c>
       <c r="O247">
         <v>2094989</v>
@@ -12743,7 +12743,7 @@
         <v>159.56</v>
       </c>
       <c r="J248">
-        <v>28.11</v>
+        <v>28.13</v>
       </c>
       <c r="K248">
         <v>13.51</v>
@@ -12755,7 +12755,7 @@
         <v>16421783</v>
       </c>
       <c r="N248">
-        <v>7987182</v>
+        <v>7987482</v>
       </c>
       <c r="O248">
         <v>2141778</v>
@@ -12796,7 +12796,7 @@
         <v>160.09</v>
       </c>
       <c r="J249">
-        <v>28.17</v>
+        <v>28.19</v>
       </c>
       <c r="K249">
         <v>13.57</v>
@@ -12808,7 +12808,7 @@
         <v>16653669</v>
       </c>
       <c r="N249">
-        <v>8026433</v>
+        <v>8026733</v>
       </c>
       <c r="O249">
         <v>2171650</v>
@@ -12861,7 +12861,7 @@
         <v>16873887</v>
       </c>
       <c r="N250">
-        <v>8091439</v>
+        <v>8091739</v>
       </c>
       <c r="O250">
         <v>2192132</v>
@@ -12914,7 +12914,7 @@
         <v>17230868</v>
       </c>
       <c r="N251">
-        <v>8214514</v>
+        <v>8214814</v>
       </c>
       <c r="O251">
         <v>2238233</v>
@@ -12967,7 +12967,7 @@
         <v>17568931</v>
       </c>
       <c r="N252">
-        <v>8411616</v>
+        <v>8411916</v>
       </c>
       <c r="O252">
         <v>2272225</v>
@@ -13114,7 +13114,7 @@
         <v>169.18</v>
       </c>
       <c r="J255">
-        <v>30.47</v>
+        <v>30.46</v>
       </c>
       <c r="K255">
         <v>13.35</v>
@@ -13273,7 +13273,7 @@
         <v>170.13</v>
       </c>
       <c r="J258">
-        <v>32.48</v>
+        <v>32.47</v>
       </c>
       <c r="K258">
         <v>13.9</v>
@@ -13308,7 +13308,7 @@
         <v>1496634</v>
       </c>
       <c r="D259">
-        <v>588585</v>
+        <v>588594</v>
       </c>
       <c r="E259">
         <v>277356</v>
@@ -13338,7 +13338,7 @@
         <v>22650261</v>
       </c>
       <c r="N259">
-        <v>9984564</v>
+        <v>9984573</v>
       </c>
       <c r="O259">
         <v>2824805</v>
@@ -13391,7 +13391,7 @@
         <v>23387666</v>
       </c>
       <c r="N260">
-        <v>10078405</v>
+        <v>10078414</v>
       </c>
       <c r="O260">
         <v>2966371</v>
@@ -13414,7 +13414,7 @@
         <v>1518933</v>
       </c>
       <c r="D261">
-        <v>691257</v>
+        <v>691256</v>
       </c>
       <c r="E261">
         <v>316484</v>
@@ -13444,7 +13444,7 @@
         <v>23868636</v>
       </c>
       <c r="N261">
-        <v>10102862</v>
+        <v>10102870</v>
       </c>
       <c r="O261">
         <v>3080430</v>
@@ -13464,10 +13464,10 @@
         <v>33511</v>
       </c>
       <c r="B262">
-        <v>1358799</v>
+        <v>1358766</v>
       </c>
       <c r="D262">
-        <v>541597</v>
+        <v>541600</v>
       </c>
       <c r="E262">
         <v>275684</v>
@@ -13497,7 +13497,7 @@
         <v>24372065</v>
       </c>
       <c r="N262">
-        <v>10147281</v>
+        <v>10147292</v>
       </c>
       <c r="O262">
         <v>3187381</v>
@@ -13550,7 +13550,7 @@
         <v>24801204</v>
       </c>
       <c r="N263">
-        <v>10151259</v>
+        <v>10151270</v>
       </c>
       <c r="O263">
         <v>3292647</v>
@@ -13603,7 +13603,7 @@
         <v>24999802</v>
       </c>
       <c r="N264">
-        <v>10039564</v>
+        <v>10039575</v>
       </c>
       <c r="O264">
         <v>3362519</v>
@@ -13656,7 +13656,7 @@
         <v>25446271</v>
       </c>
       <c r="N265">
-        <v>10074550</v>
+        <v>10074561</v>
       </c>
       <c r="O265">
         <v>3472019</v>
@@ -13709,7 +13709,7 @@
         <v>25640586</v>
       </c>
       <c r="N266">
-        <v>9984857</v>
+        <v>9984868</v>
       </c>
       <c r="O266">
         <v>3566138</v>
@@ -13762,7 +13762,7 @@
         <v>25734633</v>
       </c>
       <c r="N267">
-        <v>9875268</v>
+        <v>9875279</v>
       </c>
       <c r="O267">
         <v>3640526</v>
@@ -13815,7 +13815,7 @@
         <v>25873044</v>
       </c>
       <c r="N268">
-        <v>9785739</v>
+        <v>9785750</v>
       </c>
       <c r="O268">
         <v>3722157</v>
@@ -13868,7 +13868,7 @@
         <v>25785239</v>
       </c>
       <c r="N269">
-        <v>9702516</v>
+        <v>9702527</v>
       </c>
       <c r="O269">
         <v>3781823</v>
@@ -13921,7 +13921,7 @@
         <v>25494797</v>
       </c>
       <c r="N270">
-        <v>9588566</v>
+        <v>9588577</v>
       </c>
       <c r="O270">
         <v>3793494</v>
@@ -13974,7 +13974,7 @@
         <v>25613491</v>
       </c>
       <c r="N271">
-        <v>9621741</v>
+        <v>9621743</v>
       </c>
       <c r="O271">
         <v>3851531</v>
@@ -14027,7 +14027,7 @@
         <v>25527904</v>
       </c>
       <c r="N272">
-        <v>9612565</v>
+        <v>9612567</v>
       </c>
       <c r="O272">
         <v>3860001</v>
@@ -14080,7 +14080,7 @@
         <v>25516360</v>
       </c>
       <c r="N273">
-        <v>9648574</v>
+        <v>9648577</v>
       </c>
       <c r="O273">
         <v>3855643</v>
@@ -15640,7 +15640,7 @@
         <v>1424768</v>
       </c>
       <c r="D303">
-        <v>772382</v>
+        <v>772392</v>
       </c>
       <c r="E303">
         <v>209034</v>
@@ -15670,7 +15670,7 @@
         <v>21454564</v>
       </c>
       <c r="N303">
-        <v>7815183</v>
+        <v>7815193</v>
       </c>
       <c r="O303">
         <v>2926756</v>
@@ -15690,7 +15690,7 @@
         <v>34789</v>
       </c>
       <c r="B304">
-        <v>1453764</v>
+        <v>1453750</v>
       </c>
       <c r="D304">
         <v>660155</v>
@@ -15723,7 +15723,7 @@
         <v>21239723</v>
       </c>
       <c r="N304">
-        <v>7764819</v>
+        <v>7764829</v>
       </c>
       <c r="O304">
         <v>2884945</v>
@@ -15776,7 +15776,7 @@
         <v>21078175</v>
       </c>
       <c r="N305">
-        <v>7734864</v>
+        <v>7734874</v>
       </c>
       <c r="O305">
         <v>2843897</v>
@@ -15829,7 +15829,7 @@
         <v>21087186</v>
       </c>
       <c r="N306">
-        <v>7737929</v>
+        <v>7737939</v>
       </c>
       <c r="O306">
         <v>2816565</v>
@@ -15882,7 +15882,7 @@
         <v>20976850</v>
       </c>
       <c r="N307">
-        <v>7755865</v>
+        <v>7755875</v>
       </c>
       <c r="O307">
         <v>2772737</v>
@@ -15935,7 +15935,7 @@
         <v>21034004</v>
       </c>
       <c r="N308">
-        <v>7835602</v>
+        <v>7835612</v>
       </c>
       <c r="O308">
         <v>2748430</v>
@@ -15988,7 +15988,7 @@
         <v>21022791</v>
       </c>
       <c r="N309">
-        <v>7871010</v>
+        <v>7871020</v>
       </c>
       <c r="O309">
         <v>2716998</v>
@@ -16041,7 +16041,7 @@
         <v>20993540</v>
       </c>
       <c r="N310">
-        <v>7893172</v>
+        <v>7893182</v>
       </c>
       <c r="O310">
         <v>2690365</v>
@@ -16094,7 +16094,7 @@
         <v>21136122</v>
       </c>
       <c r="N311">
-        <v>7955857</v>
+        <v>7955867</v>
       </c>
       <c r="O311">
         <v>2687438</v>
@@ -16147,7 +16147,7 @@
         <v>21224909</v>
       </c>
       <c r="N312">
-        <v>8014378</v>
+        <v>8014388</v>
       </c>
       <c r="O312">
         <v>2673184</v>
@@ -16200,7 +16200,7 @@
         <v>21282797</v>
       </c>
       <c r="N313">
-        <v>8035229</v>
+        <v>8035239</v>
       </c>
       <c r="O313">
         <v>2661773</v>
@@ -16253,7 +16253,7 @@
         <v>21624067</v>
       </c>
       <c r="N314">
-        <v>8171208</v>
+        <v>8171218</v>
       </c>
       <c r="O314">
         <v>2678469</v>
@@ -17333,7 +17333,7 @@
         <v>35734</v>
       </c>
       <c r="B335">
-        <v>1253498</v>
+        <v>1253478</v>
       </c>
       <c r="D335">
         <v>454304</v>
@@ -17651,7 +17651,7 @@
         <v>35915</v>
       </c>
       <c r="B341">
-        <v>1239471</v>
+        <v>1239485</v>
       </c>
       <c r="D341">
         <v>496030</v>
@@ -17757,7 +17757,7 @@
         <v>35976</v>
       </c>
       <c r="B343">
-        <v>1436988</v>
+        <v>1436997</v>
       </c>
       <c r="D343">
         <v>526283</v>
@@ -18764,7 +18764,7 @@
         <v>36556</v>
       </c>
       <c r="B362">
-        <v>1794130</v>
+        <v>1794097</v>
       </c>
       <c r="D362">
         <v>1007314</v>
@@ -19742,7 +19742,7 @@
         <v>3101.4</v>
       </c>
       <c r="D380">
-        <v>942973</v>
+        <v>942982</v>
       </c>
       <c r="E380">
         <v>256343</v>
@@ -19772,7 +19772,7 @@
         <v>25433709</v>
       </c>
       <c r="N380">
-        <v>8562888</v>
+        <v>8562897</v>
       </c>
       <c r="O380">
         <v>2331582</v>
@@ -19828,7 +19828,7 @@
         <v>26409071</v>
       </c>
       <c r="N381">
-        <v>8735626</v>
+        <v>8735635</v>
       </c>
       <c r="O381">
         <v>2396575</v>
@@ -19884,7 +19884,7 @@
         <v>27354013</v>
       </c>
       <c r="N382">
-        <v>8893958</v>
+        <v>8893967</v>
       </c>
       <c r="O382">
         <v>2476985</v>
@@ -19940,7 +19940,7 @@
         <v>28733387</v>
       </c>
       <c r="N383">
-        <v>9293160</v>
+        <v>9293169</v>
       </c>
       <c r="O383">
         <v>2594333</v>
@@ -19996,7 +19996,7 @@
         <v>30055176</v>
       </c>
       <c r="N384">
-        <v>9601271</v>
+        <v>9601280</v>
       </c>
       <c r="O384">
         <v>2700964</v>
@@ -20052,7 +20052,7 @@
         <v>31667095</v>
       </c>
       <c r="N385">
-        <v>9868193</v>
+        <v>9868202</v>
       </c>
       <c r="O385">
         <v>2829191</v>
@@ -20108,7 +20108,7 @@
         <v>33234908</v>
       </c>
       <c r="N386">
-        <v>10128484</v>
+        <v>10128493</v>
       </c>
       <c r="O386">
         <v>2973194</v>
@@ -20164,7 +20164,7 @@
         <v>34641357</v>
       </c>
       <c r="N387">
-        <v>10245454</v>
+        <v>10245463</v>
       </c>
       <c r="O387">
         <v>3103582</v>
@@ -20220,7 +20220,7 @@
         <v>36010053</v>
       </c>
       <c r="N388">
-        <v>10303343</v>
+        <v>10303352</v>
       </c>
       <c r="O388">
         <v>3283780</v>
@@ -20276,7 +20276,7 @@
         <v>37433295</v>
       </c>
       <c r="N389">
-        <v>10380776</v>
+        <v>10380785</v>
       </c>
       <c r="O389">
         <v>3511027</v>
@@ -20332,7 +20332,7 @@
         <v>38455572</v>
       </c>
       <c r="N390">
-        <v>10393258</v>
+        <v>10393267</v>
       </c>
       <c r="O390">
         <v>3681104</v>
@@ -20388,7 +20388,7 @@
         <v>39283367</v>
       </c>
       <c r="N391">
-        <v>10387139</v>
+        <v>10387148</v>
       </c>
       <c r="O391">
         <v>3822500</v>
@@ -22088,7 +22088,7 @@
         <v>38383</v>
       </c>
       <c r="B422">
-        <v>1977731</v>
+        <v>1977721</v>
       </c>
       <c r="C422">
         <v>3311.8</v>
@@ -23208,7 +23208,7 @@
         <v>38990</v>
       </c>
       <c r="B442">
-        <v>1074377</v>
+        <v>1074378</v>
       </c>
       <c r="C442">
         <v>2063.1</v>
@@ -29654,7 +29654,7 @@
         <v>2147.9</v>
       </c>
       <c r="D557">
-        <v>418906</v>
+        <v>418915</v>
       </c>
       <c r="E557">
         <v>205883</v>
@@ -29684,7 +29684,7 @@
         <v>31942597</v>
       </c>
       <c r="N557">
-        <v>6338591</v>
+        <v>6338600</v>
       </c>
       <c r="O557">
         <v>2431729</v>
@@ -29740,7 +29740,7 @@
         <v>32205379</v>
       </c>
       <c r="N558">
-        <v>6352861</v>
+        <v>6352870</v>
       </c>
       <c r="O558">
         <v>2434772</v>
@@ -29796,7 +29796,7 @@
         <v>32112341</v>
       </c>
       <c r="N559">
-        <v>6334437</v>
+        <v>6334446</v>
       </c>
       <c r="O559">
         <v>2413047</v>
@@ -29852,7 +29852,7 @@
         <v>32002531</v>
       </c>
       <c r="N560">
-        <v>6258012</v>
+        <v>6258021</v>
       </c>
       <c r="O560">
         <v>2394512</v>
@@ -29908,7 +29908,7 @@
         <v>32179771</v>
       </c>
       <c r="N561">
-        <v>6273721</v>
+        <v>6273730</v>
       </c>
       <c r="O561">
         <v>2395163</v>
@@ -29964,7 +29964,7 @@
         <v>31986852</v>
       </c>
       <c r="N562">
-        <v>6231295</v>
+        <v>6231304</v>
       </c>
       <c r="O562">
         <v>2370544</v>
@@ -30020,7 +30020,7 @@
         <v>32094765</v>
       </c>
       <c r="N563">
-        <v>6208345</v>
+        <v>6208354</v>
       </c>
       <c r="O563">
         <v>2368363</v>
@@ -30076,7 +30076,7 @@
         <v>32037220</v>
       </c>
       <c r="N564">
-        <v>6185848</v>
+        <v>6185857</v>
       </c>
       <c r="O564">
         <v>2350508</v>
@@ -30132,7 +30132,7 @@
         <v>31688353</v>
       </c>
       <c r="N565">
-        <v>6097383</v>
+        <v>6097392</v>
       </c>
       <c r="O565">
         <v>2323716</v>
@@ -30188,7 +30188,7 @@
         <v>31931357</v>
       </c>
       <c r="N566">
-        <v>6082071</v>
+        <v>6082080</v>
       </c>
       <c r="O566">
         <v>2328073</v>
@@ -30244,7 +30244,7 @@
         <v>31554829</v>
       </c>
       <c r="N567">
-        <v>5994649</v>
+        <v>5994658</v>
       </c>
       <c r="O567">
         <v>2300036</v>
@@ -30300,7 +30300,7 @@
         <v>31277884</v>
       </c>
       <c r="N568">
-        <v>5940527</v>
+        <v>5940536</v>
       </c>
       <c r="O568">
         <v>2273730</v>
@@ -30872,7 +30872,7 @@
         <v>14428</v>
       </c>
       <c r="R578">
-        <v>278536</v>
+        <v>278449</v>
       </c>
     </row>
     <row r="579">
@@ -30928,7 +30928,7 @@
         <v>14473</v>
       </c>
       <c r="R579">
-        <v>281407</v>
+        <v>279909</v>
       </c>
     </row>
     <row r="580">
@@ -30984,7 +30984,7 @@
         <v>14471</v>
       </c>
       <c r="R580">
-        <v>283722</v>
+        <v>283292</v>
       </c>
     </row>
     <row r="581">
@@ -31040,7 +31040,7 @@
         <v>14467</v>
       </c>
       <c r="R581">
-        <v>288622</v>
+        <v>288960</v>
       </c>
     </row>
     <row r="582">
@@ -31096,7 +31096,7 @@
         <v>14482</v>
       </c>
       <c r="R582">
-        <v>290059</v>
+        <v>290687</v>
       </c>
     </row>
     <row r="583">
@@ -31152,7 +31152,7 @@
         <v>14505</v>
       </c>
       <c r="R583">
-        <v>290567</v>
+        <v>291527</v>
       </c>
     </row>
     <row r="584">
@@ -31208,7 +31208,7 @@
         <v>14462</v>
       </c>
       <c r="R584">
-        <v>294781</v>
+        <v>293903</v>
       </c>
     </row>
     <row r="585">
@@ -31264,7 +31264,7 @@
         <v>14493</v>
       </c>
       <c r="R585">
-        <v>299258</v>
+        <v>299820</v>
       </c>
     </row>
     <row r="586">
@@ -31320,7 +31320,7 @@
         <v>14486</v>
       </c>
       <c r="R586">
-        <v>288216</v>
+        <v>286639</v>
       </c>
     </row>
     <row r="587">
@@ -31376,7 +31376,7 @@
         <v>14491</v>
       </c>
       <c r="R587">
-        <v>287133</v>
+        <v>287931</v>
       </c>
     </row>
     <row r="588">
@@ -31432,7 +31432,7 @@
         <v>14499</v>
       </c>
       <c r="R588">
-        <v>285853</v>
+        <v>285473</v>
       </c>
     </row>
     <row r="589">
@@ -31488,7 +31488,7 @@
         <v>14527</v>
       </c>
       <c r="R589">
-        <v>285645</v>
+        <v>286077</v>
       </c>
     </row>
     <row r="590">
@@ -31544,7 +31544,7 @@
         <v>14527</v>
       </c>
       <c r="R590">
-        <v>295719</v>
+        <v>295045</v>
       </c>
     </row>
     <row r="591">
@@ -31600,7 +31600,7 @@
         <v>14533</v>
       </c>
       <c r="R591">
-        <v>305067</v>
+        <v>303216</v>
       </c>
     </row>
     <row r="592">
@@ -31656,7 +31656,7 @@
         <v>14567</v>
       </c>
       <c r="R592">
-        <v>306010</v>
+        <v>303666</v>
       </c>
     </row>
     <row r="593">
@@ -31712,7 +31712,7 @@
         <v>14600</v>
       </c>
       <c r="R593">
-        <v>323581</v>
+        <v>326008</v>
       </c>
     </row>
     <row r="594">
@@ -31768,7 +31768,7 @@
         <v>14583</v>
       </c>
       <c r="R594">
-        <v>319247</v>
+        <v>320255</v>
       </c>
     </row>
     <row r="595">
@@ -31824,7 +31824,7 @@
         <v>14601</v>
       </c>
       <c r="R595">
-        <v>317261</v>
+        <v>316198</v>
       </c>
     </row>
     <row r="596">
@@ -31880,7 +31880,7 @@
         <v>14552</v>
       </c>
       <c r="R596">
-        <v>324076</v>
+        <v>325832</v>
       </c>
     </row>
     <row r="597">
@@ -31936,7 +31936,7 @@
         <v>14558</v>
       </c>
       <c r="R597">
-        <v>320471</v>
+        <v>320836</v>
       </c>
     </row>
     <row r="598">
@@ -31992,7 +31992,7 @@
         <v>14582</v>
       </c>
       <c r="R598">
-        <v>326913</v>
+        <v>325421</v>
       </c>
     </row>
     <row r="599">
@@ -32048,7 +32048,7 @@
         <v>14594</v>
       </c>
       <c r="R599">
-        <v>321971</v>
+        <v>322378</v>
       </c>
     </row>
     <row r="600">
@@ -32104,7 +32104,7 @@
         <v>14619</v>
       </c>
       <c r="R600">
-        <v>323942</v>
+        <v>323472</v>
       </c>
     </row>
     <row r="601">
@@ -32160,7 +32160,7 @@
         <v>14638</v>
       </c>
       <c r="R601">
-        <v>327795</v>
+        <v>327296</v>
       </c>
     </row>
     <row r="602">
@@ -32216,7 +32216,7 @@
         <v>14664</v>
       </c>
       <c r="R602">
-        <v>341963</v>
+        <v>341359</v>
       </c>
     </row>
     <row r="603">
@@ -32272,7 +32272,7 @@
         <v>14692</v>
       </c>
       <c r="R603">
-        <v>343097</v>
+        <v>345542</v>
       </c>
     </row>
     <row r="604">
@@ -32328,7 +32328,7 @@
         <v>14688</v>
       </c>
       <c r="R604">
-        <v>346286</v>
+        <v>343949</v>
       </c>
     </row>
     <row r="605">
@@ -32384,7 +32384,7 @@
         <v>13921</v>
       </c>
       <c r="R605">
-        <v>337598</v>
+        <v>340158</v>
       </c>
     </row>
     <row r="606">
@@ -32440,7 +32440,7 @@
         <v>13458</v>
       </c>
       <c r="R606">
-        <v>346584</v>
+        <v>344898</v>
       </c>
     </row>
     <row r="607">
@@ -32496,7 +32496,7 @@
         <v>13460</v>
       </c>
       <c r="R607">
-        <v>342378</v>
+        <v>343392</v>
       </c>
     </row>
     <row r="608">
@@ -32552,7 +32552,7 @@
         <v>13526</v>
       </c>
       <c r="R608">
-        <v>336713</v>
+        <v>337856</v>
       </c>
     </row>
     <row r="609">
@@ -32608,7 +32608,7 @@
         <v>13724</v>
       </c>
       <c r="R609">
-        <v>335100</v>
+        <v>334024</v>
       </c>
     </row>
     <row r="610">
@@ -32664,7 +32664,7 @@
         <v>13715</v>
       </c>
       <c r="R610">
-        <v>334831</v>
+        <v>335220</v>
       </c>
     </row>
     <row r="611">
@@ -32720,7 +32720,7 @@
         <v>13750</v>
       </c>
       <c r="R611">
-        <v>337476</v>
+        <v>338214</v>
       </c>
     </row>
     <row r="612">
@@ -32776,7 +32776,7 @@
         <v>13717</v>
       </c>
       <c r="R612">
-        <v>343612</v>
+        <v>340985</v>
       </c>
     </row>
     <row r="613">
@@ -32832,7 +32832,7 @@
         <v>13698</v>
       </c>
       <c r="R613">
-        <v>343531</v>
+        <v>345152</v>
       </c>
     </row>
     <row r="614">
@@ -32888,7 +32888,7 @@
         <v>13743</v>
       </c>
       <c r="R614">
-        <v>345096</v>
+        <v>342295</v>
       </c>
     </row>
     <row r="615">
@@ -32944,7 +32944,7 @@
         <v>13728</v>
       </c>
       <c r="R615">
-        <v>336315</v>
+        <v>334159</v>
       </c>
     </row>
     <row r="616">
@@ -33000,7 +33000,7 @@
         <v>13779</v>
       </c>
       <c r="R616">
-        <v>336681</v>
+        <v>337880</v>
       </c>
     </row>
     <row r="617">
@@ -33056,7 +33056,7 @@
         <v>13827</v>
       </c>
       <c r="R617">
-        <v>334978</v>
+        <v>336247</v>
       </c>
     </row>
     <row r="618">
@@ -33112,7 +33112,7 @@
         <v>13849</v>
       </c>
       <c r="R618">
-        <v>337801</v>
+        <v>337543</v>
       </c>
     </row>
     <row r="619">
@@ -33168,7 +33168,7 @@
         <v>13917</v>
       </c>
       <c r="R619">
-        <v>328950</v>
+        <v>329898</v>
       </c>
     </row>
     <row r="620">
@@ -33224,7 +33224,7 @@
         <v>13990</v>
       </c>
       <c r="R620">
-        <v>329615</v>
+        <v>330467</v>
       </c>
     </row>
     <row r="621">
@@ -33280,7 +33280,7 @@
         <v>14057</v>
       </c>
       <c r="R621">
-        <v>334864</v>
+        <v>332900</v>
       </c>
     </row>
     <row r="622">
@@ -33312,22 +33312,22 @@
         <v>352.03</v>
       </c>
       <c r="J622">
-        <v>29.06</v>
+        <v>29.07</v>
       </c>
       <c r="K622">
-        <v>21.08</v>
+        <v>21.09</v>
       </c>
       <c r="L622">
         <v>340.13</v>
       </c>
       <c r="M622">
-        <v>58977633</v>
+        <v>58977257</v>
       </c>
       <c r="N622">
-        <v>8867291</v>
+        <v>8860180</v>
       </c>
       <c r="O622">
-        <v>8844302</v>
+        <v>8844628</v>
       </c>
       <c r="P622">
         <v>5139</v>
@@ -33336,7 +33336,7 @@
         <v>14055</v>
       </c>
       <c r="R622">
-        <v>326687</v>
+        <v>327369</v>
       </c>
     </row>
     <row r="623">
@@ -33371,19 +33371,19 @@
         <v>34.85</v>
       </c>
       <c r="K623">
-        <v>19.56</v>
+        <v>19.58</v>
       </c>
       <c r="L623">
         <v>344.49</v>
       </c>
       <c r="M623">
-        <v>52904462</v>
+        <v>52904086</v>
       </c>
       <c r="N623">
-        <v>8457701</v>
+        <v>8450590</v>
       </c>
       <c r="O623">
-        <v>6715937</v>
+        <v>6716263</v>
       </c>
       <c r="P623">
         <v>5132</v>
@@ -33392,7 +33392,7 @@
         <v>14035</v>
       </c>
       <c r="R623">
-        <v>326597</v>
+        <v>324962</v>
       </c>
     </row>
     <row r="624">
@@ -33427,19 +33427,19 @@
         <v>39.27</v>
       </c>
       <c r="K624">
-        <v>18.64</v>
+        <v>18.66</v>
       </c>
       <c r="L624">
         <v>347.36</v>
       </c>
       <c r="M624">
-        <v>48445736</v>
+        <v>48445361</v>
       </c>
       <c r="N624">
-        <v>8045507</v>
+        <v>8038396</v>
       </c>
       <c r="O624">
-        <v>5597086</v>
+        <v>5597412</v>
       </c>
       <c r="P624">
         <v>5121</v>
@@ -33448,7 +33448,7 @@
         <v>14035</v>
       </c>
       <c r="R624">
-        <v>331859</v>
+        <v>331225</v>
       </c>
     </row>
     <row r="625">
@@ -33483,19 +33483,19 @@
         <v>40.35</v>
       </c>
       <c r="K625">
-        <v>17.9</v>
+        <v>17.92</v>
       </c>
       <c r="L625">
         <v>349.82</v>
       </c>
       <c r="M625">
-        <v>44248635</v>
+        <v>44248259</v>
       </c>
       <c r="N625">
-        <v>7582816</v>
+        <v>7575705</v>
       </c>
       <c r="O625">
-        <v>4737483</v>
+        <v>4737809</v>
       </c>
       <c r="P625">
         <v>5122</v>
@@ -33504,7 +33504,7 @@
         <v>14071</v>
       </c>
       <c r="R625">
-        <v>331023</v>
+        <v>332079</v>
       </c>
     </row>
     <row r="626">
@@ -33539,19 +33539,19 @@
         <v>40.27</v>
       </c>
       <c r="K626">
-        <v>17.39</v>
+        <v>17.41</v>
       </c>
       <c r="L626">
         <v>352.71</v>
       </c>
       <c r="M626">
-        <v>41265312</v>
+        <v>41264936</v>
       </c>
       <c r="N626">
-        <v>7202166</v>
+        <v>7195055</v>
       </c>
       <c r="O626">
-        <v>4093250</v>
+        <v>4093576</v>
       </c>
       <c r="P626">
         <v>5087</v>
@@ -33560,7 +33560,7 @@
         <v>14091</v>
       </c>
       <c r="R626">
-        <v>336477</v>
+        <v>335367</v>
       </c>
     </row>
     <row r="627">
@@ -33595,19 +33595,19 @@
         <v>38.7</v>
       </c>
       <c r="K627">
-        <v>16.93</v>
+        <v>16.95</v>
       </c>
       <c r="L627">
         <v>355.86</v>
       </c>
       <c r="M627">
-        <v>38612550</v>
+        <v>38612174</v>
       </c>
       <c r="N627">
-        <v>6829812</v>
+        <v>6822701</v>
       </c>
       <c r="O627">
-        <v>3599110</v>
+        <v>3599436</v>
       </c>
       <c r="P627">
         <v>5070</v>
@@ -33616,7 +33616,7 @@
         <v>14097</v>
       </c>
       <c r="R627">
-        <v>342490</v>
+        <v>339940</v>
       </c>
     </row>
     <row r="628">
@@ -33648,22 +33648,22 @@
         <v>408.04</v>
       </c>
       <c r="J628">
-        <v>35.62</v>
+        <v>35.65</v>
       </c>
       <c r="K628">
-        <v>16.62</v>
+        <v>16.64</v>
       </c>
       <c r="L628">
         <v>359.83</v>
       </c>
       <c r="M628">
-        <v>35806596</v>
+        <v>35806221</v>
       </c>
       <c r="N628">
-        <v>6354484</v>
+        <v>6347373</v>
       </c>
       <c r="O628">
-        <v>3158708</v>
+        <v>3159034</v>
       </c>
       <c r="P628">
         <v>5057</v>
@@ -33672,7 +33672,7 @@
         <v>14116</v>
       </c>
       <c r="R628">
-        <v>342356</v>
+        <v>343309</v>
       </c>
     </row>
     <row r="629">
@@ -33704,22 +33704,22 @@
         <v>404.03</v>
       </c>
       <c r="J629">
-        <v>34</v>
+        <v>34.03</v>
       </c>
       <c r="K629">
-        <v>17.5</v>
+        <v>17.53</v>
       </c>
       <c r="L629">
         <v>363.49</v>
       </c>
       <c r="M629">
-        <v>33624523</v>
+        <v>33624147</v>
       </c>
       <c r="N629">
-        <v>5594389</v>
+        <v>5587278</v>
       </c>
       <c r="O629">
-        <v>2875209</v>
+        <v>2875535</v>
       </c>
       <c r="P629">
         <v>5075</v>
@@ -33728,7 +33728,7 @@
         <v>14137</v>
       </c>
       <c r="R629">
-        <v>348326</v>
+        <v>349983</v>
       </c>
     </row>
     <row r="630">
@@ -33760,22 +33760,22 @@
         <v>397.2</v>
       </c>
       <c r="J630">
-        <v>32.7</v>
+        <v>32.73</v>
       </c>
       <c r="K630">
-        <v>17.47</v>
+        <v>17.5</v>
       </c>
       <c r="L630">
         <v>367.94</v>
       </c>
       <c r="M630">
-        <v>31524073</v>
+        <v>31523698</v>
       </c>
       <c r="N630">
-        <v>5169852</v>
+        <v>5162741</v>
       </c>
       <c r="O630">
-        <v>2630539</v>
+        <v>2630865</v>
       </c>
       <c r="P630">
         <v>5095</v>
@@ -33784,7 +33784,7 @@
         <v>14145</v>
       </c>
       <c r="R630">
-        <v>343789</v>
+        <v>342679</v>
       </c>
     </row>
     <row r="631">
@@ -33816,22 +33816,22 @@
         <v>394.69</v>
       </c>
       <c r="J631">
-        <v>31.7</v>
+        <v>31.73</v>
       </c>
       <c r="K631">
-        <v>16.97</v>
+        <v>16.99</v>
       </c>
       <c r="L631">
         <v>372.8</v>
       </c>
       <c r="M631">
-        <v>29232123</v>
+        <v>29231748</v>
       </c>
       <c r="N631">
-        <v>4851753</v>
+        <v>4844642</v>
       </c>
       <c r="O631">
-        <v>2403701</v>
+        <v>2404027</v>
       </c>
       <c r="P631">
         <v>5104</v>
@@ -33840,7 +33840,7 @@
         <v>14168</v>
       </c>
       <c r="R631">
-        <v>347954</v>
+        <v>349662</v>
       </c>
     </row>
     <row r="632">
@@ -33872,22 +33872,22 @@
         <v>384.2</v>
       </c>
       <c r="J632">
-        <v>31</v>
+        <v>31.03</v>
       </c>
       <c r="K632">
-        <v>16.41</v>
+        <v>16.44</v>
       </c>
       <c r="L632">
         <v>377.47</v>
       </c>
       <c r="M632">
-        <v>27530957</v>
+        <v>27530581</v>
       </c>
       <c r="N632">
-        <v>4642425</v>
+        <v>4635314</v>
       </c>
       <c r="O632">
-        <v>2232430</v>
+        <v>2232756</v>
       </c>
       <c r="P632">
         <v>5140</v>
@@ -33896,7 +33896,7 @@
         <v>14280</v>
       </c>
       <c r="R632">
-        <v>359534</v>
+        <v>357378</v>
       </c>
     </row>
     <row r="633">
@@ -33928,22 +33928,22 @@
         <v>390.91</v>
       </c>
       <c r="J633">
-        <v>30.42</v>
+        <v>30.45</v>
       </c>
       <c r="K633">
-        <v>15.58</v>
+        <v>15.6</v>
       </c>
       <c r="L633">
         <v>382.72</v>
       </c>
       <c r="M633">
-        <v>26101993</v>
+        <v>26101618</v>
       </c>
       <c r="N633">
-        <v>4549365</v>
+        <v>4542254</v>
       </c>
       <c r="O633">
-        <v>2077437</v>
+        <v>2077763</v>
       </c>
       <c r="P633">
         <v>5146</v>
@@ -33952,7 +33952,7 @@
         <v>14264</v>
       </c>
       <c r="R633">
-        <v>361704</v>
+        <v>362881</v>
       </c>
     </row>
     <row r="634">
@@ -33984,22 +33984,22 @@
         <v>404.38</v>
       </c>
       <c r="J634">
-        <v>29.5</v>
+        <v>29.53</v>
       </c>
       <c r="K634">
-        <v>15.36</v>
+        <v>15.35</v>
       </c>
       <c r="L634">
-        <v>387.64</v>
+        <v>387.66</v>
       </c>
       <c r="M634">
-        <v>25075803</v>
+        <v>25074946</v>
       </c>
       <c r="N634">
-        <v>4359415</v>
+        <v>4362093</v>
       </c>
       <c r="O634">
-        <v>1874641</v>
+        <v>1874576</v>
       </c>
       <c r="P634">
         <v>5148</v>
@@ -34008,7 +34008,7 @@
         <v>14269</v>
       </c>
       <c r="R634">
-        <v>366800</v>
+        <v>366384</v>
       </c>
     </row>
     <row r="635">
@@ -34040,22 +34040,22 @@
         <v>406.58</v>
       </c>
       <c r="J635">
-        <v>30.09</v>
+        <v>30.13</v>
       </c>
       <c r="K635">
-        <v>14.99</v>
+        <v>14.98</v>
       </c>
       <c r="L635">
-        <v>392.71</v>
+        <v>392.73</v>
       </c>
       <c r="M635">
-        <v>24553517</v>
+        <v>24552660</v>
       </c>
       <c r="N635">
-        <v>4305271</v>
+        <v>4307949</v>
       </c>
       <c r="O635">
-        <v>1683239</v>
+        <v>1683174</v>
       </c>
       <c r="P635">
         <v>5139</v>
@@ -34064,7 +34064,7 @@
         <v>14301</v>
       </c>
       <c r="R635">
-        <v>366024</v>
+        <v>365642</v>
       </c>
     </row>
     <row r="636">
@@ -34096,22 +34096,22 @@
         <v>417.71</v>
       </c>
       <c r="J636">
-        <v>30.65</v>
+        <v>30.69</v>
       </c>
       <c r="K636">
-        <v>14.47</v>
+        <v>14.46</v>
       </c>
       <c r="L636">
-        <v>397.34</v>
+        <v>397.35</v>
       </c>
       <c r="M636">
-        <v>24205309</v>
+        <v>24204452</v>
       </c>
       <c r="N636">
-        <v>4331037</v>
+        <v>4333715</v>
       </c>
       <c r="O636">
-        <v>1584571</v>
+        <v>1584506</v>
       </c>
       <c r="P636">
         <v>5162</v>
@@ -34120,7 +34120,7 @@
         <v>14337</v>
       </c>
       <c r="R636">
-        <v>367116</v>
+        <v>366244</v>
       </c>
     </row>
     <row r="637">
@@ -34152,22 +34152,22 @@
         <v>422.64</v>
       </c>
       <c r="J637">
-        <v>31.27</v>
+        <v>31.32</v>
       </c>
       <c r="K637">
-        <v>14.14</v>
+        <v>14.13</v>
       </c>
       <c r="L637">
-        <v>401.55</v>
+        <v>401.57</v>
       </c>
       <c r="M637">
-        <v>24250155</v>
+        <v>24249298</v>
       </c>
       <c r="N637">
-        <v>4384916</v>
+        <v>4387594</v>
       </c>
       <c r="O637">
-        <v>1517282</v>
+        <v>1517217</v>
       </c>
       <c r="P637">
         <v>5136</v>
@@ -34176,7 +34176,7 @@
         <v>14364</v>
       </c>
       <c r="R637">
-        <v>372938</v>
+        <v>373987</v>
       </c>
     </row>
     <row r="638">
@@ -34208,22 +34208,22 @@
         <v>430.45</v>
       </c>
       <c r="J638">
-        <v>31.88</v>
+        <v>31.93</v>
       </c>
       <c r="K638">
-        <v>13.82</v>
+        <v>13.81</v>
       </c>
       <c r="L638">
-        <v>406.25</v>
+        <v>406.27</v>
       </c>
       <c r="M638">
-        <v>24731131</v>
+        <v>24730274</v>
       </c>
       <c r="N638">
-        <v>4509277</v>
+        <v>4511955</v>
       </c>
       <c r="O638">
-        <v>1480064</v>
+        <v>1479999</v>
       </c>
       <c r="P638">
         <v>5199</v>
@@ -34232,7 +34232,7 @@
         <v>14411</v>
       </c>
       <c r="R638">
-        <v>378357</v>
+        <v>379392</v>
       </c>
     </row>
     <row r="639">
@@ -34264,22 +34264,22 @@
         <v>437.85</v>
       </c>
       <c r="J639">
-        <v>32.08</v>
+        <v>32.13</v>
       </c>
       <c r="K639">
-        <v>13.65</v>
+        <v>13.64</v>
       </c>
       <c r="L639">
-        <v>410.21</v>
+        <v>410.23</v>
       </c>
       <c r="M639">
-        <v>25135170</v>
+        <v>25134313</v>
       </c>
       <c r="N639">
-        <v>4587600</v>
+        <v>4590278</v>
       </c>
       <c r="O639">
-        <v>1459645</v>
+        <v>1459580</v>
       </c>
       <c r="P639">
         <v>5219</v>
@@ -34288,7 +34288,7 @@
         <v>14439</v>
       </c>
       <c r="R639">
-        <v>387772</v>
+        <v>387843</v>
       </c>
     </row>
     <row r="640">
@@ -34320,22 +34320,22 @@
         <v>441.38</v>
       </c>
       <c r="J640">
-        <v>32.61</v>
+        <v>32.59</v>
       </c>
       <c r="K640">
-        <v>13.62</v>
+        <v>13.61</v>
       </c>
       <c r="L640">
-        <v>413.84</v>
+        <v>413.86</v>
       </c>
       <c r="M640">
-        <v>25570647</v>
+        <v>25569790</v>
       </c>
       <c r="N640">
-        <v>4629292</v>
+        <v>4631970</v>
       </c>
       <c r="O640">
-        <v>1421710</v>
+        <v>1421645</v>
       </c>
       <c r="P640">
         <v>5235</v>
@@ -34344,7 +34344,7 @@
         <v>14453</v>
       </c>
       <c r="R640">
-        <v>394738</v>
+        <v>397990</v>
       </c>
     </row>
     <row r="641">
@@ -34376,22 +34376,22 @@
         <v>435.4</v>
       </c>
       <c r="J641">
-        <v>33.57</v>
+        <v>33.55</v>
       </c>
       <c r="K641">
-        <v>13.72</v>
+        <v>13.71</v>
       </c>
       <c r="L641">
-        <v>416.62</v>
+        <v>416.63</v>
       </c>
       <c r="M641">
-        <v>26298172</v>
+        <v>26297315</v>
       </c>
       <c r="N641">
-        <v>4691317</v>
+        <v>4693995</v>
       </c>
       <c r="O641">
-        <v>1445207</v>
+        <v>1445142</v>
       </c>
       <c r="P641">
         <v>5251</v>
@@ -34400,7 +34400,7 @@
         <v>14478</v>
       </c>
       <c r="R641">
-        <v>403577</v>
+        <v>405401</v>
       </c>
     </row>
     <row r="642">
@@ -34432,22 +34432,22 @@
         <v>438.63</v>
       </c>
       <c r="J642">
-        <v>34.07</v>
+        <v>34.05</v>
       </c>
       <c r="K642">
         <v>13.81</v>
       </c>
       <c r="L642">
-        <v>420.04</v>
+        <v>420.06</v>
       </c>
       <c r="M642">
-        <v>27131137</v>
+        <v>27130280</v>
       </c>
       <c r="N642">
-        <v>4766277</v>
+        <v>4768955</v>
       </c>
       <c r="O642">
-        <v>1475556</v>
+        <v>1475491</v>
       </c>
       <c r="P642">
         <v>5272</v>
@@ -34456,7 +34456,7 @@
         <v>14509</v>
       </c>
       <c r="R642">
-        <v>411117</v>
+        <v>417406</v>
       </c>
     </row>
     <row r="643">
@@ -34488,22 +34488,22 @@
         <v>434.67</v>
       </c>
       <c r="J643">
-        <v>34.32</v>
+        <v>34.3</v>
       </c>
       <c r="K643">
-        <v>13.83</v>
+        <v>13.82</v>
       </c>
       <c r="L643">
-        <v>422.92</v>
+        <v>422.94</v>
       </c>
       <c r="M643">
-        <v>27877878</v>
+        <v>27877021</v>
       </c>
       <c r="N643">
-        <v>4857351</v>
+        <v>4860029</v>
       </c>
       <c r="O643">
-        <v>1504960</v>
+        <v>1504895</v>
       </c>
       <c r="P643">
         <v>5294</v>
@@ -34512,7 +34512,7 @@
         <v>14565</v>
       </c>
       <c r="R643">
-        <v>418667</v>
+        <v>423949</v>
       </c>
     </row>
     <row r="644">
@@ -34544,22 +34544,22 @@
         <v>423.76</v>
       </c>
       <c r="J644">
-        <v>34.53</v>
+        <v>34.51</v>
       </c>
       <c r="K644">
-        <v>13.97</v>
+        <v>13.96</v>
       </c>
       <c r="L644">
-        <v>425.6</v>
+        <v>425.61</v>
       </c>
       <c r="M644">
-        <v>28931011</v>
+        <v>28930154</v>
       </c>
       <c r="N644">
-        <v>4957035</v>
+        <v>4959713</v>
       </c>
       <c r="O644">
-        <v>1556991</v>
+        <v>1556926</v>
       </c>
       <c r="P644">
         <v>5303</v>
@@ -34568,7 +34568,7 @@
         <v>14589</v>
       </c>
       <c r="R644">
-        <v>417761</v>
+        <v>422871</v>
       </c>
     </row>
     <row r="645">
@@ -34600,22 +34600,22 @@
         <v>433.94</v>
       </c>
       <c r="J645">
-        <v>34.76</v>
+        <v>34.74</v>
       </c>
       <c r="K645">
-        <v>14.05</v>
+        <v>14.04</v>
       </c>
       <c r="L645">
-        <v>428.95</v>
+        <v>428.96</v>
       </c>
       <c r="M645">
-        <v>29723007</v>
+        <v>29722150</v>
       </c>
       <c r="N645">
-        <v>5024060</v>
+        <v>5026738</v>
       </c>
       <c r="O645">
-        <v>1594594</v>
+        <v>1594529</v>
       </c>
       <c r="P645">
         <v>5324</v>
@@ -34624,7 +34624,7 @@
         <v>14603</v>
       </c>
       <c r="R645">
-        <v>420853</v>
+        <v>428148</v>
       </c>
     </row>
     <row r="646">
@@ -34632,7 +34632,7 @@
         <v>45199</v>
       </c>
       <c r="B646">
-        <v>753093</v>
+        <v>753224</v>
       </c>
       <c r="C646">
         <v>1567.9</v>
@@ -34644,7 +34644,7 @@
         <v>141157</v>
       </c>
       <c r="F646">
-        <v>6549102</v>
+        <v>6550045</v>
       </c>
       <c r="G646">
         <v>5497178</v>
@@ -34656,7 +34656,7 @@
         <v>445.04</v>
       </c>
       <c r="J646">
-        <v>35.27</v>
+        <v>35.25</v>
       </c>
       <c r="K646">
         <v>14.17</v>
@@ -34680,7 +34680,7 @@
         <v>14653</v>
       </c>
       <c r="R646">
-        <v>429575</v>
+        <v>436947</v>
       </c>
     </row>
     <row r="647">
@@ -34712,7 +34712,7 @@
         <v>446.34</v>
       </c>
       <c r="J647">
-        <v>35.99</v>
+        <v>35.97</v>
       </c>
       <c r="K647">
         <v>14.32</v>
@@ -34736,7 +34736,7 @@
         <v>14693</v>
       </c>
       <c r="R647">
-        <v>440206</v>
+        <v>444351</v>
       </c>
     </row>
     <row r="648">
@@ -34768,7 +34768,7 @@
         <v>451.54</v>
       </c>
       <c r="J648">
-        <v>36.24</v>
+        <v>36.22</v>
       </c>
       <c r="K648">
         <v>14.43</v>
@@ -34792,7 +34792,7 @@
         <v>14728</v>
       </c>
       <c r="R648">
-        <v>445839</v>
+        <v>453531</v>
       </c>
     </row>
     <row r="649">
@@ -34824,7 +34824,7 @@
         <v>452.63</v>
       </c>
       <c r="J649">
-        <v>36.48</v>
+        <v>36.46</v>
       </c>
       <c r="K649">
         <v>14.62</v>
@@ -34848,7 +34848,7 @@
         <v>14763</v>
       </c>
       <c r="R649">
-        <v>446422</v>
+        <v>456086</v>
       </c>
     </row>
     <row r="650">
@@ -34880,7 +34880,7 @@
         <v>459.4</v>
       </c>
       <c r="J650">
-        <v>36.64</v>
+        <v>36.62</v>
       </c>
       <c r="K650">
         <v>14.75</v>
@@ -34904,7 +34904,7 @@
         <v>14786</v>
       </c>
       <c r="R650">
-        <v>442338</v>
+        <v>449421</v>
       </c>
     </row>
     <row r="651">
@@ -34936,7 +34936,7 @@
         <v>459.63</v>
       </c>
       <c r="J651">
-        <v>36.93</v>
+        <v>36.91</v>
       </c>
       <c r="K651">
         <v>14.85</v>
@@ -34960,7 +34960,7 @@
         <v>14835</v>
       </c>
       <c r="R651">
-        <v>445503</v>
+        <v>460527</v>
       </c>
     </row>
     <row r="652">
@@ -35016,7 +35016,7 @@
         <v>14890</v>
       </c>
       <c r="R652">
-        <v>450173</v>
+        <v>455814</v>
       </c>
     </row>
     <row r="653">
@@ -35072,7 +35072,7 @@
         <v>14877</v>
       </c>
       <c r="R653">
-        <v>450938</v>
+        <v>460896</v>
       </c>
     </row>
     <row r="654">
@@ -35128,7 +35128,7 @@
         <v>14905</v>
       </c>
       <c r="R654">
-        <v>450559</v>
+        <v>458902</v>
       </c>
     </row>
     <row r="655">
@@ -35184,7 +35184,7 @@
         <v>14915</v>
       </c>
       <c r="R655">
-        <v>452201</v>
+        <v>454153</v>
       </c>
     </row>
     <row r="656">
@@ -35192,28 +35192,28 @@
         <v>45504</v>
       </c>
       <c r="B656">
-        <v>1065996</v>
+        <v>1065985</v>
       </c>
       <c r="C656">
         <v>1901</v>
       </c>
       <c r="D656">
-        <v>522125</v>
+        <v>522126</v>
       </c>
       <c r="E656">
-        <v>181829</v>
+        <v>181830</v>
       </c>
       <c r="F656">
-        <v>8487876</v>
+        <v>8487327</v>
       </c>
       <c r="G656">
-        <v>7347349</v>
+        <v>7347371</v>
       </c>
       <c r="H656">
-        <v>3163985</v>
+        <v>3164825</v>
       </c>
       <c r="I656">
-        <v>438.16</v>
+        <v>438.26</v>
       </c>
       <c r="J656">
         <v>38.01</v>
@@ -35222,16 +35222,16 @@
         <v>15.18</v>
       </c>
       <c r="L656">
-        <v>450.23</v>
+        <v>450.24</v>
       </c>
       <c r="M656">
-        <v>35307517</v>
+        <v>35308357</v>
       </c>
       <c r="N656">
-        <v>5258456</v>
+        <v>5258457</v>
       </c>
       <c r="O656">
-        <v>1978634</v>
+        <v>1978635</v>
       </c>
       <c r="P656">
         <v>5444</v>
@@ -35240,7 +35240,7 @@
         <v>14946</v>
       </c>
       <c r="R656">
-        <v>456588</v>
+        <v>464102</v>
       </c>
     </row>
     <row r="657">
@@ -35248,28 +35248,28 @@
         <v>45535</v>
       </c>
       <c r="B657">
-        <v>848460</v>
+        <v>848530</v>
       </c>
       <c r="C657">
         <v>1817.9</v>
       </c>
       <c r="D657">
-        <v>408600</v>
+        <v>408601</v>
       </c>
       <c r="E657">
-        <v>164528</v>
+        <v>164530</v>
       </c>
       <c r="F657">
-        <v>7586180</v>
+        <v>7586087</v>
       </c>
       <c r="G657">
-        <v>6466287</v>
+        <v>6466303</v>
       </c>
       <c r="H657">
-        <v>2800253</v>
+        <v>2800932</v>
       </c>
       <c r="I657">
-        <v>440.91</v>
+        <v>441.01</v>
       </c>
       <c r="J657">
         <v>38.03</v>
@@ -35278,16 +35278,16 @@
         <v>15.21</v>
       </c>
       <c r="L657">
-        <v>450.82</v>
+        <v>450.84</v>
       </c>
       <c r="M657">
-        <v>35299907</v>
+        <v>35301426</v>
       </c>
       <c r="N657">
-        <v>5241206</v>
+        <v>5241208</v>
       </c>
       <c r="O657">
-        <v>1987040</v>
+        <v>1987043</v>
       </c>
       <c r="P657">
         <v>5453</v>
@@ -35296,7 +35296,7 @@
         <v>14973</v>
       </c>
       <c r="R657">
-        <v>458308</v>
+        <v>469078</v>
       </c>
     </row>
     <row r="658">
@@ -35304,28 +35304,28 @@
         <v>45565</v>
       </c>
       <c r="B658">
-        <v>792151</v>
+        <v>792023</v>
       </c>
       <c r="C658">
         <v>1615.9</v>
       </c>
       <c r="D658">
-        <v>351269</v>
+        <v>351268</v>
       </c>
       <c r="E658">
-        <v>169526</v>
+        <v>169527</v>
       </c>
       <c r="F658">
-        <v>7613775</v>
+        <v>7613230</v>
       </c>
       <c r="G658">
-        <v>6230313</v>
+        <v>6230312</v>
       </c>
       <c r="H658">
-        <v>2752870</v>
+        <v>2753546</v>
       </c>
       <c r="I658">
-        <v>450.94</v>
+        <v>451.05</v>
       </c>
       <c r="J658">
         <v>38.63</v>
@@ -35334,16 +35334,16 @@
         <v>15.3</v>
       </c>
       <c r="L658">
-        <v>451.22</v>
+        <v>451.25</v>
       </c>
       <c r="M658">
-        <v>35651697</v>
+        <v>35653893</v>
       </c>
       <c r="N658">
-        <v>5255969</v>
+        <v>5255970</v>
       </c>
       <c r="O658">
-        <v>2015409</v>
+        <v>2015413</v>
       </c>
       <c r="P658">
         <v>5468</v>
@@ -35352,7 +35352,7 @@
         <v>14986</v>
       </c>
       <c r="R658">
-        <v>466887</v>
+        <v>470037</v>
       </c>
     </row>
     <row r="659">
@@ -35390,16 +35390,16 @@
         <v>15.2</v>
       </c>
       <c r="L659">
-        <v>452.16</v>
+        <v>452.18</v>
       </c>
       <c r="M659">
-        <v>35640470</v>
+        <v>35642665</v>
       </c>
       <c r="N659">
-        <v>5281067</v>
+        <v>5281068</v>
       </c>
       <c r="O659">
-        <v>2010970</v>
+        <v>2010974</v>
       </c>
       <c r="P659">
         <v>5484</v>
@@ -35408,7 +35408,7 @@
         <v>15012</v>
       </c>
       <c r="R659">
-        <v>468844</v>
+        <v>474646</v>
       </c>
     </row>
     <row r="660">
@@ -35446,16 +35446,16 @@
         <v>15.25</v>
       </c>
       <c r="L660">
-        <v>452.81</v>
+        <v>452.83</v>
       </c>
       <c r="M660">
-        <v>35645428</v>
+        <v>35647623</v>
       </c>
       <c r="N660">
-        <v>5256639</v>
+        <v>5256640</v>
       </c>
       <c r="O660">
-        <v>2015370</v>
+        <v>2015374</v>
       </c>
       <c r="P660">
         <v>5493</v>
@@ -35464,7 +35464,7 @@
         <v>15022</v>
       </c>
       <c r="R660">
-        <v>469357</v>
+        <v>472134</v>
       </c>
     </row>
     <row r="661">
@@ -35502,16 +35502,16 @@
         <v>15.27</v>
       </c>
       <c r="L661">
-        <v>453.87</v>
+        <v>453.89</v>
       </c>
       <c r="M661">
-        <v>36309115</v>
+        <v>36311311</v>
       </c>
       <c r="N661">
-        <v>5333072</v>
+        <v>5333073</v>
       </c>
       <c r="O661">
-        <v>2050418</v>
+        <v>2050422</v>
       </c>
       <c r="P661">
         <v>5512</v>
@@ -35520,7 +35520,7 @@
         <v>15036</v>
       </c>
       <c r="R661">
-        <v>470075</v>
+        <v>466925</v>
       </c>
     </row>
     <row r="662">
@@ -35528,7 +35528,7 @@
         <v>45688</v>
       </c>
       <c r="B662">
-        <v>1230480</v>
+        <v>1230263</v>
       </c>
       <c r="C662">
         <v>2144.7</v>
@@ -35540,7 +35540,7 @@
         <v>180879</v>
       </c>
       <c r="F662">
-        <v>9272720</v>
+        <v>9270888</v>
       </c>
       <c r="G662">
         <v>7923862</v>
@@ -35558,16 +35558,16 @@
         <v>15.17</v>
       </c>
       <c r="L662">
-        <v>454.8</v>
+        <v>454.83</v>
       </c>
       <c r="M662">
-        <v>36184973</v>
+        <v>36187169</v>
       </c>
       <c r="N662">
-        <v>5341620</v>
+        <v>5341621</v>
       </c>
       <c r="O662">
-        <v>2046794</v>
+        <v>2046798</v>
       </c>
       <c r="P662">
         <v>5524</v>
@@ -35576,7 +35576,7 @@
         <v>15053</v>
       </c>
       <c r="R662">
-        <v>471070</v>
+        <v>468212</v>
       </c>
     </row>
     <row r="663">
@@ -35584,7 +35584,7 @@
         <v>45716</v>
       </c>
       <c r="B663">
-        <v>905084</v>
+        <v>904887</v>
       </c>
       <c r="C663">
         <v>2141</v>
@@ -35596,7 +35596,7 @@
         <v>165056</v>
       </c>
       <c r="F663">
-        <v>8661513</v>
+        <v>8657563</v>
       </c>
       <c r="G663">
         <v>7509946</v>
@@ -35614,16 +35614,16 @@
         <v>15.21</v>
       </c>
       <c r="L663">
-        <v>455.91</v>
+        <v>455.94</v>
       </c>
       <c r="M663">
-        <v>36326076</v>
+        <v>36328272</v>
       </c>
       <c r="N663">
-        <v>5334786</v>
+        <v>5334787</v>
       </c>
       <c r="O663">
-        <v>2054381</v>
+        <v>2054385</v>
       </c>
       <c r="P663">
         <v>5514</v>
@@ -35632,7 +35632,7 @@
         <v>15071</v>
       </c>
       <c r="R663">
-        <v>474386</v>
+        <v>467885</v>
       </c>
     </row>
     <row r="664">
@@ -35640,7 +35640,7 @@
         <v>45747</v>
       </c>
       <c r="B664">
-        <v>890794</v>
+        <v>890716</v>
       </c>
       <c r="C664">
         <v>2065.1</v>
@@ -35652,7 +35652,7 @@
         <v>188320</v>
       </c>
       <c r="F664">
-        <v>9620921</v>
+        <v>9621697</v>
       </c>
       <c r="G664">
         <v>8149650</v>
@@ -35661,7 +35661,7 @@
         <v>3743494</v>
       </c>
       <c r="I664">
-        <v>467.75</v>
+        <v>467.76</v>
       </c>
       <c r="J664">
         <v>39.55</v>
@@ -35670,16 +35670,16 @@
         <v>15.3</v>
       </c>
       <c r="L664">
-        <v>457.08</v>
+        <v>457.11</v>
       </c>
       <c r="M664">
-        <v>36781593</v>
+        <v>36783789</v>
       </c>
       <c r="N664">
-        <v>5357361</v>
+        <v>5357362</v>
       </c>
       <c r="O664">
-        <v>2078927</v>
+        <v>2078931</v>
       </c>
       <c r="P664">
         <v>5515</v>
@@ -35688,35 +35688,169 @@
         <v>15087</v>
       </c>
       <c r="R664">
-        <v>474713</v>
+        <v>470613</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" s="2">
         <v>45777</v>
       </c>
+      <c r="B665">
+        <v>943634</v>
+      </c>
       <c r="C665">
         <v>1877</v>
       </c>
+      <c r="D665">
+        <v>401311</v>
+      </c>
+      <c r="E665">
+        <v>188757</v>
+      </c>
+      <c r="F665">
+        <v>7912222</v>
+      </c>
+      <c r="G665">
+        <v>6972911</v>
+      </c>
+      <c r="H665">
+        <v>3204879</v>
+      </c>
+      <c r="I665">
+        <v>468.53</v>
+      </c>
+      <c r="J665">
+        <v>39.43</v>
+      </c>
+      <c r="K665">
+        <v>15.22</v>
+      </c>
+      <c r="L665">
+        <v>458.19</v>
+      </c>
+      <c r="M665">
+        <v>36812035</v>
+      </c>
+      <c r="N665">
+        <v>5375536</v>
+      </c>
+      <c r="O665">
+        <v>2082073</v>
+      </c>
       <c r="P665">
-        <v>5518</v>
+        <v>5526</v>
       </c>
       <c r="Q665">
-        <v>15098</v>
+        <v>15114</v>
       </c>
       <c r="R665">
-        <v>475961</v>
+        <v>472575</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" s="2">
         <v>45808</v>
       </c>
+      <c r="B666">
+        <v>896012</v>
+      </c>
+      <c r="C666">
+        <v>1760.6</v>
+      </c>
+      <c r="D666">
+        <v>371424</v>
+      </c>
+      <c r="E666">
+        <v>174005</v>
+      </c>
+      <c r="F666">
+        <v>7225145</v>
+      </c>
+      <c r="G666">
+        <v>6143233</v>
+      </c>
+      <c r="H666">
+        <v>2799930</v>
+      </c>
+      <c r="I666">
+        <v>465.32</v>
+      </c>
+      <c r="J666">
+        <v>39.71</v>
+      </c>
+      <c r="K666">
+        <v>15.27</v>
+      </c>
+      <c r="L666">
+        <v>458.9</v>
+      </c>
+      <c r="M666">
+        <v>36918224</v>
+      </c>
+      <c r="N666">
+        <v>5367988</v>
+      </c>
+      <c r="O666">
+        <v>2087568</v>
+      </c>
       <c r="P666">
-        <v>5518</v>
+        <v>5533</v>
       </c>
       <c r="Q666">
-        <v>15119</v>
+        <v>15139</v>
+      </c>
+      <c r="R666">
+        <v>472529</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="2">
+        <v>45838</v>
+      </c>
+      <c r="B667">
+        <v>1035435</v>
+      </c>
+      <c r="D667">
+        <v>459016</v>
+      </c>
+      <c r="E667">
+        <v>180279</v>
+      </c>
+      <c r="F667">
+        <v>8494020</v>
+      </c>
+      <c r="G667">
+        <v>6941309</v>
+      </c>
+      <c r="H667">
+        <v>3102992</v>
+      </c>
+      <c r="I667">
+        <v>455.84</v>
+      </c>
+      <c r="J667">
+        <v>39.53</v>
+      </c>
+      <c r="K667">
+        <v>15.29</v>
+      </c>
+      <c r="L667">
+        <v>459.72</v>
+      </c>
+      <c r="M667">
+        <v>37397811</v>
+      </c>
+      <c r="N667">
+        <v>5421447</v>
+      </c>
+      <c r="O667">
+        <v>2108293</v>
+      </c>
+      <c r="P667">
+        <v>5580</v>
+      </c>
+      <c r="Q667">
+        <v>15172</v>
       </c>
     </row>
   </sheetData>

--- a/data/monthly_state_ui.xlsx
+++ b/data/monthly_state_ui.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R667"/>
+  <dimension ref="A1:R668"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -35192,7 +35192,7 @@
         <v>45504</v>
       </c>
       <c r="B656">
-        <v>1065985</v>
+        <v>1065311</v>
       </c>
       <c r="C656">
         <v>1901</v>
@@ -35248,7 +35248,7 @@
         <v>45535</v>
       </c>
       <c r="B657">
-        <v>848530</v>
+        <v>847941</v>
       </c>
       <c r="C657">
         <v>1817.9</v>
@@ -35304,7 +35304,7 @@
         <v>45565</v>
       </c>
       <c r="B658">
-        <v>792023</v>
+        <v>791479</v>
       </c>
       <c r="C658">
         <v>1615.9</v>
@@ -35360,7 +35360,7 @@
         <v>45596</v>
       </c>
       <c r="B659">
-        <v>976719</v>
+        <v>976085</v>
       </c>
       <c r="C659">
         <v>1620.6</v>
@@ -35416,7 +35416,7 @@
         <v>45626</v>
       </c>
       <c r="B660">
-        <v>940793</v>
+        <v>939443</v>
       </c>
       <c r="C660">
         <v>1681.3</v>
@@ -35472,7 +35472,7 @@
         <v>45657</v>
       </c>
       <c r="B661">
-        <v>1286671</v>
+        <v>1284695</v>
       </c>
       <c r="C661">
         <v>1926.7</v>
@@ -35528,7 +35528,7 @@
         <v>45688</v>
       </c>
       <c r="B662">
-        <v>1230263</v>
+        <v>1229040</v>
       </c>
       <c r="C662">
         <v>2144.7</v>
@@ -35584,7 +35584,7 @@
         <v>45716</v>
       </c>
       <c r="B663">
-        <v>904887</v>
+        <v>903834</v>
       </c>
       <c r="C663">
         <v>2141</v>
@@ -35640,7 +35640,7 @@
         <v>45747</v>
       </c>
       <c r="B664">
-        <v>890716</v>
+        <v>889620</v>
       </c>
       <c r="C664">
         <v>2065.1</v>
@@ -35696,7 +35696,7 @@
         <v>45777</v>
       </c>
       <c r="B665">
-        <v>943634</v>
+        <v>942880</v>
       </c>
       <c r="C665">
         <v>1877</v>
@@ -35708,7 +35708,7 @@
         <v>188757</v>
       </c>
       <c r="F665">
-        <v>7912222</v>
+        <v>7912629</v>
       </c>
       <c r="G665">
         <v>6972911</v>
@@ -35744,7 +35744,7 @@
         <v>15114</v>
       </c>
       <c r="R665">
-        <v>472575</v>
+        <v>475304</v>
       </c>
     </row>
     <row r="666">
@@ -35752,28 +35752,28 @@
         <v>45808</v>
       </c>
       <c r="B666">
-        <v>896012</v>
+        <v>894787</v>
       </c>
       <c r="C666">
         <v>1760.6</v>
       </c>
       <c r="D666">
-        <v>371424</v>
+        <v>371539</v>
       </c>
       <c r="E666">
-        <v>174005</v>
+        <v>173824</v>
       </c>
       <c r="F666">
-        <v>7225145</v>
+        <v>7225007</v>
       </c>
       <c r="G666">
-        <v>6143233</v>
+        <v>6139864</v>
       </c>
       <c r="H666">
-        <v>2799930</v>
+        <v>2798144</v>
       </c>
       <c r="I666">
-        <v>465.32</v>
+        <v>465.28</v>
       </c>
       <c r="J666">
         <v>39.71</v>
@@ -35785,22 +35785,22 @@
         <v>458.9</v>
       </c>
       <c r="M666">
-        <v>36918224</v>
+        <v>36916439</v>
       </c>
       <c r="N666">
-        <v>5367988</v>
+        <v>5368103</v>
       </c>
       <c r="O666">
-        <v>2087568</v>
+        <v>2087387</v>
       </c>
       <c r="P666">
-        <v>5533</v>
+        <v>5515</v>
       </c>
       <c r="Q666">
-        <v>15139</v>
+        <v>15101</v>
       </c>
       <c r="R666">
-        <v>472529</v>
+        <v>474694</v>
       </c>
     </row>
     <row r="667">
@@ -35808,25 +35808,28 @@
         <v>45838</v>
       </c>
       <c r="B667">
-        <v>1035435</v>
+        <v>1032107</v>
+      </c>
+      <c r="C667">
+        <v>1479.3</v>
       </c>
       <c r="D667">
-        <v>459016</v>
+        <v>460026</v>
       </c>
       <c r="E667">
-        <v>180279</v>
+        <v>180267</v>
       </c>
       <c r="F667">
-        <v>8494020</v>
+        <v>8502534</v>
       </c>
       <c r="G667">
-        <v>6941309</v>
+        <v>6959332</v>
       </c>
       <c r="H667">
-        <v>3102992</v>
+        <v>3111116</v>
       </c>
       <c r="I667">
-        <v>455.84</v>
+        <v>455.85</v>
       </c>
       <c r="J667">
         <v>39.53</v>
@@ -35838,19 +35841,60 @@
         <v>459.72</v>
       </c>
       <c r="M667">
-        <v>37397811</v>
+        <v>37404150</v>
       </c>
       <c r="N667">
-        <v>5421447</v>
+        <v>5422572</v>
       </c>
       <c r="O667">
-        <v>2108293</v>
+        <v>2108100</v>
       </c>
       <c r="P667">
-        <v>5580</v>
+        <v>5525</v>
       </c>
       <c r="Q667">
-        <v>15172</v>
+        <v>15111</v>
+      </c>
+      <c r="R667">
+        <v>476993</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="2">
+        <v>45869</v>
+      </c>
+      <c r="D668">
+        <v>7515</v>
+      </c>
+      <c r="E668">
+        <v>1472</v>
+      </c>
+      <c r="H668">
+        <v>18748</v>
+      </c>
+      <c r="J668">
+        <v>36.09</v>
+      </c>
+      <c r="K668">
+        <v>15.41</v>
+      </c>
+      <c r="L668">
+        <v>461.53</v>
+      </c>
+      <c r="M668">
+        <v>34258073</v>
+      </c>
+      <c r="N668">
+        <v>4907961</v>
+      </c>
+      <c r="O668">
+        <v>1927742</v>
+      </c>
+      <c r="P668">
+        <v>5530</v>
+      </c>
+      <c r="Q668">
+        <v>15108</v>
       </c>
     </row>
   </sheetData>

--- a/data/monthly_state_ui.xlsx
+++ b/data/monthly_state_ui.xlsx
@@ -35481,7 +35481,7 @@
         <v>541872</v>
       </c>
       <c r="E661">
-        <v>194341</v>
+        <v>194486</v>
       </c>
       <c r="F661">
         <v>9204452</v>
@@ -35496,7 +35496,7 @@
         <v>463.85</v>
       </c>
       <c r="J661">
-        <v>39.38</v>
+        <v>39.39</v>
       </c>
       <c r="K661">
         <v>15.27</v>
@@ -35511,7 +35511,7 @@
         <v>5333073</v>
       </c>
       <c r="O661">
-        <v>2050422</v>
+        <v>2050567</v>
       </c>
       <c r="P661">
         <v>5512</v>
@@ -35537,7 +35537,7 @@
         <v>689057</v>
       </c>
       <c r="E662">
-        <v>180879</v>
+        <v>181369</v>
       </c>
       <c r="F662">
         <v>9270888</v>
@@ -35552,7 +35552,7 @@
         <v>469.31</v>
       </c>
       <c r="J662">
-        <v>38.92</v>
+        <v>38.94</v>
       </c>
       <c r="K662">
         <v>15.17</v>
@@ -35567,7 +35567,7 @@
         <v>5341621</v>
       </c>
       <c r="O662">
-        <v>2046798</v>
+        <v>2047433</v>
       </c>
       <c r="P662">
         <v>5524</v>
@@ -35593,7 +35593,7 @@
         <v>483723</v>
       </c>
       <c r="E663">
-        <v>165056</v>
+        <v>165517</v>
       </c>
       <c r="F663">
         <v>8657563</v>
@@ -35608,7 +35608,7 @@
         <v>471.52</v>
       </c>
       <c r="J663">
-        <v>39.2</v>
+        <v>39.22</v>
       </c>
       <c r="K663">
         <v>15.21</v>
@@ -35623,7 +35623,7 @@
         <v>5334787</v>
       </c>
       <c r="O663">
-        <v>2054385</v>
+        <v>2055481</v>
       </c>
       <c r="P663">
         <v>5514</v>
@@ -35649,7 +35649,7 @@
         <v>431634</v>
       </c>
       <c r="E664">
-        <v>188320</v>
+        <v>188778</v>
       </c>
       <c r="F664">
         <v>9621697</v>
@@ -35664,7 +35664,7 @@
         <v>467.76</v>
       </c>
       <c r="J664">
-        <v>39.55</v>
+        <v>39.58</v>
       </c>
       <c r="K664">
         <v>15.3</v>
@@ -35679,7 +35679,7 @@
         <v>5357362</v>
       </c>
       <c r="O664">
-        <v>2078931</v>
+        <v>2080485</v>
       </c>
       <c r="P664">
         <v>5515</v>
@@ -35696,31 +35696,31 @@
         <v>45777</v>
       </c>
       <c r="B665">
-        <v>942880</v>
+        <v>942921</v>
       </c>
       <c r="C665">
         <v>1877</v>
       </c>
       <c r="D665">
-        <v>401311</v>
+        <v>401308</v>
       </c>
       <c r="E665">
-        <v>188757</v>
+        <v>189319</v>
       </c>
       <c r="F665">
-        <v>7912629</v>
+        <v>7912998</v>
       </c>
       <c r="G665">
-        <v>6972911</v>
+        <v>6972902</v>
       </c>
       <c r="H665">
-        <v>3204879</v>
+        <v>3204874</v>
       </c>
       <c r="I665">
         <v>468.53</v>
       </c>
       <c r="J665">
-        <v>39.43</v>
+        <v>39.47</v>
       </c>
       <c r="K665">
         <v>15.22</v>
@@ -35729,13 +35729,13 @@
         <v>458.19</v>
       </c>
       <c r="M665">
-        <v>36812035</v>
+        <v>36812030</v>
       </c>
       <c r="N665">
-        <v>5375536</v>
+        <v>5375533</v>
       </c>
       <c r="O665">
-        <v>2082073</v>
+        <v>2084189</v>
       </c>
       <c r="P665">
         <v>5526</v>
@@ -35761,10 +35761,10 @@
         <v>371539</v>
       </c>
       <c r="E666">
-        <v>173824</v>
+        <v>174208</v>
       </c>
       <c r="F666">
-        <v>7225007</v>
+        <v>7224989</v>
       </c>
       <c r="G666">
         <v>6139864</v>
@@ -35776,7 +35776,7 @@
         <v>465.28</v>
       </c>
       <c r="J666">
-        <v>39.71</v>
+        <v>39.76</v>
       </c>
       <c r="K666">
         <v>15.27</v>
@@ -35785,13 +35785,13 @@
         <v>458.9</v>
       </c>
       <c r="M666">
-        <v>36916439</v>
+        <v>36916434</v>
       </c>
       <c r="N666">
-        <v>5368103</v>
+        <v>5368100</v>
       </c>
       <c r="O666">
-        <v>2087387</v>
+        <v>2089887</v>
       </c>
       <c r="P666">
         <v>5515</v>
@@ -35808,46 +35808,46 @@
         <v>45838</v>
       </c>
       <c r="B667">
-        <v>1032107</v>
+        <v>1032546</v>
       </c>
       <c r="C667">
-        <v>1479.3</v>
+        <v>1860.9</v>
       </c>
       <c r="D667">
-        <v>460026</v>
+        <v>457397</v>
       </c>
       <c r="E667">
-        <v>180267</v>
+        <v>178940</v>
       </c>
       <c r="F667">
-        <v>8502534</v>
+        <v>8573393</v>
       </c>
       <c r="G667">
-        <v>6959332</v>
+        <v>6954177</v>
       </c>
       <c r="H667">
-        <v>3111116</v>
+        <v>3103168</v>
       </c>
       <c r="I667">
-        <v>455.85</v>
+        <v>455.59</v>
       </c>
       <c r="J667">
-        <v>39.53</v>
+        <v>39.55</v>
       </c>
       <c r="K667">
-        <v>15.29</v>
+        <v>15.3</v>
       </c>
       <c r="L667">
-        <v>459.72</v>
+        <v>459.7</v>
       </c>
       <c r="M667">
-        <v>37404150</v>
+        <v>37396197</v>
       </c>
       <c r="N667">
-        <v>5422572</v>
+        <v>5419940</v>
       </c>
       <c r="O667">
-        <v>2108100</v>
+        <v>2109273</v>
       </c>
       <c r="P667">
         <v>5525</v>
@@ -35863,32 +35863,47 @@
       <c r="A668" s="2">
         <v>45869</v>
       </c>
+      <c r="B668">
+        <v>985989</v>
+      </c>
+      <c r="C668">
+        <v>2004.2</v>
+      </c>
       <c r="D668">
-        <v>7515</v>
+        <v>508090</v>
       </c>
       <c r="E668">
-        <v>1472</v>
+        <v>182815</v>
+      </c>
+      <c r="F668">
+        <v>8405033</v>
+      </c>
+      <c r="G668">
+        <v>7256308</v>
       </c>
       <c r="H668">
-        <v>18748</v>
+        <v>3266414</v>
+      </c>
+      <c r="I668">
+        <v>458.42</v>
       </c>
       <c r="J668">
-        <v>36.09</v>
+        <v>39.51</v>
       </c>
       <c r="K668">
-        <v>15.41</v>
+        <v>15.32</v>
       </c>
       <c r="L668">
-        <v>461.53</v>
+        <v>461.49</v>
       </c>
       <c r="M668">
-        <v>34258073</v>
+        <v>37497786</v>
       </c>
       <c r="N668">
-        <v>4907961</v>
+        <v>5405904</v>
       </c>
       <c r="O668">
-        <v>1927742</v>
+        <v>2110258</v>
       </c>
       <c r="P668">
         <v>5530</v>

--- a/data/monthly_state_ui.xlsx
+++ b/data/monthly_state_ui.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R668"/>
+  <dimension ref="A1:R669"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -35528,7 +35528,7 @@
         <v>45688</v>
       </c>
       <c r="B662">
-        <v>1229040</v>
+        <v>1229039</v>
       </c>
       <c r="C662">
         <v>2144.7</v>
@@ -35540,7 +35540,7 @@
         <v>181369</v>
       </c>
       <c r="F662">
-        <v>9270888</v>
+        <v>9270872</v>
       </c>
       <c r="G662">
         <v>7923862</v>
@@ -35596,7 +35596,7 @@
         <v>165517</v>
       </c>
       <c r="F663">
-        <v>8657563</v>
+        <v>8657553</v>
       </c>
       <c r="G663">
         <v>7509946</v>
@@ -35640,7 +35640,7 @@
         <v>45747</v>
       </c>
       <c r="B664">
-        <v>889620</v>
+        <v>889619</v>
       </c>
       <c r="C664">
         <v>2065.1</v>
@@ -35652,7 +35652,7 @@
         <v>188778</v>
       </c>
       <c r="F664">
-        <v>9621697</v>
+        <v>9621688</v>
       </c>
       <c r="G664">
         <v>8149650</v>
@@ -35708,7 +35708,7 @@
         <v>189319</v>
       </c>
       <c r="F665">
-        <v>7912998</v>
+        <v>7912994</v>
       </c>
       <c r="G665">
         <v>6972902</v>
@@ -35752,7 +35752,7 @@
         <v>45808</v>
       </c>
       <c r="B666">
-        <v>894787</v>
+        <v>894785</v>
       </c>
       <c r="C666">
         <v>1760.6</v>
@@ -35764,7 +35764,7 @@
         <v>174208</v>
       </c>
       <c r="F666">
-        <v>7224989</v>
+        <v>7224983</v>
       </c>
       <c r="G666">
         <v>6139864</v>
@@ -35800,7 +35800,7 @@
         <v>15101</v>
       </c>
       <c r="R666">
-        <v>474694</v>
+        <v>475285</v>
       </c>
     </row>
     <row r="667">
@@ -35808,7 +35808,7 @@
         <v>45838</v>
       </c>
       <c r="B667">
-        <v>1032546</v>
+        <v>1032545</v>
       </c>
       <c r="C667">
         <v>1860.9</v>
@@ -35820,7 +35820,7 @@
         <v>178940</v>
       </c>
       <c r="F667">
-        <v>8573393</v>
+        <v>8573388</v>
       </c>
       <c r="G667">
         <v>6954177</v>
@@ -35850,13 +35850,13 @@
         <v>2109273</v>
       </c>
       <c r="P667">
-        <v>5525</v>
+        <v>5511</v>
       </c>
       <c r="Q667">
-        <v>15111</v>
+        <v>15128</v>
       </c>
       <c r="R667">
-        <v>476993</v>
+        <v>476567</v>
       </c>
     </row>
     <row r="668">
@@ -35864,28 +35864,28 @@
         <v>45869</v>
       </c>
       <c r="B668">
-        <v>985989</v>
+        <v>982388</v>
       </c>
       <c r="C668">
         <v>2004.2</v>
       </c>
       <c r="D668">
-        <v>508090</v>
+        <v>507983</v>
       </c>
       <c r="E668">
-        <v>182815</v>
+        <v>182814</v>
       </c>
       <c r="F668">
-        <v>8405033</v>
+        <v>8405149</v>
       </c>
       <c r="G668">
-        <v>7256308</v>
+        <v>7257173</v>
       </c>
       <c r="H668">
-        <v>3266414</v>
+        <v>3266454</v>
       </c>
       <c r="I668">
-        <v>458.42</v>
+        <v>458.8</v>
       </c>
       <c r="J668">
         <v>39.51</v>
@@ -35894,22 +35894,75 @@
         <v>15.32</v>
       </c>
       <c r="L668">
-        <v>461.49</v>
+        <v>461.52</v>
       </c>
       <c r="M668">
-        <v>37497786</v>
+        <v>37497825</v>
       </c>
       <c r="N668">
-        <v>5405904</v>
+        <v>5405797</v>
       </c>
       <c r="O668">
-        <v>2110258</v>
+        <v>2110257</v>
       </c>
       <c r="P668">
-        <v>5530</v>
+        <v>5506</v>
       </c>
       <c r="Q668">
-        <v>15108</v>
+        <v>15145</v>
+      </c>
+      <c r="R668">
+        <v>476961</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="2">
+        <v>45900</v>
+      </c>
+      <c r="B669">
+        <v>46125</v>
+      </c>
+      <c r="D669">
+        <v>22154</v>
+      </c>
+      <c r="E669">
+        <v>7739</v>
+      </c>
+      <c r="F669">
+        <v>413209</v>
+      </c>
+      <c r="G669">
+        <v>306656</v>
+      </c>
+      <c r="H669">
+        <v>97862</v>
+      </c>
+      <c r="I669">
+        <v>322.93</v>
+      </c>
+      <c r="J669">
+        <v>36.62</v>
+      </c>
+      <c r="K669">
+        <v>15.27</v>
+      </c>
+      <c r="L669">
+        <v>462.68</v>
+      </c>
+      <c r="M669">
+        <v>34794756</v>
+      </c>
+      <c r="N669">
+        <v>5019350</v>
+      </c>
+      <c r="O669">
+        <v>1953466</v>
+      </c>
+      <c r="P669">
+        <v>5493</v>
+      </c>
+      <c r="Q669">
+        <v>15157</v>
       </c>
     </row>
   </sheetData>

--- a/data/monthly_state_ui.xlsx
+++ b/data/monthly_state_ui.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R669"/>
+  <dimension ref="A1:R672"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -35366,19 +35366,19 @@
         <v>1620.6</v>
       </c>
       <c r="D659">
-        <v>392515</v>
+        <v>392510</v>
       </c>
       <c r="E659">
         <v>165270</v>
       </c>
       <c r="F659">
-        <v>6904002</v>
+        <v>6903930</v>
       </c>
       <c r="G659">
-        <v>5923756</v>
+        <v>5923720</v>
       </c>
       <c r="H659">
-        <v>2667049</v>
+        <v>2667036</v>
       </c>
       <c r="I659">
         <v>458.86</v>
@@ -35393,10 +35393,10 @@
         <v>452.18</v>
       </c>
       <c r="M659">
-        <v>35642665</v>
+        <v>35642652</v>
       </c>
       <c r="N659">
-        <v>5281068</v>
+        <v>5281063</v>
       </c>
       <c r="O659">
         <v>2010974</v>
@@ -35416,25 +35416,25 @@
         <v>45626</v>
       </c>
       <c r="B660">
-        <v>939443</v>
+        <v>939442</v>
       </c>
       <c r="C660">
         <v>1681.3</v>
       </c>
       <c r="D660">
-        <v>368900</v>
+        <v>368899</v>
       </c>
       <c r="E660">
         <v>155499</v>
       </c>
       <c r="F660">
-        <v>6728140</v>
+        <v>6728120</v>
       </c>
       <c r="G660">
-        <v>5563171</v>
+        <v>5563149</v>
       </c>
       <c r="H660">
-        <v>2513669</v>
+        <v>2513659</v>
       </c>
       <c r="I660">
         <v>460.95</v>
@@ -35449,10 +35449,10 @@
         <v>452.83</v>
       </c>
       <c r="M660">
-        <v>35647623</v>
+        <v>35647600</v>
       </c>
       <c r="N660">
-        <v>5256640</v>
+        <v>5256634</v>
       </c>
       <c r="O660">
         <v>2015374</v>
@@ -35478,19 +35478,19 @@
         <v>1926.7</v>
       </c>
       <c r="D661">
-        <v>541872</v>
+        <v>541863</v>
       </c>
       <c r="E661">
-        <v>194486</v>
+        <v>194487</v>
       </c>
       <c r="F661">
-        <v>9204452</v>
+        <v>9204384</v>
       </c>
       <c r="G661">
-        <v>7721373</v>
+        <v>7721328</v>
       </c>
       <c r="H661">
-        <v>3513259</v>
+        <v>3513240</v>
       </c>
       <c r="I661">
         <v>463.85</v>
@@ -35505,13 +35505,13 @@
         <v>453.89</v>
       </c>
       <c r="M661">
-        <v>36311311</v>
+        <v>36311269</v>
       </c>
       <c r="N661">
-        <v>5333073</v>
+        <v>5333058</v>
       </c>
       <c r="O661">
-        <v>2050567</v>
+        <v>2050568</v>
       </c>
       <c r="P661">
         <v>5512</v>
@@ -35561,13 +35561,13 @@
         <v>454.83</v>
       </c>
       <c r="M662">
-        <v>36187169</v>
+        <v>36187127</v>
       </c>
       <c r="N662">
-        <v>5341621</v>
+        <v>5341606</v>
       </c>
       <c r="O662">
-        <v>2047433</v>
+        <v>2047434</v>
       </c>
       <c r="P662">
         <v>5524</v>
@@ -35617,13 +35617,13 @@
         <v>455.94</v>
       </c>
       <c r="M663">
-        <v>36328272</v>
+        <v>36328230</v>
       </c>
       <c r="N663">
-        <v>5334787</v>
+        <v>5334772</v>
       </c>
       <c r="O663">
-        <v>2055481</v>
+        <v>2055482</v>
       </c>
       <c r="P663">
         <v>5514</v>
@@ -35673,13 +35673,13 @@
         <v>457.11</v>
       </c>
       <c r="M664">
-        <v>36783789</v>
+        <v>36783747</v>
       </c>
       <c r="N664">
-        <v>5357362</v>
+        <v>5357347</v>
       </c>
       <c r="O664">
-        <v>2080485</v>
+        <v>2080486</v>
       </c>
       <c r="P664">
         <v>5515</v>
@@ -35729,13 +35729,13 @@
         <v>458.19</v>
       </c>
       <c r="M665">
-        <v>36812030</v>
+        <v>36811988</v>
       </c>
       <c r="N665">
-        <v>5375533</v>
+        <v>5375518</v>
       </c>
       <c r="O665">
-        <v>2084189</v>
+        <v>2084190</v>
       </c>
       <c r="P665">
         <v>5526</v>
@@ -35785,13 +35785,13 @@
         <v>458.9</v>
       </c>
       <c r="M666">
-        <v>36916434</v>
+        <v>36916392</v>
       </c>
       <c r="N666">
-        <v>5368100</v>
+        <v>5368085</v>
       </c>
       <c r="O666">
-        <v>2089887</v>
+        <v>2089888</v>
       </c>
       <c r="P666">
         <v>5515</v>
@@ -35808,28 +35808,28 @@
         <v>45838</v>
       </c>
       <c r="B667">
-        <v>1032545</v>
+        <v>1031839</v>
       </c>
       <c r="C667">
         <v>1860.9</v>
       </c>
       <c r="D667">
-        <v>457397</v>
+        <v>457394</v>
       </c>
       <c r="E667">
-        <v>178940</v>
+        <v>178819</v>
       </c>
       <c r="F667">
-        <v>8573388</v>
+        <v>8573274</v>
       </c>
       <c r="G667">
-        <v>6954177</v>
+        <v>6954166</v>
       </c>
       <c r="H667">
-        <v>3103168</v>
+        <v>3100962</v>
       </c>
       <c r="I667">
-        <v>455.59</v>
+        <v>455.27</v>
       </c>
       <c r="J667">
         <v>39.55</v>
@@ -35838,16 +35838,16 @@
         <v>15.3</v>
       </c>
       <c r="L667">
-        <v>459.7</v>
+        <v>459.67</v>
       </c>
       <c r="M667">
-        <v>37396197</v>
+        <v>37393949</v>
       </c>
       <c r="N667">
-        <v>5419940</v>
+        <v>5419922</v>
       </c>
       <c r="O667">
-        <v>2109273</v>
+        <v>2109153</v>
       </c>
       <c r="P667">
         <v>5511</v>
@@ -35856,7 +35856,7 @@
         <v>15128</v>
       </c>
       <c r="R667">
-        <v>476567</v>
+        <v>477452</v>
       </c>
     </row>
     <row r="668">
@@ -35864,55 +35864,55 @@
         <v>45869</v>
       </c>
       <c r="B668">
-        <v>982388</v>
+        <v>980979</v>
       </c>
       <c r="C668">
         <v>2004.2</v>
       </c>
       <c r="D668">
-        <v>507983</v>
+        <v>510131</v>
       </c>
       <c r="E668">
-        <v>182814</v>
+        <v>182274</v>
       </c>
       <c r="F668">
-        <v>8405149</v>
+        <v>8421956</v>
       </c>
       <c r="G668">
-        <v>7257173</v>
+        <v>7295134</v>
       </c>
       <c r="H668">
-        <v>3266454</v>
+        <v>3288702</v>
       </c>
       <c r="I668">
-        <v>458.8</v>
+        <v>459.83</v>
       </c>
       <c r="J668">
-        <v>39.51</v>
+        <v>39.49</v>
       </c>
       <c r="K668">
         <v>15.32</v>
       </c>
       <c r="L668">
-        <v>461.52</v>
+        <v>461.59</v>
       </c>
       <c r="M668">
-        <v>37497825</v>
+        <v>37517826</v>
       </c>
       <c r="N668">
-        <v>5405797</v>
+        <v>5407927</v>
       </c>
       <c r="O668">
-        <v>2110257</v>
+        <v>2109597</v>
       </c>
       <c r="P668">
-        <v>5506</v>
+        <v>5505</v>
       </c>
       <c r="Q668">
-        <v>15145</v>
+        <v>15158</v>
       </c>
       <c r="R668">
-        <v>476961</v>
+        <v>478424</v>
       </c>
     </row>
     <row r="669">
@@ -35920,49 +35920,211 @@
         <v>45900</v>
       </c>
       <c r="B669">
-        <v>46125</v>
+        <v>837185</v>
+      </c>
+      <c r="C669">
+        <v>1906.9</v>
       </c>
       <c r="D669">
-        <v>22154</v>
+        <v>406082</v>
       </c>
       <c r="E669">
-        <v>7739</v>
+        <v>177775</v>
       </c>
       <c r="F669">
-        <v>413209</v>
+        <v>8429787</v>
       </c>
       <c r="G669">
-        <v>306656</v>
+        <v>6919720</v>
       </c>
       <c r="H669">
-        <v>97862</v>
+        <v>3095975</v>
       </c>
       <c r="I669">
-        <v>322.93</v>
+        <v>457.06</v>
       </c>
       <c r="J669">
-        <v>36.62</v>
+        <v>39.79</v>
       </c>
       <c r="K669">
-        <v>15.27</v>
+        <v>15.41</v>
       </c>
       <c r="L669">
-        <v>462.68</v>
+        <v>462.81</v>
       </c>
       <c r="M669">
-        <v>34794756</v>
+        <v>37812870</v>
       </c>
       <c r="N669">
-        <v>5019350</v>
+        <v>5405408</v>
       </c>
       <c r="O669">
-        <v>1953466</v>
+        <v>2122842</v>
       </c>
       <c r="P669">
-        <v>5493</v>
+        <v>5478</v>
       </c>
       <c r="Q669">
-        <v>15157</v>
+        <v>15168</v>
+      </c>
+      <c r="R669">
+        <v>478555</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="2">
+        <v>45930</v>
+      </c>
+      <c r="B670">
+        <v>852461</v>
+      </c>
+      <c r="C670">
+        <v>1709.7</v>
+      </c>
+      <c r="D670">
+        <v>369969</v>
+      </c>
+      <c r="E670">
+        <v>178882</v>
+      </c>
+      <c r="F670">
+        <v>7502514</v>
+      </c>
+      <c r="G670">
+        <v>6623282</v>
+      </c>
+      <c r="H670">
+        <v>3039112</v>
+      </c>
+      <c r="I670">
+        <v>469.54</v>
+      </c>
+      <c r="J670">
+        <v>39.8</v>
+      </c>
+      <c r="K670">
+        <v>15.43</v>
+      </c>
+      <c r="L670">
+        <v>464.21</v>
+      </c>
+      <c r="M670">
+        <v>38098435</v>
+      </c>
+      <c r="N670">
+        <v>5424109</v>
+      </c>
+      <c r="O670">
+        <v>2132197</v>
+      </c>
+      <c r="P670">
+        <v>5486</v>
+      </c>
+      <c r="Q670">
+        <v>15168</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="2">
+        <v>45961</v>
+      </c>
+      <c r="B671">
+        <v>924251</v>
+      </c>
+      <c r="C671">
+        <v>1689.4</v>
+      </c>
+      <c r="D671">
+        <v>380062</v>
+      </c>
+      <c r="E671">
+        <v>170539</v>
+      </c>
+      <c r="F671">
+        <v>6982033</v>
+      </c>
+      <c r="G671">
+        <v>5980413</v>
+      </c>
+      <c r="H671">
+        <v>2837711</v>
+      </c>
+      <c r="I671">
+        <v>485.72</v>
+      </c>
+      <c r="J671">
+        <v>39.76</v>
+      </c>
+      <c r="K671">
+        <v>15.48</v>
+      </c>
+      <c r="L671">
+        <v>466.12</v>
+      </c>
+      <c r="M671">
+        <v>38269110</v>
+      </c>
+      <c r="N671">
+        <v>5411661</v>
+      </c>
+      <c r="O671">
+        <v>2137466</v>
+      </c>
+      <c r="P671">
+        <v>5474</v>
+      </c>
+      <c r="Q671">
+        <v>15185</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="2">
+        <v>45991</v>
+      </c>
+      <c r="B672">
+        <v>934796</v>
+      </c>
+      <c r="D672">
+        <v>379999</v>
+      </c>
+      <c r="E672">
+        <v>169916</v>
+      </c>
+      <c r="F672">
+        <v>7512082</v>
+      </c>
+      <c r="G672">
+        <v>5952369</v>
+      </c>
+      <c r="H672">
+        <v>2830953</v>
+      </c>
+      <c r="I672">
+        <v>487.78</v>
+      </c>
+      <c r="J672">
+        <v>40.09</v>
+      </c>
+      <c r="K672">
+        <v>15.52</v>
+      </c>
+      <c r="L672">
+        <v>467.98</v>
+      </c>
+      <c r="M672">
+        <v>38586405</v>
+      </c>
+      <c r="N672">
+        <v>5422761</v>
+      </c>
+      <c r="O672">
+        <v>2151883</v>
+      </c>
+      <c r="P672">
+        <v>5477</v>
+      </c>
+      <c r="Q672">
+        <v>15183</v>
       </c>
     </row>
   </sheetData>

--- a/data/monthly_state_ui.xlsx
+++ b/data/monthly_state_ui.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R672"/>
+  <dimension ref="A1:R673"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -35864,7 +35864,7 @@
         <v>45869</v>
       </c>
       <c r="B668">
-        <v>980979</v>
+        <v>981136</v>
       </c>
       <c r="C668">
         <v>2004.2</v>
@@ -35912,7 +35912,7 @@
         <v>15158</v>
       </c>
       <c r="R668">
-        <v>478424</v>
+        <v>480190</v>
       </c>
     </row>
     <row r="669">
@@ -35920,7 +35920,7 @@
         <v>45900</v>
       </c>
       <c r="B669">
-        <v>837185</v>
+        <v>837361</v>
       </c>
       <c r="C669">
         <v>1906.9</v>
@@ -35968,7 +35968,7 @@
         <v>15168</v>
       </c>
       <c r="R669">
-        <v>478555</v>
+        <v>481748</v>
       </c>
     </row>
     <row r="670">
@@ -35976,7 +35976,7 @@
         <v>45930</v>
       </c>
       <c r="B670">
-        <v>852461</v>
+        <v>852588</v>
       </c>
       <c r="C670">
         <v>1709.7</v>
@@ -35985,13 +35985,13 @@
         <v>369969</v>
       </c>
       <c r="E670">
-        <v>178882</v>
+        <v>178883</v>
       </c>
       <c r="F670">
-        <v>7502514</v>
+        <v>7502517</v>
       </c>
       <c r="G670">
-        <v>6623282</v>
+        <v>6623265</v>
       </c>
       <c r="H670">
         <v>3039112</v>
@@ -36015,13 +36015,16 @@
         <v>5424109</v>
       </c>
       <c r="O670">
-        <v>2132197</v>
+        <v>2132198</v>
       </c>
       <c r="P670">
         <v>5486</v>
       </c>
       <c r="Q670">
         <v>15168</v>
+      </c>
+      <c r="R670">
+        <v>485022</v>
       </c>
     </row>
     <row r="671">
@@ -36068,13 +36071,16 @@
         <v>5411661</v>
       </c>
       <c r="O671">
-        <v>2137466</v>
+        <v>2137467</v>
       </c>
       <c r="P671">
-        <v>5474</v>
+        <v>5473</v>
       </c>
       <c r="Q671">
-        <v>15185</v>
+        <v>15186</v>
+      </c>
+      <c r="R671">
+        <v>486256</v>
       </c>
     </row>
     <row r="672">
@@ -36082,25 +36088,25 @@
         <v>45991</v>
       </c>
       <c r="B672">
-        <v>934796</v>
+        <v>932682</v>
       </c>
       <c r="D672">
-        <v>379999</v>
+        <v>380214</v>
       </c>
       <c r="E672">
-        <v>169916</v>
+        <v>169893</v>
       </c>
       <c r="F672">
-        <v>7512082</v>
+        <v>7525804</v>
       </c>
       <c r="G672">
-        <v>5952369</v>
+        <v>5950591</v>
       </c>
       <c r="H672">
-        <v>2830953</v>
+        <v>2832070</v>
       </c>
       <c r="I672">
-        <v>487.78</v>
+        <v>487.68</v>
       </c>
       <c r="J672">
         <v>40.09</v>
@@ -36112,19 +36118,69 @@
         <v>467.98</v>
       </c>
       <c r="M672">
-        <v>38586405</v>
+        <v>38587521</v>
       </c>
       <c r="N672">
-        <v>5422761</v>
+        <v>5422976</v>
       </c>
       <c r="O672">
-        <v>2151883</v>
+        <v>2151861</v>
       </c>
       <c r="P672">
-        <v>5477</v>
+        <v>5474</v>
       </c>
       <c r="Q672">
-        <v>15183</v>
+        <v>15188</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="2">
+        <v>46022</v>
+      </c>
+      <c r="B673">
+        <v>1090401</v>
+      </c>
+      <c r="D673">
+        <v>461712</v>
+      </c>
+      <c r="E673">
+        <v>162551</v>
+      </c>
+      <c r="F673">
+        <v>7294960</v>
+      </c>
+      <c r="G673">
+        <v>6474054</v>
+      </c>
+      <c r="H673">
+        <v>3033390</v>
+      </c>
+      <c r="I673">
+        <v>479.1</v>
+      </c>
+      <c r="J673">
+        <v>39.11</v>
+      </c>
+      <c r="K673">
+        <v>15.51</v>
+      </c>
+      <c r="L673">
+        <v>469.22</v>
+      </c>
+      <c r="M673">
+        <v>38107671</v>
+      </c>
+      <c r="N673">
+        <v>5342825</v>
+      </c>
+      <c r="O673">
+        <v>2119925</v>
+      </c>
+      <c r="P673">
+        <v>5467</v>
+      </c>
+      <c r="Q673">
+        <v>15206</v>
       </c>
     </row>
   </sheetData>

--- a/data/monthly_state_ui.xlsx
+++ b/data/monthly_state_ui.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R673"/>
+  <dimension ref="A1:R674"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -32882,10 +32882,10 @@
         <v>12105826</v>
       </c>
       <c r="P614">
-        <v>5150</v>
+        <v>5142</v>
       </c>
       <c r="Q614">
-        <v>13743</v>
+        <v>13715</v>
       </c>
       <c r="R614">
         <v>342295</v>
@@ -32938,10 +32938,10 @@
         <v>12600385</v>
       </c>
       <c r="P615">
-        <v>5154</v>
+        <v>5153</v>
       </c>
       <c r="Q615">
-        <v>13728</v>
+        <v>13718</v>
       </c>
       <c r="R615">
         <v>334159</v>
@@ -32994,10 +32994,10 @@
         <v>13044263</v>
       </c>
       <c r="P616">
-        <v>5192</v>
+        <v>5186</v>
       </c>
       <c r="Q616">
-        <v>13779</v>
+        <v>13773</v>
       </c>
       <c r="R616">
         <v>337880</v>
@@ -33050,10 +33050,10 @@
         <v>13246975</v>
       </c>
       <c r="P617">
-        <v>5187</v>
+        <v>5180</v>
       </c>
       <c r="Q617">
-        <v>13827</v>
+        <v>13819</v>
       </c>
       <c r="R617">
         <v>336247</v>
@@ -33106,10 +33106,10 @@
         <v>13354228</v>
       </c>
       <c r="P618">
-        <v>5174</v>
+        <v>5178</v>
       </c>
       <c r="Q618">
-        <v>13849</v>
+        <v>13865</v>
       </c>
       <c r="R618">
         <v>337543</v>
@@ -33162,10 +33162,10 @@
         <v>13081161</v>
       </c>
       <c r="P619">
-        <v>5199</v>
+        <v>5197</v>
       </c>
       <c r="Q619">
-        <v>13917</v>
+        <v>13947</v>
       </c>
       <c r="R619">
         <v>329898</v>
@@ -33218,10 +33218,10 @@
         <v>12415951</v>
       </c>
       <c r="P620">
-        <v>5177</v>
+        <v>5180</v>
       </c>
       <c r="Q620">
-        <v>13990</v>
+        <v>13967</v>
       </c>
       <c r="R620">
         <v>330467</v>
@@ -33274,10 +33274,10 @@
         <v>11621754</v>
       </c>
       <c r="P621">
-        <v>5155</v>
+        <v>5153</v>
       </c>
       <c r="Q621">
-        <v>14057</v>
+        <v>14095</v>
       </c>
       <c r="R621">
         <v>332900</v>
@@ -33330,10 +33330,10 @@
         <v>8844628</v>
       </c>
       <c r="P622">
-        <v>5139</v>
+        <v>5137</v>
       </c>
       <c r="Q622">
-        <v>14055</v>
+        <v>14078</v>
       </c>
       <c r="R622">
         <v>327369</v>
@@ -33389,7 +33389,7 @@
         <v>5132</v>
       </c>
       <c r="Q623">
-        <v>14035</v>
+        <v>14017</v>
       </c>
       <c r="R623">
         <v>324962</v>
@@ -33442,10 +33442,10 @@
         <v>5597412</v>
       </c>
       <c r="P624">
-        <v>5121</v>
+        <v>5124</v>
       </c>
       <c r="Q624">
-        <v>14035</v>
+        <v>14033</v>
       </c>
       <c r="R624">
         <v>331225</v>
@@ -33498,10 +33498,10 @@
         <v>4737809</v>
       </c>
       <c r="P625">
-        <v>5122</v>
+        <v>5121</v>
       </c>
       <c r="Q625">
-        <v>14071</v>
+        <v>14059</v>
       </c>
       <c r="R625">
         <v>332079</v>
@@ -33554,10 +33554,10 @@
         <v>4093576</v>
       </c>
       <c r="P626">
-        <v>5087</v>
+        <v>5089</v>
       </c>
       <c r="Q626">
-        <v>14091</v>
+        <v>14081</v>
       </c>
       <c r="R626">
         <v>335367</v>
@@ -33610,10 +33610,10 @@
         <v>3599436</v>
       </c>
       <c r="P627">
-        <v>5070</v>
+        <v>5069</v>
       </c>
       <c r="Q627">
-        <v>14097</v>
+        <v>14089</v>
       </c>
       <c r="R627">
         <v>339940</v>
@@ -33666,10 +33666,10 @@
         <v>3159034</v>
       </c>
       <c r="P628">
-        <v>5057</v>
+        <v>5052</v>
       </c>
       <c r="Q628">
-        <v>14116</v>
+        <v>14114</v>
       </c>
       <c r="R628">
         <v>343309</v>
@@ -33722,10 +33722,10 @@
         <v>2875535</v>
       </c>
       <c r="P629">
-        <v>5075</v>
+        <v>5068</v>
       </c>
       <c r="Q629">
-        <v>14137</v>
+        <v>14135</v>
       </c>
       <c r="R629">
         <v>349983</v>
@@ -33778,10 +33778,10 @@
         <v>2630865</v>
       </c>
       <c r="P630">
-        <v>5095</v>
+        <v>5100</v>
       </c>
       <c r="Q630">
-        <v>14145</v>
+        <v>14163</v>
       </c>
       <c r="R630">
         <v>342679</v>
@@ -33834,10 +33834,10 @@
         <v>2404027</v>
       </c>
       <c r="P631">
-        <v>5104</v>
+        <v>5107</v>
       </c>
       <c r="Q631">
-        <v>14168</v>
+        <v>14182</v>
       </c>
       <c r="R631">
         <v>349662</v>
@@ -33890,10 +33890,10 @@
         <v>2232756</v>
       </c>
       <c r="P632">
-        <v>5140</v>
+        <v>5137</v>
       </c>
       <c r="Q632">
-        <v>14280</v>
+        <v>14307</v>
       </c>
       <c r="R632">
         <v>357378</v>
@@ -33946,10 +33946,10 @@
         <v>2077763</v>
       </c>
       <c r="P633">
-        <v>5146</v>
+        <v>5144</v>
       </c>
       <c r="Q633">
-        <v>14264</v>
+        <v>14301</v>
       </c>
       <c r="R633">
         <v>362881</v>
@@ -34002,10 +34002,10 @@
         <v>1874576</v>
       </c>
       <c r="P634">
-        <v>5148</v>
+        <v>5149</v>
       </c>
       <c r="Q634">
-        <v>14269</v>
+        <v>14283</v>
       </c>
       <c r="R634">
         <v>366384</v>
@@ -34058,10 +34058,10 @@
         <v>1683174</v>
       </c>
       <c r="P635">
-        <v>5139</v>
+        <v>5140</v>
       </c>
       <c r="Q635">
-        <v>14301</v>
+        <v>14283</v>
       </c>
       <c r="R635">
         <v>365642</v>
@@ -34114,10 +34114,10 @@
         <v>1584506</v>
       </c>
       <c r="P636">
-        <v>5162</v>
+        <v>5163</v>
       </c>
       <c r="Q636">
-        <v>14337</v>
+        <v>14339</v>
       </c>
       <c r="R636">
         <v>366244</v>
@@ -34170,10 +34170,10 @@
         <v>1517217</v>
       </c>
       <c r="P637">
-        <v>5136</v>
+        <v>5133</v>
       </c>
       <c r="Q637">
-        <v>14364</v>
+        <v>14358</v>
       </c>
       <c r="R637">
         <v>373987</v>
@@ -34229,7 +34229,7 @@
         <v>5199</v>
       </c>
       <c r="Q638">
-        <v>14411</v>
+        <v>14405</v>
       </c>
       <c r="R638">
         <v>379392</v>
@@ -34282,10 +34282,10 @@
         <v>1459580</v>
       </c>
       <c r="P639">
-        <v>5219</v>
+        <v>5218</v>
       </c>
       <c r="Q639">
-        <v>14439</v>
+        <v>14433</v>
       </c>
       <c r="R639">
         <v>387843</v>
@@ -34338,10 +34338,10 @@
         <v>1421645</v>
       </c>
       <c r="P640">
-        <v>5235</v>
+        <v>5232</v>
       </c>
       <c r="Q640">
-        <v>14453</v>
+        <v>14455</v>
       </c>
       <c r="R640">
         <v>397990</v>
@@ -34394,10 +34394,10 @@
         <v>1445142</v>
       </c>
       <c r="P641">
-        <v>5251</v>
+        <v>5252</v>
       </c>
       <c r="Q641">
-        <v>14478</v>
+        <v>14486</v>
       </c>
       <c r="R641">
         <v>405401</v>
@@ -34450,10 +34450,10 @@
         <v>1475491</v>
       </c>
       <c r="P642">
-        <v>5272</v>
+        <v>5278</v>
       </c>
       <c r="Q642">
-        <v>14509</v>
+        <v>14529</v>
       </c>
       <c r="R642">
         <v>417406</v>
@@ -34506,10 +34506,10 @@
         <v>1504895</v>
       </c>
       <c r="P643">
-        <v>5294</v>
+        <v>5295</v>
       </c>
       <c r="Q643">
-        <v>14565</v>
+        <v>14572</v>
       </c>
       <c r="R643">
         <v>423949</v>
@@ -34562,10 +34562,10 @@
         <v>1556926</v>
       </c>
       <c r="P644">
-        <v>5303</v>
+        <v>5298</v>
       </c>
       <c r="Q644">
-        <v>14589</v>
+        <v>14609</v>
       </c>
       <c r="R644">
         <v>422871</v>
@@ -34618,10 +34618,10 @@
         <v>1594529</v>
       </c>
       <c r="P645">
-        <v>5324</v>
+        <v>5320</v>
       </c>
       <c r="Q645">
-        <v>14603</v>
+        <v>14641</v>
       </c>
       <c r="R645">
         <v>428148</v>
@@ -34677,7 +34677,7 @@
         <v>5337</v>
       </c>
       <c r="Q646">
-        <v>14653</v>
+        <v>14660</v>
       </c>
       <c r="R646">
         <v>436947</v>
@@ -34730,10 +34730,10 @@
         <v>1688430</v>
       </c>
       <c r="P647">
-        <v>5359</v>
+        <v>5361</v>
       </c>
       <c r="Q647">
-        <v>14693</v>
+        <v>14676</v>
       </c>
       <c r="R647">
         <v>444351</v>
@@ -34786,10 +34786,10 @@
         <v>1727451</v>
       </c>
       <c r="P648">
-        <v>5366</v>
+        <v>5363</v>
       </c>
       <c r="Q648">
-        <v>14728</v>
+        <v>14713</v>
       </c>
       <c r="R648">
         <v>453531</v>
@@ -34842,10 +34842,10 @@
         <v>1772185</v>
       </c>
       <c r="P649">
-        <v>5378</v>
+        <v>5372</v>
       </c>
       <c r="Q649">
-        <v>14763</v>
+        <v>14755</v>
       </c>
       <c r="R649">
         <v>456086</v>
@@ -34898,10 +34898,10 @@
         <v>1816373</v>
       </c>
       <c r="P650">
-        <v>5390</v>
+        <v>5388</v>
       </c>
       <c r="Q650">
-        <v>14786</v>
+        <v>14781</v>
       </c>
       <c r="R650">
         <v>449421</v>
@@ -34954,10 +34954,10 @@
         <v>1855195</v>
       </c>
       <c r="P651">
-        <v>5404</v>
+        <v>5405</v>
       </c>
       <c r="Q651">
-        <v>14835</v>
+        <v>14826</v>
       </c>
       <c r="R651">
         <v>460527</v>
@@ -35010,10 +35010,10 @@
         <v>1888538</v>
       </c>
       <c r="P652">
-        <v>5414</v>
+        <v>5413</v>
       </c>
       <c r="Q652">
-        <v>14890</v>
+        <v>14894</v>
       </c>
       <c r="R652">
         <v>455814</v>
@@ -35066,10 +35066,10 @@
         <v>1925423</v>
       </c>
       <c r="P653">
-        <v>5418</v>
+        <v>5421</v>
       </c>
       <c r="Q653">
-        <v>14877</v>
+        <v>14884</v>
       </c>
       <c r="R653">
         <v>460896</v>
@@ -35125,7 +35125,7 @@
         <v>5420</v>
       </c>
       <c r="Q654">
-        <v>14905</v>
+        <v>14909</v>
       </c>
       <c r="R654">
         <v>458902</v>
@@ -35178,10 +35178,10 @@
         <v>1962179</v>
       </c>
       <c r="P655">
-        <v>5429</v>
+        <v>5423</v>
       </c>
       <c r="Q655">
-        <v>14915</v>
+        <v>14911</v>
       </c>
       <c r="R655">
         <v>454153</v>
@@ -35234,10 +35234,10 @@
         <v>1978635</v>
       </c>
       <c r="P656">
-        <v>5444</v>
+        <v>5443</v>
       </c>
       <c r="Q656">
-        <v>14946</v>
+        <v>14950</v>
       </c>
       <c r="R656">
         <v>464102</v>
@@ -35290,10 +35290,10 @@
         <v>1987043</v>
       </c>
       <c r="P657">
-        <v>5453</v>
+        <v>5468</v>
       </c>
       <c r="Q657">
-        <v>14973</v>
+        <v>14957</v>
       </c>
       <c r="R657">
         <v>469078</v>
@@ -35346,10 +35346,10 @@
         <v>2015413</v>
       </c>
       <c r="P658">
-        <v>5468</v>
+        <v>5479</v>
       </c>
       <c r="Q658">
-        <v>14986</v>
+        <v>14958</v>
       </c>
       <c r="R658">
         <v>470037</v>
@@ -35402,10 +35402,10 @@
         <v>2010974</v>
       </c>
       <c r="P659">
-        <v>5484</v>
+        <v>5492</v>
       </c>
       <c r="Q659">
-        <v>15012</v>
+        <v>14981</v>
       </c>
       <c r="R659">
         <v>474646</v>
@@ -35458,10 +35458,10 @@
         <v>2015374</v>
       </c>
       <c r="P660">
-        <v>5493</v>
+        <v>5502</v>
       </c>
       <c r="Q660">
-        <v>15022</v>
+        <v>14993</v>
       </c>
       <c r="R660">
         <v>472134</v>
@@ -35514,10 +35514,10 @@
         <v>2050568</v>
       </c>
       <c r="P661">
-        <v>5512</v>
+        <v>5515</v>
       </c>
       <c r="Q661">
-        <v>15036</v>
+        <v>15005</v>
       </c>
       <c r="R661">
         <v>466925</v>
@@ -35570,10 +35570,10 @@
         <v>2047434</v>
       </c>
       <c r="P662">
-        <v>5524</v>
+        <v>5525</v>
       </c>
       <c r="Q662">
-        <v>15053</v>
+        <v>15022</v>
       </c>
       <c r="R662">
         <v>468212</v>
@@ -35626,10 +35626,10 @@
         <v>2055482</v>
       </c>
       <c r="P663">
-        <v>5514</v>
+        <v>5525</v>
       </c>
       <c r="Q663">
-        <v>15071</v>
+        <v>15037</v>
       </c>
       <c r="R663">
         <v>467885</v>
@@ -35682,10 +35682,10 @@
         <v>2080486</v>
       </c>
       <c r="P664">
-        <v>5515</v>
+        <v>5523</v>
       </c>
       <c r="Q664">
-        <v>15087</v>
+        <v>15048</v>
       </c>
       <c r="R664">
         <v>470613</v>
@@ -35738,10 +35738,10 @@
         <v>2084190</v>
       </c>
       <c r="P665">
-        <v>5526</v>
+        <v>5522</v>
       </c>
       <c r="Q665">
-        <v>15114</v>
+        <v>15070</v>
       </c>
       <c r="R665">
         <v>475304</v>
@@ -35797,7 +35797,7 @@
         <v>5515</v>
       </c>
       <c r="Q666">
-        <v>15101</v>
+        <v>15094</v>
       </c>
       <c r="R666">
         <v>475285</v>
@@ -35850,10 +35850,10 @@
         <v>2109153</v>
       </c>
       <c r="P667">
-        <v>5511</v>
+        <v>5516</v>
       </c>
       <c r="Q667">
-        <v>15128</v>
+        <v>15126</v>
       </c>
       <c r="R667">
         <v>477452</v>
@@ -35906,10 +35906,10 @@
         <v>2109597</v>
       </c>
       <c r="P668">
-        <v>5505</v>
+        <v>5504</v>
       </c>
       <c r="Q668">
-        <v>15158</v>
+        <v>15146</v>
       </c>
       <c r="R668">
         <v>480190</v>
@@ -35962,10 +35962,10 @@
         <v>2122842</v>
       </c>
       <c r="P669">
-        <v>5478</v>
+        <v>5487</v>
       </c>
       <c r="Q669">
-        <v>15168</v>
+        <v>15132</v>
       </c>
       <c r="R669">
         <v>481748</v>
@@ -36018,10 +36018,10 @@
         <v>2132198</v>
       </c>
       <c r="P670">
-        <v>5486</v>
+        <v>5497</v>
       </c>
       <c r="Q670">
-        <v>15168</v>
+        <v>15132</v>
       </c>
       <c r="R670">
         <v>485022</v>
@@ -36032,7 +36032,7 @@
         <v>45961</v>
       </c>
       <c r="B671">
-        <v>924251</v>
+        <v>923951</v>
       </c>
       <c r="C671">
         <v>1689.4</v>
@@ -36044,7 +36044,7 @@
         <v>170539</v>
       </c>
       <c r="F671">
-        <v>6982033</v>
+        <v>6981949</v>
       </c>
       <c r="G671">
         <v>5980413</v>
@@ -36074,10 +36074,10 @@
         <v>2137467</v>
       </c>
       <c r="P671">
-        <v>5473</v>
+        <v>5493</v>
       </c>
       <c r="Q671">
-        <v>15186</v>
+        <v>15149</v>
       </c>
       <c r="R671">
         <v>486256</v>
@@ -36088,49 +36088,52 @@
         <v>45991</v>
       </c>
       <c r="B672">
-        <v>932682</v>
+        <v>944804</v>
+      </c>
+      <c r="C672">
+        <v>1766.7</v>
       </c>
       <c r="D672">
-        <v>380214</v>
+        <v>382977</v>
       </c>
       <c r="E672">
-        <v>169893</v>
+        <v>169583</v>
       </c>
       <c r="F672">
-        <v>7525804</v>
+        <v>7596783</v>
       </c>
       <c r="G672">
-        <v>5950591</v>
+        <v>5961933</v>
       </c>
       <c r="H672">
-        <v>2832070</v>
+        <v>2835263</v>
       </c>
       <c r="I672">
-        <v>487.68</v>
+        <v>487.66</v>
       </c>
       <c r="J672">
-        <v>40.09</v>
+        <v>40.08</v>
       </c>
       <c r="K672">
-        <v>15.52</v>
+        <v>15.51</v>
       </c>
       <c r="L672">
         <v>467.98</v>
       </c>
       <c r="M672">
-        <v>38587521</v>
+        <v>38590714</v>
       </c>
       <c r="N672">
-        <v>5422976</v>
+        <v>5425739</v>
       </c>
       <c r="O672">
-        <v>2151861</v>
+        <v>2151551</v>
       </c>
       <c r="P672">
-        <v>5474</v>
+        <v>5481</v>
       </c>
       <c r="Q672">
-        <v>15188</v>
+        <v>15145</v>
       </c>
     </row>
     <row r="673">
@@ -36138,49 +36141,63 @@
         <v>46022</v>
       </c>
       <c r="B673">
-        <v>1090401</v>
+        <v>1285497</v>
+      </c>
+      <c r="C673">
+        <v>1974.9</v>
       </c>
       <c r="D673">
-        <v>461712</v>
+        <v>547548</v>
       </c>
       <c r="E673">
-        <v>162551</v>
+        <v>192436</v>
       </c>
       <c r="F673">
-        <v>7294960</v>
+        <v>8746904</v>
       </c>
       <c r="G673">
-        <v>6474054</v>
+        <v>7817564</v>
       </c>
       <c r="H673">
-        <v>3033390</v>
+        <v>3794240</v>
       </c>
       <c r="I673">
-        <v>479.1</v>
+        <v>497.52</v>
       </c>
       <c r="J673">
-        <v>39.11</v>
+        <v>39.66</v>
       </c>
       <c r="K673">
         <v>15.51</v>
       </c>
       <c r="L673">
-        <v>469.22</v>
+        <v>471.08</v>
       </c>
       <c r="M673">
-        <v>38107671</v>
+        <v>38871714</v>
       </c>
       <c r="N673">
-        <v>5342825</v>
+        <v>5431424</v>
       </c>
       <c r="O673">
-        <v>2119925</v>
+        <v>2149500</v>
       </c>
       <c r="P673">
-        <v>5467</v>
+        <v>5471</v>
       </c>
       <c r="Q673">
-        <v>15206</v>
+        <v>15152</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="2">
+        <v>46053</v>
+      </c>
+      <c r="P674">
+        <v>5453</v>
+      </c>
+      <c r="Q674">
+        <v>15162</v>
       </c>
     </row>
   </sheetData>

--- a/data/monthly_state_ui.xlsx
+++ b/data/monthly_state_ui.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R674"/>
+  <dimension ref="A1:R675"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -36024,7 +36024,7 @@
         <v>15132</v>
       </c>
       <c r="R670">
-        <v>485022</v>
+        <v>487347</v>
       </c>
     </row>
     <row r="671">
@@ -36080,7 +36080,7 @@
         <v>15149</v>
       </c>
       <c r="R671">
-        <v>486256</v>
+        <v>487527</v>
       </c>
     </row>
     <row r="672">
@@ -36135,34 +36135,37 @@
       <c r="Q672">
         <v>15145</v>
       </c>
+      <c r="R672">
+        <v>486489</v>
+      </c>
     </row>
     <row r="673">
       <c r="A673" s="2">
         <v>46022</v>
       </c>
       <c r="B673">
-        <v>1285497</v>
+        <v>1285782</v>
       </c>
       <c r="C673">
         <v>1974.9</v>
       </c>
       <c r="D673">
-        <v>547548</v>
+        <v>547322</v>
       </c>
       <c r="E673">
-        <v>192436</v>
+        <v>192399</v>
       </c>
       <c r="F673">
-        <v>8746904</v>
+        <v>8741250</v>
       </c>
       <c r="G673">
-        <v>7817564</v>
+        <v>7813783</v>
       </c>
       <c r="H673">
-        <v>3794240</v>
+        <v>3792657</v>
       </c>
       <c r="I673">
-        <v>497.52</v>
+        <v>497.56</v>
       </c>
       <c r="J673">
         <v>39.66</v>
@@ -36174,30 +36177,86 @@
         <v>471.08</v>
       </c>
       <c r="M673">
-        <v>38871714</v>
+        <v>38870131</v>
       </c>
       <c r="N673">
-        <v>5431424</v>
+        <v>5431198</v>
       </c>
       <c r="O673">
-        <v>2149500</v>
+        <v>2149463</v>
       </c>
       <c r="P673">
-        <v>5471</v>
+        <v>5476</v>
       </c>
       <c r="Q673">
-        <v>15152</v>
+        <v>15151</v>
+      </c>
+      <c r="R673">
+        <v>483260</v>
       </c>
     </row>
     <row r="674">
       <c r="A674" s="2">
         <v>46053</v>
       </c>
+      <c r="B674">
+        <v>1161791</v>
+      </c>
+      <c r="C674">
+        <v>2105.6</v>
+      </c>
+      <c r="D674">
+        <v>642376</v>
+      </c>
+      <c r="E674">
+        <v>182859</v>
+      </c>
+      <c r="F674">
+        <v>8970205</v>
+      </c>
+      <c r="G674">
+        <v>7708449</v>
+      </c>
+      <c r="H674">
+        <v>3752803</v>
+      </c>
+      <c r="I674">
+        <v>498.09</v>
+      </c>
+      <c r="J674">
+        <v>39.77</v>
+      </c>
+      <c r="K674">
+        <v>15.61</v>
+      </c>
+      <c r="L674">
+        <v>473.72</v>
+      </c>
+      <c r="M674">
+        <v>38969876</v>
+      </c>
+      <c r="N674">
+        <v>5384517</v>
+      </c>
+      <c r="O674">
+        <v>2150953</v>
+      </c>
       <c r="P674">
-        <v>5453</v>
+        <v>5475</v>
       </c>
       <c r="Q674">
-        <v>15162</v>
+        <v>15161</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="2">
+        <v>46081</v>
+      </c>
+      <c r="P675">
+        <v>5480</v>
+      </c>
+      <c r="Q675">
+        <v>15160</v>
       </c>
     </row>
   </sheetData>

--- a/data/monthly_state_ui.xlsx
+++ b/data/monthly_state_ui.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R675"/>
+  <dimension ref="A1:R676"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -35864,25 +35864,25 @@
         <v>45869</v>
       </c>
       <c r="B668">
-        <v>981136</v>
+        <v>981550</v>
       </c>
       <c r="C668">
         <v>2004.2</v>
       </c>
       <c r="D668">
-        <v>510131</v>
+        <v>510167</v>
       </c>
       <c r="E668">
-        <v>182274</v>
+        <v>182275</v>
       </c>
       <c r="F668">
-        <v>8421956</v>
+        <v>8421915</v>
       </c>
       <c r="G668">
-        <v>7295134</v>
+        <v>7295233</v>
       </c>
       <c r="H668">
-        <v>3288702</v>
+        <v>3288759</v>
       </c>
       <c r="I668">
         <v>459.83</v>
@@ -35897,13 +35897,13 @@
         <v>461.59</v>
       </c>
       <c r="M668">
-        <v>37517826</v>
+        <v>37517883</v>
       </c>
       <c r="N668">
-        <v>5407927</v>
+        <v>5407963</v>
       </c>
       <c r="O668">
-        <v>2109597</v>
+        <v>2109598</v>
       </c>
       <c r="P668">
         <v>5504</v>
@@ -35920,25 +35920,25 @@
         <v>45900</v>
       </c>
       <c r="B669">
-        <v>837361</v>
+        <v>837631</v>
       </c>
       <c r="C669">
         <v>1906.9</v>
       </c>
       <c r="D669">
-        <v>406082</v>
+        <v>406108</v>
       </c>
       <c r="E669">
-        <v>177775</v>
+        <v>177776</v>
       </c>
       <c r="F669">
-        <v>8429787</v>
+        <v>8429756</v>
       </c>
       <c r="G669">
-        <v>6919720</v>
+        <v>6919792</v>
       </c>
       <c r="H669">
-        <v>3095975</v>
+        <v>3096034</v>
       </c>
       <c r="I669">
         <v>457.06</v>
@@ -35953,13 +35953,13 @@
         <v>462.81</v>
       </c>
       <c r="M669">
-        <v>37812870</v>
+        <v>37812985</v>
       </c>
       <c r="N669">
-        <v>5405408</v>
+        <v>5405470</v>
       </c>
       <c r="O669">
-        <v>2122842</v>
+        <v>2122844</v>
       </c>
       <c r="P669">
         <v>5487</v>
@@ -35976,25 +35976,25 @@
         <v>45930</v>
       </c>
       <c r="B670">
-        <v>852588</v>
+        <v>852802</v>
       </c>
       <c r="C670">
         <v>1709.7</v>
       </c>
       <c r="D670">
-        <v>369969</v>
+        <v>369998</v>
       </c>
       <c r="E670">
-        <v>178883</v>
+        <v>178887</v>
       </c>
       <c r="F670">
-        <v>7502517</v>
+        <v>7502522</v>
       </c>
       <c r="G670">
-        <v>6623265</v>
+        <v>6623344</v>
       </c>
       <c r="H670">
-        <v>3039112</v>
+        <v>3039165</v>
       </c>
       <c r="I670">
         <v>469.54</v>
@@ -36009,13 +36009,13 @@
         <v>464.21</v>
       </c>
       <c r="M670">
-        <v>38098435</v>
+        <v>38098604</v>
       </c>
       <c r="N670">
-        <v>5424109</v>
+        <v>5424200</v>
       </c>
       <c r="O670">
-        <v>2132198</v>
+        <v>2132204</v>
       </c>
       <c r="P670">
         <v>5497</v>
@@ -36065,13 +36065,13 @@
         <v>466.12</v>
       </c>
       <c r="M671">
-        <v>38269110</v>
+        <v>38269280</v>
       </c>
       <c r="N671">
-        <v>5411661</v>
+        <v>5411752</v>
       </c>
       <c r="O671">
-        <v>2137467</v>
+        <v>2137473</v>
       </c>
       <c r="P671">
         <v>5493</v>
@@ -36088,7 +36088,7 @@
         <v>45991</v>
       </c>
       <c r="B672">
-        <v>944804</v>
+        <v>945078</v>
       </c>
       <c r="C672">
         <v>1766.7</v>
@@ -36121,13 +36121,13 @@
         <v>467.98</v>
       </c>
       <c r="M672">
-        <v>38590714</v>
+        <v>38590883</v>
       </c>
       <c r="N672">
-        <v>5425739</v>
+        <v>5425830</v>
       </c>
       <c r="O672">
-        <v>2151551</v>
+        <v>2151557</v>
       </c>
       <c r="P672">
         <v>5481</v>
@@ -36136,7 +36136,7 @@
         <v>15145</v>
       </c>
       <c r="R672">
-        <v>486489</v>
+        <v>488821</v>
       </c>
     </row>
     <row r="673">
@@ -36177,13 +36177,13 @@
         <v>471.08</v>
       </c>
       <c r="M673">
-        <v>38870131</v>
+        <v>38870300</v>
       </c>
       <c r="N673">
-        <v>5431198</v>
+        <v>5431289</v>
       </c>
       <c r="O673">
-        <v>2149463</v>
+        <v>2149469</v>
       </c>
       <c r="P673">
         <v>5476</v>
@@ -36192,7 +36192,7 @@
         <v>15151</v>
       </c>
       <c r="R673">
-        <v>483260</v>
+        <v>487768</v>
       </c>
     </row>
     <row r="674">
@@ -36200,28 +36200,28 @@
         <v>46053</v>
       </c>
       <c r="B674">
-        <v>1161791</v>
+        <v>1161466</v>
       </c>
       <c r="C674">
         <v>2105.6</v>
       </c>
       <c r="D674">
-        <v>642376</v>
+        <v>642221</v>
       </c>
       <c r="E674">
-        <v>182859</v>
+        <v>182707</v>
       </c>
       <c r="F674">
-        <v>8970205</v>
+        <v>8967994</v>
       </c>
       <c r="G674">
-        <v>7708449</v>
+        <v>7706482</v>
       </c>
       <c r="H674">
-        <v>3752803</v>
+        <v>3752090</v>
       </c>
       <c r="I674">
-        <v>498.09</v>
+        <v>498.12</v>
       </c>
       <c r="J674">
         <v>39.77</v>
@@ -36230,33 +36230,86 @@
         <v>15.61</v>
       </c>
       <c r="L674">
-        <v>473.72</v>
+        <v>473.73</v>
       </c>
       <c r="M674">
-        <v>38969876</v>
+        <v>38969333</v>
       </c>
       <c r="N674">
-        <v>5384517</v>
+        <v>5384453</v>
       </c>
       <c r="O674">
-        <v>2150953</v>
+        <v>2150807</v>
       </c>
       <c r="P674">
-        <v>5475</v>
+        <v>5479</v>
       </c>
       <c r="Q674">
-        <v>15161</v>
+        <v>15165</v>
+      </c>
+      <c r="R674">
+        <v>490622</v>
       </c>
     </row>
     <row r="675">
       <c r="A675" s="2">
         <v>46081</v>
       </c>
+      <c r="B675">
+        <v>870690</v>
+      </c>
+      <c r="D675">
+        <v>501489</v>
+      </c>
+      <c r="E675">
+        <v>166604</v>
+      </c>
+      <c r="F675">
+        <v>8658844</v>
+      </c>
+      <c r="G675">
+        <v>7497492</v>
+      </c>
+      <c r="H675">
+        <v>3707842</v>
+      </c>
+      <c r="I675">
+        <v>505.41</v>
+      </c>
+      <c r="J675">
+        <v>39.81</v>
+      </c>
+      <c r="K675">
+        <v>15.55</v>
+      </c>
+      <c r="L675">
+        <v>476.76</v>
+      </c>
+      <c r="M675">
+        <v>39196997</v>
+      </c>
+      <c r="N675">
+        <v>5402219</v>
+      </c>
+      <c r="O675">
+        <v>2151894</v>
+      </c>
       <c r="P675">
         <v>5480</v>
       </c>
       <c r="Q675">
-        <v>15160</v>
+        <v>15169</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="2">
+        <v>46112</v>
+      </c>
+      <c r="P676">
+        <v>5476</v>
+      </c>
+      <c r="Q676">
+        <v>15183</v>
       </c>
     </row>
   </sheetData>

--- a/data/monthly_state_ui.xlsx
+++ b/data/monthly_state_ui.xlsx
@@ -9869,7 +9869,7 @@
         <v>235008</v>
       </c>
       <c r="F194">
-        <v>14582389</v>
+        <v>14713714</v>
       </c>
       <c r="G194">
         <v>13027499</v>
@@ -9975,7 +9975,7 @@
         <v>219934</v>
       </c>
       <c r="F196">
-        <v>12935633</v>
+        <v>13070015</v>
       </c>
       <c r="G196">
         <v>11730221</v>
@@ -10134,7 +10134,7 @@
         <v>212380</v>
       </c>
       <c r="F199">
-        <v>10143793</v>
+        <v>10180428</v>
       </c>
       <c r="G199">
         <v>9028611</v>
@@ -10293,7 +10293,7 @@
         <v>211859</v>
       </c>
       <c r="F202">
-        <v>9577738</v>
+        <v>10031217</v>
       </c>
       <c r="G202">
         <v>8724780</v>
@@ -10346,7 +10346,7 @@
         <v>223173</v>
       </c>
       <c r="F203">
-        <v>9570267</v>
+        <v>9819412</v>
       </c>
       <c r="G203">
         <v>8695175</v>
@@ -35528,28 +35528,28 @@
         <v>45688</v>
       </c>
       <c r="B662">
-        <v>1229039</v>
+        <v>1229141</v>
       </c>
       <c r="C662">
         <v>2144.7</v>
       </c>
       <c r="D662">
-        <v>689057</v>
+        <v>688712</v>
       </c>
       <c r="E662">
-        <v>181369</v>
+        <v>181496</v>
       </c>
       <c r="F662">
-        <v>9270872</v>
+        <v>9270989</v>
       </c>
       <c r="G662">
-        <v>7923862</v>
+        <v>7926461</v>
       </c>
       <c r="H662">
-        <v>3653058</v>
+        <v>3653758</v>
       </c>
       <c r="I662">
-        <v>469.31</v>
+        <v>469.22</v>
       </c>
       <c r="J662">
         <v>38.94</v>
@@ -35558,16 +35558,16 @@
         <v>15.17</v>
       </c>
       <c r="L662">
-        <v>454.83</v>
+        <v>454.82</v>
       </c>
       <c r="M662">
-        <v>36187127</v>
+        <v>36187827</v>
       </c>
       <c r="N662">
-        <v>5341606</v>
+        <v>5341261</v>
       </c>
       <c r="O662">
-        <v>2047434</v>
+        <v>2047561</v>
       </c>
       <c r="P662">
         <v>5525</v>
@@ -35584,28 +35584,28 @@
         <v>45716</v>
       </c>
       <c r="B663">
-        <v>903834</v>
+        <v>903900</v>
       </c>
       <c r="C663">
         <v>2141</v>
       </c>
       <c r="D663">
-        <v>483723</v>
+        <v>483300</v>
       </c>
       <c r="E663">
-        <v>165517</v>
+        <v>165518</v>
       </c>
       <c r="F663">
-        <v>8657553</v>
+        <v>8657657</v>
       </c>
       <c r="G663">
-        <v>7509946</v>
+        <v>7509945</v>
       </c>
       <c r="H663">
-        <v>3480178</v>
+        <v>3480197</v>
       </c>
       <c r="I663">
-        <v>471.52</v>
+        <v>471.51</v>
       </c>
       <c r="J663">
         <v>39.22</v>
@@ -35614,16 +35614,16 @@
         <v>15.21</v>
       </c>
       <c r="L663">
-        <v>455.94</v>
+        <v>455.93</v>
       </c>
       <c r="M663">
-        <v>36328230</v>
+        <v>36328948</v>
       </c>
       <c r="N663">
-        <v>5334772</v>
+        <v>5334004</v>
       </c>
       <c r="O663">
-        <v>2055482</v>
+        <v>2055610</v>
       </c>
       <c r="P663">
         <v>5525</v>
@@ -35640,46 +35640,46 @@
         <v>45747</v>
       </c>
       <c r="B664">
-        <v>889619</v>
+        <v>889680</v>
       </c>
       <c r="C664">
         <v>2065.1</v>
       </c>
       <c r="D664">
-        <v>431634</v>
+        <v>431167</v>
       </c>
       <c r="E664">
-        <v>188778</v>
+        <v>188784</v>
       </c>
       <c r="F664">
-        <v>9621688</v>
+        <v>9621785</v>
       </c>
       <c r="G664">
-        <v>8149650</v>
+        <v>8149709</v>
       </c>
       <c r="H664">
-        <v>3743494</v>
+        <v>3743539</v>
       </c>
       <c r="I664">
-        <v>467.76</v>
+        <v>467.75</v>
       </c>
       <c r="J664">
-        <v>39.58</v>
+        <v>39.59</v>
       </c>
       <c r="K664">
         <v>15.3</v>
       </c>
       <c r="L664">
-        <v>457.11</v>
+        <v>457.1</v>
       </c>
       <c r="M664">
-        <v>36783747</v>
+        <v>36784511</v>
       </c>
       <c r="N664">
-        <v>5357347</v>
+        <v>5356112</v>
       </c>
       <c r="O664">
-        <v>2080486</v>
+        <v>2080620</v>
       </c>
       <c r="P664">
         <v>5523</v>
@@ -35696,46 +35696,46 @@
         <v>45777</v>
       </c>
       <c r="B665">
-        <v>942921</v>
+        <v>942976</v>
       </c>
       <c r="C665">
         <v>1877</v>
       </c>
       <c r="D665">
-        <v>401308</v>
+        <v>400726</v>
       </c>
       <c r="E665">
-        <v>189319</v>
+        <v>189309</v>
       </c>
       <c r="F665">
-        <v>7912994</v>
+        <v>7913076</v>
       </c>
       <c r="G665">
-        <v>6972902</v>
+        <v>6972826</v>
       </c>
       <c r="H665">
-        <v>3204874</v>
+        <v>3204868</v>
       </c>
       <c r="I665">
-        <v>468.53</v>
+        <v>468.52</v>
       </c>
       <c r="J665">
         <v>39.47</v>
       </c>
       <c r="K665">
-        <v>15.22</v>
+        <v>15.23</v>
       </c>
       <c r="L665">
-        <v>458.19</v>
+        <v>458.18</v>
       </c>
       <c r="M665">
-        <v>36811988</v>
+        <v>36812745</v>
       </c>
       <c r="N665">
-        <v>5375518</v>
+        <v>5373701</v>
       </c>
       <c r="O665">
-        <v>2084190</v>
+        <v>2084314</v>
       </c>
       <c r="P665">
         <v>5522</v>
@@ -35752,46 +35752,46 @@
         <v>45808</v>
       </c>
       <c r="B666">
-        <v>894785</v>
+        <v>894858</v>
       </c>
       <c r="C666">
         <v>1760.6</v>
       </c>
       <c r="D666">
-        <v>371539</v>
+        <v>370965</v>
       </c>
       <c r="E666">
-        <v>174208</v>
+        <v>174214</v>
       </c>
       <c r="F666">
-        <v>7224983</v>
+        <v>7225163</v>
       </c>
       <c r="G666">
-        <v>6139864</v>
+        <v>6140058</v>
       </c>
       <c r="H666">
-        <v>2798144</v>
+        <v>2798186</v>
       </c>
       <c r="I666">
-        <v>465.28</v>
+        <v>465.25</v>
       </c>
       <c r="J666">
         <v>39.76</v>
       </c>
       <c r="K666">
-        <v>15.27</v>
+        <v>15.28</v>
       </c>
       <c r="L666">
-        <v>458.9</v>
+        <v>458.88</v>
       </c>
       <c r="M666">
-        <v>36916392</v>
+        <v>36917191</v>
       </c>
       <c r="N666">
-        <v>5368085</v>
+        <v>5365694</v>
       </c>
       <c r="O666">
-        <v>2089888</v>
+        <v>2090018</v>
       </c>
       <c r="P666">
         <v>5515</v>
@@ -35808,28 +35808,28 @@
         <v>45838</v>
       </c>
       <c r="B667">
-        <v>1031839</v>
+        <v>1031918</v>
       </c>
       <c r="C667">
         <v>1860.9</v>
       </c>
       <c r="D667">
-        <v>457394</v>
+        <v>456816</v>
       </c>
       <c r="E667">
-        <v>178819</v>
+        <v>178825</v>
       </c>
       <c r="F667">
-        <v>8573274</v>
+        <v>8573406</v>
       </c>
       <c r="G667">
-        <v>6954166</v>
+        <v>6954221</v>
       </c>
       <c r="H667">
-        <v>3100962</v>
+        <v>3100995</v>
       </c>
       <c r="I667">
-        <v>455.27</v>
+        <v>455.28</v>
       </c>
       <c r="J667">
         <v>39.55</v>
@@ -35838,16 +35838,16 @@
         <v>15.3</v>
       </c>
       <c r="L667">
-        <v>459.67</v>
+        <v>459.66</v>
       </c>
       <c r="M667">
-        <v>37393949</v>
+        <v>37394781</v>
       </c>
       <c r="N667">
-        <v>5419922</v>
+        <v>5416953</v>
       </c>
       <c r="O667">
-        <v>2109153</v>
+        <v>2109289</v>
       </c>
       <c r="P667">
         <v>5516</v>
@@ -35864,46 +35864,46 @@
         <v>45869</v>
       </c>
       <c r="B668">
-        <v>981550</v>
+        <v>981627</v>
       </c>
       <c r="C668">
         <v>2004.2</v>
       </c>
       <c r="D668">
-        <v>510167</v>
+        <v>509550</v>
       </c>
       <c r="E668">
-        <v>182275</v>
+        <v>182609</v>
       </c>
       <c r="F668">
-        <v>8421915</v>
+        <v>8421960</v>
       </c>
       <c r="G668">
-        <v>7295233</v>
+        <v>7300670</v>
       </c>
       <c r="H668">
-        <v>3288759</v>
+        <v>3290187</v>
       </c>
       <c r="I668">
-        <v>459.83</v>
+        <v>459.66</v>
       </c>
       <c r="J668">
-        <v>39.49</v>
+        <v>39.51</v>
       </c>
       <c r="K668">
-        <v>15.32</v>
+        <v>15.33</v>
       </c>
       <c r="L668">
-        <v>461.59</v>
+        <v>461.56</v>
       </c>
       <c r="M668">
-        <v>37517883</v>
+        <v>37520143</v>
       </c>
       <c r="N668">
-        <v>5407963</v>
+        <v>5404377</v>
       </c>
       <c r="O668">
-        <v>2109598</v>
+        <v>2110068</v>
       </c>
       <c r="P668">
         <v>5504</v>
@@ -35920,46 +35920,46 @@
         <v>45900</v>
       </c>
       <c r="B669">
-        <v>837631</v>
+        <v>837602</v>
       </c>
       <c r="C669">
         <v>1906.9</v>
       </c>
       <c r="D669">
-        <v>406108</v>
+        <v>405660</v>
       </c>
       <c r="E669">
-        <v>177776</v>
+        <v>177777</v>
       </c>
       <c r="F669">
-        <v>8429756</v>
+        <v>8429794</v>
       </c>
       <c r="G669">
-        <v>6919792</v>
+        <v>6919811</v>
       </c>
       <c r="H669">
-        <v>3096034</v>
+        <v>3096051</v>
       </c>
       <c r="I669">
-        <v>457.06</v>
+        <v>457.05</v>
       </c>
       <c r="J669">
-        <v>39.79</v>
+        <v>39.81</v>
       </c>
       <c r="K669">
-        <v>15.41</v>
+        <v>15.42</v>
       </c>
       <c r="L669">
-        <v>462.81</v>
+        <v>462.78</v>
       </c>
       <c r="M669">
-        <v>37812985</v>
+        <v>37815262</v>
       </c>
       <c r="N669">
-        <v>5405470</v>
+        <v>5401436</v>
       </c>
       <c r="O669">
-        <v>2122844</v>
+        <v>2123315</v>
       </c>
       <c r="P669">
         <v>5487</v>
@@ -35976,46 +35976,46 @@
         <v>45930</v>
       </c>
       <c r="B670">
-        <v>852802</v>
+        <v>852782</v>
       </c>
       <c r="C670">
         <v>1709.7</v>
       </c>
       <c r="D670">
-        <v>369998</v>
+        <v>369609</v>
       </c>
       <c r="E670">
         <v>178887</v>
       </c>
       <c r="F670">
-        <v>7502522</v>
+        <v>7502566</v>
       </c>
       <c r="G670">
-        <v>6623344</v>
+        <v>6623253</v>
       </c>
       <c r="H670">
-        <v>3039165</v>
+        <v>3039174</v>
       </c>
       <c r="I670">
         <v>469.54</v>
       </c>
       <c r="J670">
-        <v>39.8</v>
+        <v>39.82</v>
       </c>
       <c r="K670">
-        <v>15.43</v>
+        <v>15.44</v>
       </c>
       <c r="L670">
-        <v>464.21</v>
+        <v>464.18</v>
       </c>
       <c r="M670">
-        <v>38098604</v>
+        <v>38100889</v>
       </c>
       <c r="N670">
-        <v>5424200</v>
+        <v>5419777</v>
       </c>
       <c r="O670">
-        <v>2132204</v>
+        <v>2132675</v>
       </c>
       <c r="P670">
         <v>5497</v>
@@ -36032,46 +36032,46 @@
         <v>45961</v>
       </c>
       <c r="B671">
-        <v>923951</v>
+        <v>923962</v>
       </c>
       <c r="C671">
         <v>1689.4</v>
       </c>
       <c r="D671">
-        <v>380062</v>
+        <v>379561</v>
       </c>
       <c r="E671">
-        <v>170539</v>
+        <v>170537</v>
       </c>
       <c r="F671">
-        <v>6981949</v>
+        <v>6981993</v>
       </c>
       <c r="G671">
-        <v>5980413</v>
+        <v>5980353</v>
       </c>
       <c r="H671">
-        <v>2837711</v>
+        <v>2837717</v>
       </c>
       <c r="I671">
-        <v>485.72</v>
+        <v>485.7</v>
       </c>
       <c r="J671">
-        <v>39.76</v>
+        <v>39.79</v>
       </c>
       <c r="K671">
-        <v>15.48</v>
+        <v>15.49</v>
       </c>
       <c r="L671">
-        <v>466.12</v>
+        <v>466.09</v>
       </c>
       <c r="M671">
-        <v>38269280</v>
+        <v>38271571</v>
       </c>
       <c r="N671">
-        <v>5411752</v>
+        <v>5406828</v>
       </c>
       <c r="O671">
-        <v>2137473</v>
+        <v>2137942</v>
       </c>
       <c r="P671">
         <v>5493</v>
@@ -36088,46 +36088,46 @@
         <v>45991</v>
       </c>
       <c r="B672">
-        <v>945078</v>
+        <v>945075</v>
       </c>
       <c r="C672">
         <v>1766.7</v>
       </c>
       <c r="D672">
-        <v>382977</v>
+        <v>382611</v>
       </c>
       <c r="E672">
-        <v>169583</v>
+        <v>169582</v>
       </c>
       <c r="F672">
-        <v>7596783</v>
+        <v>7596869</v>
       </c>
       <c r="G672">
-        <v>5961933</v>
+        <v>5961957</v>
       </c>
       <c r="H672">
-        <v>2835263</v>
+        <v>2835269</v>
       </c>
       <c r="I672">
-        <v>487.66</v>
+        <v>487.64</v>
       </c>
       <c r="J672">
-        <v>40.08</v>
+        <v>40.11</v>
       </c>
       <c r="K672">
-        <v>15.51</v>
+        <v>15.53</v>
       </c>
       <c r="L672">
-        <v>467.98</v>
+        <v>467.95</v>
       </c>
       <c r="M672">
-        <v>38590883</v>
+        <v>38593180</v>
       </c>
       <c r="N672">
-        <v>5425830</v>
+        <v>5420540</v>
       </c>
       <c r="O672">
-        <v>2151557</v>
+        <v>2152025</v>
       </c>
       <c r="P672">
         <v>5481</v>
@@ -36144,46 +36144,46 @@
         <v>46022</v>
       </c>
       <c r="B673">
-        <v>1285782</v>
+        <v>1285761</v>
       </c>
       <c r="C673">
         <v>1974.9</v>
       </c>
       <c r="D673">
-        <v>547322</v>
+        <v>546902</v>
       </c>
       <c r="E673">
-        <v>192399</v>
+        <v>192398</v>
       </c>
       <c r="F673">
-        <v>8741250</v>
+        <v>8741358</v>
       </c>
       <c r="G673">
-        <v>7813783</v>
+        <v>7813813</v>
       </c>
       <c r="H673">
-        <v>3792657</v>
+        <v>3792659</v>
       </c>
       <c r="I673">
-        <v>497.56</v>
+        <v>497.54</v>
       </c>
       <c r="J673">
-        <v>39.66</v>
+        <v>39.69</v>
       </c>
       <c r="K673">
-        <v>15.51</v>
+        <v>15.53</v>
       </c>
       <c r="L673">
-        <v>471.08</v>
+        <v>471.05</v>
       </c>
       <c r="M673">
-        <v>38870300</v>
+        <v>38872600</v>
       </c>
       <c r="N673">
-        <v>5431289</v>
+        <v>5425579</v>
       </c>
       <c r="O673">
-        <v>2149469</v>
+        <v>2149936</v>
       </c>
       <c r="P673">
         <v>5476</v>
@@ -36200,46 +36200,46 @@
         <v>46053</v>
       </c>
       <c r="B674">
-        <v>1161466</v>
+        <v>1161429</v>
       </c>
       <c r="C674">
         <v>2105.6</v>
       </c>
       <c r="D674">
-        <v>642221</v>
+        <v>641813</v>
       </c>
       <c r="E674">
-        <v>182707</v>
+        <v>182706</v>
       </c>
       <c r="F674">
-        <v>8967994</v>
+        <v>9000893</v>
       </c>
       <c r="G674">
-        <v>7706482</v>
+        <v>7706483</v>
       </c>
       <c r="H674">
         <v>3752090</v>
       </c>
       <c r="I674">
-        <v>498.12</v>
+        <v>498.11</v>
       </c>
       <c r="J674">
-        <v>39.77</v>
+        <v>39.8</v>
       </c>
       <c r="K674">
-        <v>15.61</v>
+        <v>15.62</v>
       </c>
       <c r="L674">
-        <v>473.73</v>
+        <v>473.7</v>
       </c>
       <c r="M674">
-        <v>38969333</v>
+        <v>38970932</v>
       </c>
       <c r="N674">
-        <v>5384453</v>
+        <v>5378680</v>
       </c>
       <c r="O674">
-        <v>2150807</v>
+        <v>2151146</v>
       </c>
       <c r="P674">
         <v>5479</v>
@@ -36256,43 +36256,46 @@
         <v>46081</v>
       </c>
       <c r="B675">
-        <v>870690</v>
+        <v>870653</v>
+      </c>
+      <c r="C675">
+        <v>2112.7</v>
       </c>
       <c r="D675">
-        <v>501489</v>
+        <v>500950</v>
       </c>
       <c r="E675">
         <v>166604</v>
       </c>
       <c r="F675">
-        <v>8658844</v>
+        <v>8658902</v>
       </c>
       <c r="G675">
-        <v>7497492</v>
+        <v>7497563</v>
       </c>
       <c r="H675">
-        <v>3707842</v>
+        <v>3707864</v>
       </c>
       <c r="I675">
-        <v>505.41</v>
+        <v>505.39</v>
       </c>
       <c r="J675">
-        <v>39.81</v>
+        <v>39.85</v>
       </c>
       <c r="K675">
-        <v>15.55</v>
+        <v>15.57</v>
       </c>
       <c r="L675">
-        <v>476.76</v>
+        <v>476.73</v>
       </c>
       <c r="M675">
-        <v>39196997</v>
+        <v>39198599</v>
       </c>
       <c r="N675">
-        <v>5402219</v>
+        <v>5396330</v>
       </c>
       <c r="O675">
-        <v>2151894</v>
+        <v>2152232</v>
       </c>
       <c r="P675">
         <v>5480</v>
@@ -36304,6 +36307,45 @@
     <row r="676">
       <c r="A676" s="2">
         <v>46112</v>
+      </c>
+      <c r="B676">
+        <v>865415</v>
+      </c>
+      <c r="D676">
+        <v>424816</v>
+      </c>
+      <c r="E676">
+        <v>193591</v>
+      </c>
+      <c r="F676">
+        <v>9678293</v>
+      </c>
+      <c r="G676">
+        <v>8464959</v>
+      </c>
+      <c r="H676">
+        <v>4181624</v>
+      </c>
+      <c r="I676">
+        <v>506.87</v>
+      </c>
+      <c r="J676">
+        <v>39.8</v>
+      </c>
+      <c r="K676">
+        <v>15.65</v>
+      </c>
+      <c r="L676">
+        <v>480.62</v>
+      </c>
+      <c r="M676">
+        <v>39636684</v>
+      </c>
+      <c r="N676">
+        <v>5389979</v>
+      </c>
+      <c r="O676">
+        <v>2157039</v>
       </c>
       <c r="P676">
         <v>5476</v>

--- a/data/monthly_state_ui.xlsx
+++ b/data/monthly_state_ui.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R676"/>
+  <dimension ref="A1:R677"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -35976,28 +35976,28 @@
         <v>45930</v>
       </c>
       <c r="B670">
-        <v>852782</v>
+        <v>852721</v>
       </c>
       <c r="C670">
         <v>1709.7</v>
       </c>
       <c r="D670">
-        <v>369609</v>
+        <v>369608</v>
       </c>
       <c r="E670">
-        <v>178887</v>
+        <v>178888</v>
       </c>
       <c r="F670">
         <v>7502566</v>
       </c>
       <c r="G670">
-        <v>6623253</v>
+        <v>6621126</v>
       </c>
       <c r="H670">
-        <v>3039174</v>
+        <v>3038080</v>
       </c>
       <c r="I670">
-        <v>469.54</v>
+        <v>469.52</v>
       </c>
       <c r="J670">
         <v>39.82</v>
@@ -36009,13 +36009,13 @@
         <v>464.18</v>
       </c>
       <c r="M670">
-        <v>38100889</v>
+        <v>38099795</v>
       </c>
       <c r="N670">
-        <v>5419777</v>
+        <v>5419776</v>
       </c>
       <c r="O670">
-        <v>2132675</v>
+        <v>2132676</v>
       </c>
       <c r="P670">
         <v>5497</v>
@@ -36032,25 +36032,25 @@
         <v>45961</v>
       </c>
       <c r="B671">
-        <v>923962</v>
+        <v>924286</v>
       </c>
       <c r="C671">
         <v>1689.4</v>
       </c>
       <c r="D671">
-        <v>379561</v>
+        <v>379596</v>
       </c>
       <c r="E671">
-        <v>170537</v>
+        <v>170538</v>
       </c>
       <c r="F671">
-        <v>6981993</v>
+        <v>6982020</v>
       </c>
       <c r="G671">
-        <v>5980353</v>
+        <v>5980436</v>
       </c>
       <c r="H671">
-        <v>2837717</v>
+        <v>2837778</v>
       </c>
       <c r="I671">
         <v>485.7</v>
@@ -36065,13 +36065,13 @@
         <v>466.09</v>
       </c>
       <c r="M671">
-        <v>38271571</v>
+        <v>38270538</v>
       </c>
       <c r="N671">
-        <v>5406828</v>
+        <v>5406862</v>
       </c>
       <c r="O671">
-        <v>2137942</v>
+        <v>2137944</v>
       </c>
       <c r="P671">
         <v>5493</v>
@@ -36121,13 +36121,13 @@
         <v>467.95</v>
       </c>
       <c r="M672">
-        <v>38593180</v>
+        <v>38592147</v>
       </c>
       <c r="N672">
-        <v>5420540</v>
+        <v>5420574</v>
       </c>
       <c r="O672">
-        <v>2152025</v>
+        <v>2152027</v>
       </c>
       <c r="P672">
         <v>5481</v>
@@ -36144,28 +36144,28 @@
         <v>46022</v>
       </c>
       <c r="B673">
-        <v>1285761</v>
+        <v>1286768</v>
       </c>
       <c r="C673">
         <v>1974.9</v>
       </c>
       <c r="D673">
-        <v>546902</v>
+        <v>546936</v>
       </c>
       <c r="E673">
         <v>192398</v>
       </c>
       <c r="F673">
-        <v>8741358</v>
+        <v>8744744</v>
       </c>
       <c r="G673">
-        <v>7813813</v>
+        <v>7813893</v>
       </c>
       <c r="H673">
-        <v>3792659</v>
+        <v>3792726</v>
       </c>
       <c r="I673">
-        <v>497.54</v>
+        <v>497.55</v>
       </c>
       <c r="J673">
         <v>39.69</v>
@@ -36177,13 +36177,13 @@
         <v>471.05</v>
       </c>
       <c r="M673">
-        <v>38872600</v>
+        <v>38871633</v>
       </c>
       <c r="N673">
-        <v>5425579</v>
+        <v>5425647</v>
       </c>
       <c r="O673">
-        <v>2149936</v>
+        <v>2149938</v>
       </c>
       <c r="P673">
         <v>5476</v>
@@ -36192,7 +36192,7 @@
         <v>15151</v>
       </c>
       <c r="R673">
-        <v>487768</v>
+        <v>488132</v>
       </c>
     </row>
     <row r="674">
@@ -36200,46 +36200,46 @@
         <v>46053</v>
       </c>
       <c r="B674">
-        <v>1161429</v>
+        <v>1153389</v>
       </c>
       <c r="C674">
         <v>2105.6</v>
       </c>
       <c r="D674">
-        <v>641813</v>
+        <v>637251</v>
       </c>
       <c r="E674">
-        <v>182706</v>
+        <v>180631</v>
       </c>
       <c r="F674">
-        <v>9000893</v>
+        <v>8926453</v>
       </c>
       <c r="G674">
-        <v>7706483</v>
+        <v>7637362</v>
       </c>
       <c r="H674">
-        <v>3752090</v>
+        <v>3737121</v>
       </c>
       <c r="I674">
-        <v>498.11</v>
+        <v>500.63</v>
       </c>
       <c r="J674">
-        <v>39.8</v>
+        <v>39.77</v>
       </c>
       <c r="K674">
         <v>15.62</v>
       </c>
       <c r="L674">
-        <v>473.7</v>
+        <v>473.91</v>
       </c>
       <c r="M674">
-        <v>38970932</v>
+        <v>38954996</v>
       </c>
       <c r="N674">
-        <v>5378680</v>
+        <v>5374186</v>
       </c>
       <c r="O674">
-        <v>2151146</v>
+        <v>2149073</v>
       </c>
       <c r="P674">
         <v>5479</v>
@@ -36248,7 +36248,7 @@
         <v>15165</v>
       </c>
       <c r="R674">
-        <v>490622</v>
+        <v>490223</v>
       </c>
     </row>
     <row r="675">
@@ -36256,52 +36256,55 @@
         <v>46081</v>
       </c>
       <c r="B675">
-        <v>870653</v>
+        <v>869941</v>
       </c>
       <c r="C675">
         <v>2112.7</v>
       </c>
       <c r="D675">
-        <v>500950</v>
+        <v>500092</v>
       </c>
       <c r="E675">
-        <v>166604</v>
+        <v>166300</v>
       </c>
       <c r="F675">
-        <v>8658902</v>
+        <v>8670269</v>
       </c>
       <c r="G675">
-        <v>7497563</v>
+        <v>7505641</v>
       </c>
       <c r="H675">
-        <v>3707864</v>
+        <v>3709920</v>
       </c>
       <c r="I675">
-        <v>505.39</v>
+        <v>505.07</v>
       </c>
       <c r="J675">
-        <v>39.85</v>
+        <v>39.8</v>
       </c>
       <c r="K675">
         <v>15.57</v>
       </c>
       <c r="L675">
-        <v>476.73</v>
+        <v>476.92</v>
       </c>
       <c r="M675">
-        <v>39198599</v>
+        <v>39184719</v>
       </c>
       <c r="N675">
-        <v>5396330</v>
+        <v>5390978</v>
       </c>
       <c r="O675">
-        <v>2152232</v>
+        <v>2149855</v>
       </c>
       <c r="P675">
-        <v>5480</v>
+        <v>5473</v>
       </c>
       <c r="Q675">
-        <v>15169</v>
+        <v>15159</v>
+      </c>
+      <c r="R675">
+        <v>490094</v>
       </c>
     </row>
     <row r="676">
@@ -36309,49 +36312,66 @@
         <v>46112</v>
       </c>
       <c r="B676">
-        <v>865415</v>
+        <v>863458</v>
+      </c>
+      <c r="C676">
+        <v>2009.6</v>
       </c>
       <c r="D676">
-        <v>424816</v>
+        <v>423395</v>
       </c>
       <c r="E676">
-        <v>193591</v>
+        <v>192720</v>
       </c>
       <c r="F676">
-        <v>9678293</v>
+        <v>9700930</v>
       </c>
       <c r="G676">
-        <v>8464959</v>
+        <v>8462470</v>
       </c>
       <c r="H676">
-        <v>4181624</v>
+        <v>4169986</v>
       </c>
       <c r="I676">
-        <v>506.87</v>
+        <v>503.96</v>
       </c>
       <c r="J676">
-        <v>39.8</v>
+        <v>39.74</v>
       </c>
       <c r="K676">
         <v>15.65</v>
       </c>
       <c r="L676">
-        <v>480.62</v>
+        <v>480.53</v>
       </c>
       <c r="M676">
-        <v>39636684</v>
+        <v>39611166</v>
       </c>
       <c r="N676">
-        <v>5389979</v>
+        <v>5383206</v>
       </c>
       <c r="O676">
-        <v>2157039</v>
+        <v>2153791</v>
       </c>
       <c r="P676">
-        <v>5476</v>
+        <v>5471</v>
       </c>
       <c r="Q676">
-        <v>15183</v>
+        <v>15171</v>
+      </c>
+      <c r="R676">
+        <v>489842</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="2">
+        <v>46142</v>
+      </c>
+      <c r="P677">
+        <v>5472</v>
+      </c>
+      <c r="Q677">
+        <v>15171</v>
       </c>
     </row>
   </sheetData>

--- a/data/monthly_state_ui.xlsx
+++ b/data/monthly_state_ui.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R677"/>
+  <dimension ref="A1:R678"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -10770,7 +10770,7 @@
         <v>206268</v>
       </c>
       <c r="F211">
-        <v>9409396</v>
+        <v>9373396</v>
       </c>
       <c r="G211">
         <v>8264366</v>
@@ -10779,7 +10779,7 @@
         <v>1120652</v>
       </c>
       <c r="I211">
-        <v>140.32</v>
+        <v>140.12</v>
       </c>
       <c r="J211">
         <v>32.1</v>
@@ -36032,7 +36032,7 @@
         <v>45961</v>
       </c>
       <c r="B671">
-        <v>924286</v>
+        <v>924025</v>
       </c>
       <c r="C671">
         <v>1689.4</v>
@@ -36041,16 +36041,16 @@
         <v>379596</v>
       </c>
       <c r="E671">
-        <v>170538</v>
+        <v>170543</v>
       </c>
       <c r="F671">
-        <v>6982020</v>
+        <v>6979391</v>
       </c>
       <c r="G671">
-        <v>5980436</v>
+        <v>5980439</v>
       </c>
       <c r="H671">
-        <v>2837778</v>
+        <v>2837785</v>
       </c>
       <c r="I671">
         <v>485.7</v>
@@ -36065,13 +36065,13 @@
         <v>466.09</v>
       </c>
       <c r="M671">
-        <v>38270538</v>
+        <v>38270545</v>
       </c>
       <c r="N671">
         <v>5406862</v>
       </c>
       <c r="O671">
-        <v>2137944</v>
+        <v>2137949</v>
       </c>
       <c r="P671">
         <v>5493</v>
@@ -36088,7 +36088,7 @@
         <v>45991</v>
       </c>
       <c r="B672">
-        <v>945075</v>
+        <v>945119</v>
       </c>
       <c r="C672">
         <v>1766.7</v>
@@ -36097,13 +36097,13 @@
         <v>382611</v>
       </c>
       <c r="E672">
-        <v>169582</v>
+        <v>169586</v>
       </c>
       <c r="F672">
-        <v>7596869</v>
+        <v>7594932</v>
       </c>
       <c r="G672">
-        <v>5961957</v>
+        <v>5961960</v>
       </c>
       <c r="H672">
         <v>2835269</v>
@@ -36121,13 +36121,13 @@
         <v>467.95</v>
       </c>
       <c r="M672">
-        <v>38592147</v>
+        <v>38592155</v>
       </c>
       <c r="N672">
         <v>5420574</v>
       </c>
       <c r="O672">
-        <v>2152027</v>
+        <v>2152036</v>
       </c>
       <c r="P672">
         <v>5481</v>
@@ -36144,7 +36144,7 @@
         <v>46022</v>
       </c>
       <c r="B673">
-        <v>1286768</v>
+        <v>1286403</v>
       </c>
       <c r="C673">
         <v>1974.9</v>
@@ -36153,16 +36153,16 @@
         <v>546936</v>
       </c>
       <c r="E673">
-        <v>192398</v>
+        <v>192404</v>
       </c>
       <c r="F673">
-        <v>8744744</v>
+        <v>8732950</v>
       </c>
       <c r="G673">
-        <v>7813893</v>
+        <v>7813896</v>
       </c>
       <c r="H673">
-        <v>3792726</v>
+        <v>3792728</v>
       </c>
       <c r="I673">
         <v>497.55</v>
@@ -36177,13 +36177,13 @@
         <v>471.05</v>
       </c>
       <c r="M673">
-        <v>38871633</v>
+        <v>38871643</v>
       </c>
       <c r="N673">
         <v>5425647</v>
       </c>
       <c r="O673">
-        <v>2149938</v>
+        <v>2149953</v>
       </c>
       <c r="P673">
         <v>5476</v>
@@ -36200,7 +36200,7 @@
         <v>46053</v>
       </c>
       <c r="B674">
-        <v>1153389</v>
+        <v>1152536</v>
       </c>
       <c r="C674">
         <v>2105.6</v>
@@ -36209,16 +36209,16 @@
         <v>637251</v>
       </c>
       <c r="E674">
-        <v>180631</v>
+        <v>180638</v>
       </c>
       <c r="F674">
-        <v>8926453</v>
+        <v>8916656</v>
       </c>
       <c r="G674">
-        <v>7637362</v>
+        <v>7637367</v>
       </c>
       <c r="H674">
-        <v>3737121</v>
+        <v>3737129</v>
       </c>
       <c r="I674">
         <v>500.63</v>
@@ -36233,13 +36233,13 @@
         <v>473.91</v>
       </c>
       <c r="M674">
-        <v>38954996</v>
+        <v>38955015</v>
       </c>
       <c r="N674">
         <v>5374186</v>
       </c>
       <c r="O674">
-        <v>2149073</v>
+        <v>2149095</v>
       </c>
       <c r="P674">
         <v>5479</v>
@@ -36256,7 +36256,7 @@
         <v>46081</v>
       </c>
       <c r="B675">
-        <v>869941</v>
+        <v>869311</v>
       </c>
       <c r="C675">
         <v>2112.7</v>
@@ -36265,16 +36265,16 @@
         <v>500092</v>
       </c>
       <c r="E675">
-        <v>166300</v>
+        <v>166311</v>
       </c>
       <c r="F675">
-        <v>8670269</v>
+        <v>8661433</v>
       </c>
       <c r="G675">
         <v>7505641</v>
       </c>
       <c r="H675">
-        <v>3709920</v>
+        <v>3462193</v>
       </c>
       <c r="I675">
         <v>505.07</v>
@@ -36289,13 +36289,13 @@
         <v>476.92</v>
       </c>
       <c r="M675">
-        <v>39184719</v>
+        <v>38937011</v>
       </c>
       <c r="N675">
         <v>5390978</v>
       </c>
       <c r="O675">
-        <v>2149855</v>
+        <v>2149888</v>
       </c>
       <c r="P675">
         <v>5473</v>
@@ -36304,7 +36304,7 @@
         <v>15159</v>
       </c>
       <c r="R675">
-        <v>490094</v>
+        <v>491753</v>
       </c>
     </row>
     <row r="676">
@@ -36312,25 +36312,25 @@
         <v>46112</v>
       </c>
       <c r="B676">
-        <v>863458</v>
+        <v>862825</v>
       </c>
       <c r="C676">
         <v>2009.6</v>
       </c>
       <c r="D676">
-        <v>423395</v>
+        <v>423396</v>
       </c>
       <c r="E676">
-        <v>192720</v>
+        <v>192723</v>
       </c>
       <c r="F676">
-        <v>9700930</v>
+        <v>9689666</v>
       </c>
       <c r="G676">
-        <v>8462470</v>
+        <v>8462498</v>
       </c>
       <c r="H676">
-        <v>4169986</v>
+        <v>4170006</v>
       </c>
       <c r="I676">
         <v>503.96</v>
@@ -36345,33 +36345,89 @@
         <v>480.53</v>
       </c>
       <c r="M676">
-        <v>39611166</v>
+        <v>39363478</v>
       </c>
       <c r="N676">
-        <v>5383206</v>
+        <v>5383207</v>
       </c>
       <c r="O676">
-        <v>2153791</v>
+        <v>2153827</v>
       </c>
       <c r="P676">
-        <v>5471</v>
+        <v>5469</v>
       </c>
       <c r="Q676">
-        <v>15171</v>
+        <v>15182</v>
       </c>
       <c r="R676">
-        <v>489842</v>
+        <v>492834</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" s="2">
         <v>46142</v>
       </c>
+      <c r="B677">
+        <v>850091</v>
+      </c>
+      <c r="C677">
+        <v>1750.1</v>
+      </c>
+      <c r="D677">
+        <v>358829</v>
+      </c>
+      <c r="E677">
+        <v>176044</v>
+      </c>
+      <c r="F677">
+        <v>7445078</v>
+      </c>
+      <c r="G677">
+        <v>6575681</v>
+      </c>
+      <c r="H677">
+        <v>3235588</v>
+      </c>
+      <c r="I677">
+        <v>504.74</v>
+      </c>
+      <c r="J677">
+        <v>39.59</v>
+      </c>
+      <c r="K677">
+        <v>15.7</v>
+      </c>
+      <c r="L677">
+        <v>483.42</v>
+      </c>
+      <c r="M677">
+        <v>39394198</v>
+      </c>
+      <c r="N677">
+        <v>5341310</v>
+      </c>
+      <c r="O677">
+        <v>2140562</v>
+      </c>
       <c r="P677">
-        <v>5472</v>
+        <v>5471</v>
       </c>
       <c r="Q677">
-        <v>15171</v>
+        <v>15188</v>
+      </c>
+      <c r="R677">
+        <v>493202</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="2">
+        <v>46173</v>
+      </c>
+      <c r="P678">
+        <v>5467</v>
+      </c>
+      <c r="Q678">
+        <v>15243</v>
       </c>
     </row>
   </sheetData>

--- a/data/monthly_state_ui.xlsx
+++ b/data/monthly_state_ui.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R678"/>
+  <dimension ref="A1:R679"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -10770,7 +10770,7 @@
         <v>206268</v>
       </c>
       <c r="F211">
-        <v>9373396</v>
+        <v>9409396</v>
       </c>
       <c r="G211">
         <v>8264366</v>
@@ -10779,7 +10779,7 @@
         <v>1120652</v>
       </c>
       <c r="I211">
-        <v>140.12</v>
+        <v>140.32</v>
       </c>
       <c r="J211">
         <v>32.1</v>
@@ -31544,7 +31544,7 @@
         <v>14527</v>
       </c>
       <c r="R590">
-        <v>295045</v>
+        <v>294973</v>
       </c>
     </row>
     <row r="591">
@@ -31600,7 +31600,7 @@
         <v>14533</v>
       </c>
       <c r="R591">
-        <v>303216</v>
+        <v>302971</v>
       </c>
     </row>
     <row r="592">
@@ -31656,7 +31656,7 @@
         <v>14567</v>
       </c>
       <c r="R592">
-        <v>303666</v>
+        <v>303562</v>
       </c>
     </row>
     <row r="593">
@@ -31712,7 +31712,7 @@
         <v>14600</v>
       </c>
       <c r="R593">
-        <v>326008</v>
+        <v>325998</v>
       </c>
     </row>
     <row r="594">
@@ -31768,7 +31768,7 @@
         <v>14583</v>
       </c>
       <c r="R594">
-        <v>320255</v>
+        <v>320278</v>
       </c>
     </row>
     <row r="595">
@@ -31824,7 +31824,7 @@
         <v>14601</v>
       </c>
       <c r="R595">
-        <v>316198</v>
+        <v>316370</v>
       </c>
     </row>
     <row r="596">
@@ -31880,7 +31880,7 @@
         <v>14552</v>
       </c>
       <c r="R596">
-        <v>325832</v>
+        <v>326104</v>
       </c>
     </row>
     <row r="597">
@@ -31936,7 +31936,7 @@
         <v>14558</v>
       </c>
       <c r="R597">
-        <v>320836</v>
+        <v>321099</v>
       </c>
     </row>
     <row r="598">
@@ -31992,7 +31992,7 @@
         <v>14582</v>
       </c>
       <c r="R598">
-        <v>325421</v>
+        <v>325269</v>
       </c>
     </row>
     <row r="599">
@@ -32048,7 +32048,7 @@
         <v>14594</v>
       </c>
       <c r="R599">
-        <v>322378</v>
+        <v>322369</v>
       </c>
     </row>
     <row r="600">
@@ -32104,7 +32104,7 @@
         <v>14619</v>
       </c>
       <c r="R600">
-        <v>323472</v>
+        <v>323469</v>
       </c>
     </row>
     <row r="601">
@@ -32160,7 +32160,7 @@
         <v>14638</v>
       </c>
       <c r="R601">
-        <v>327296</v>
+        <v>327139</v>
       </c>
     </row>
     <row r="602">
@@ -32216,7 +32216,7 @@
         <v>14664</v>
       </c>
       <c r="R602">
-        <v>341359</v>
+        <v>341218</v>
       </c>
     </row>
     <row r="603">
@@ -32272,7 +32272,7 @@
         <v>14692</v>
       </c>
       <c r="R603">
-        <v>345542</v>
+        <v>345086</v>
       </c>
     </row>
     <row r="604">
@@ -32328,7 +32328,7 @@
         <v>14688</v>
       </c>
       <c r="R604">
-        <v>343949</v>
+        <v>343651</v>
       </c>
     </row>
     <row r="605">
@@ -32384,7 +32384,7 @@
         <v>13921</v>
       </c>
       <c r="R605">
-        <v>340158</v>
+        <v>339860</v>
       </c>
     </row>
     <row r="606">
@@ -32440,7 +32440,7 @@
         <v>13458</v>
       </c>
       <c r="R606">
-        <v>344898</v>
+        <v>344624</v>
       </c>
     </row>
     <row r="607">
@@ -32496,7 +32496,7 @@
         <v>13460</v>
       </c>
       <c r="R607">
-        <v>343392</v>
+        <v>343867</v>
       </c>
     </row>
     <row r="608">
@@ -32552,7 +32552,7 @@
         <v>13526</v>
       </c>
       <c r="R608">
-        <v>337856</v>
+        <v>338258</v>
       </c>
     </row>
     <row r="609">
@@ -32608,7 +32608,7 @@
         <v>13724</v>
       </c>
       <c r="R609">
-        <v>334024</v>
+        <v>334358</v>
       </c>
     </row>
     <row r="610">
@@ -32664,7 +32664,7 @@
         <v>13715</v>
       </c>
       <c r="R610">
-        <v>335220</v>
+        <v>335397</v>
       </c>
     </row>
     <row r="611">
@@ -32720,7 +32720,7 @@
         <v>13750</v>
       </c>
       <c r="R611">
-        <v>338214</v>
+        <v>338063</v>
       </c>
     </row>
     <row r="612">
@@ -32776,7 +32776,7 @@
         <v>13717</v>
       </c>
       <c r="R612">
-        <v>340985</v>
+        <v>340746</v>
       </c>
     </row>
     <row r="613">
@@ -32832,7 +32832,7 @@
         <v>13698</v>
       </c>
       <c r="R613">
-        <v>345152</v>
+        <v>345107</v>
       </c>
     </row>
     <row r="614">
@@ -32888,7 +32888,7 @@
         <v>13715</v>
       </c>
       <c r="R614">
-        <v>342295</v>
+        <v>341966</v>
       </c>
     </row>
     <row r="615">
@@ -32944,7 +32944,7 @@
         <v>13718</v>
       </c>
       <c r="R615">
-        <v>334159</v>
+        <v>333353</v>
       </c>
     </row>
     <row r="616">
@@ -33000,7 +33000,7 @@
         <v>13773</v>
       </c>
       <c r="R616">
-        <v>337880</v>
+        <v>337537</v>
       </c>
     </row>
     <row r="617">
@@ -33056,7 +33056,7 @@
         <v>13819</v>
       </c>
       <c r="R617">
-        <v>336247</v>
+        <v>335707</v>
       </c>
     </row>
     <row r="618">
@@ -33112,7 +33112,7 @@
         <v>13865</v>
       </c>
       <c r="R618">
-        <v>337543</v>
+        <v>337175</v>
       </c>
     </row>
     <row r="619">
@@ -33168,7 +33168,7 @@
         <v>13947</v>
       </c>
       <c r="R619">
-        <v>329898</v>
+        <v>330605</v>
       </c>
     </row>
     <row r="620">
@@ -33224,7 +33224,7 @@
         <v>13967</v>
       </c>
       <c r="R620">
-        <v>330467</v>
+        <v>331065</v>
       </c>
     </row>
     <row r="621">
@@ -33280,7 +33280,7 @@
         <v>14095</v>
       </c>
       <c r="R621">
-        <v>332900</v>
+        <v>333534</v>
       </c>
     </row>
     <row r="622">
@@ -33336,7 +33336,7 @@
         <v>14078</v>
       </c>
       <c r="R622">
-        <v>327369</v>
+        <v>327690</v>
       </c>
     </row>
     <row r="623">
@@ -33392,7 +33392,7 @@
         <v>14017</v>
       </c>
       <c r="R623">
-        <v>324962</v>
+        <v>324644</v>
       </c>
     </row>
     <row r="624">
@@ -33448,7 +33448,7 @@
         <v>14033</v>
       </c>
       <c r="R624">
-        <v>331225</v>
+        <v>331001</v>
       </c>
     </row>
     <row r="625">
@@ -33504,7 +33504,7 @@
         <v>14059</v>
       </c>
       <c r="R625">
-        <v>332079</v>
+        <v>331944</v>
       </c>
     </row>
     <row r="626">
@@ -33560,7 +33560,7 @@
         <v>14081</v>
       </c>
       <c r="R626">
-        <v>335367</v>
+        <v>334948</v>
       </c>
     </row>
     <row r="627">
@@ -33616,7 +33616,7 @@
         <v>14089</v>
       </c>
       <c r="R627">
-        <v>339940</v>
+        <v>338720</v>
       </c>
     </row>
     <row r="628">
@@ -33672,7 +33672,7 @@
         <v>14114</v>
       </c>
       <c r="R628">
-        <v>343309</v>
+        <v>342413</v>
       </c>
     </row>
     <row r="629">
@@ -33728,7 +33728,7 @@
         <v>14135</v>
       </c>
       <c r="R629">
-        <v>349983</v>
+        <v>349009</v>
       </c>
     </row>
     <row r="630">
@@ -33784,7 +33784,7 @@
         <v>14163</v>
       </c>
       <c r="R630">
-        <v>342679</v>
+        <v>342272</v>
       </c>
     </row>
     <row r="631">
@@ -33840,7 +33840,7 @@
         <v>14182</v>
       </c>
       <c r="R631">
-        <v>349662</v>
+        <v>350556</v>
       </c>
     </row>
     <row r="632">
@@ -33896,7 +33896,7 @@
         <v>14307</v>
       </c>
       <c r="R632">
-        <v>357378</v>
+        <v>358234</v>
       </c>
     </row>
     <row r="633">
@@ -33952,7 +33952,7 @@
         <v>14301</v>
       </c>
       <c r="R633">
-        <v>362881</v>
+        <v>364149</v>
       </c>
     </row>
     <row r="634">
@@ -34008,7 +34008,7 @@
         <v>14283</v>
       </c>
       <c r="R634">
-        <v>366384</v>
+        <v>367023</v>
       </c>
     </row>
     <row r="635">
@@ -34064,7 +34064,7 @@
         <v>14283</v>
       </c>
       <c r="R635">
-        <v>365642</v>
+        <v>365263</v>
       </c>
     </row>
     <row r="636">
@@ -34120,7 +34120,7 @@
         <v>14339</v>
       </c>
       <c r="R636">
-        <v>366244</v>
+        <v>365834</v>
       </c>
     </row>
     <row r="637">
@@ -34176,7 +34176,7 @@
         <v>14358</v>
       </c>
       <c r="R637">
-        <v>373987</v>
+        <v>373612</v>
       </c>
     </row>
     <row r="638">
@@ -34232,7 +34232,7 @@
         <v>14405</v>
       </c>
       <c r="R638">
-        <v>379392</v>
+        <v>378766</v>
       </c>
     </row>
     <row r="639">
@@ -34288,7 +34288,7 @@
         <v>14433</v>
       </c>
       <c r="R639">
-        <v>387843</v>
+        <v>385816</v>
       </c>
     </row>
     <row r="640">
@@ -34344,7 +34344,7 @@
         <v>14455</v>
       </c>
       <c r="R640">
-        <v>397990</v>
+        <v>396101</v>
       </c>
     </row>
     <row r="641">
@@ -34400,7 +34400,7 @@
         <v>14486</v>
       </c>
       <c r="R641">
-        <v>405401</v>
+        <v>403504</v>
       </c>
     </row>
     <row r="642">
@@ -34456,7 +34456,7 @@
         <v>14529</v>
       </c>
       <c r="R642">
-        <v>417406</v>
+        <v>416954</v>
       </c>
     </row>
     <row r="643">
@@ -34512,7 +34512,7 @@
         <v>14572</v>
       </c>
       <c r="R643">
-        <v>423949</v>
+        <v>425286</v>
       </c>
     </row>
     <row r="644">
@@ -34568,7 +34568,7 @@
         <v>14609</v>
       </c>
       <c r="R644">
-        <v>422871</v>
+        <v>424299</v>
       </c>
     </row>
     <row r="645">
@@ -34624,7 +34624,7 @@
         <v>14641</v>
       </c>
       <c r="R645">
-        <v>428148</v>
+        <v>430392</v>
       </c>
     </row>
     <row r="646">
@@ -34680,7 +34680,7 @@
         <v>14660</v>
       </c>
       <c r="R646">
-        <v>436947</v>
+        <v>438089</v>
       </c>
     </row>
     <row r="647">
@@ -34736,7 +34736,7 @@
         <v>14676</v>
       </c>
       <c r="R647">
-        <v>444351</v>
+        <v>444046</v>
       </c>
     </row>
     <row r="648">
@@ -34792,7 +34792,7 @@
         <v>14713</v>
       </c>
       <c r="R648">
-        <v>453531</v>
+        <v>452621</v>
       </c>
     </row>
     <row r="649">
@@ -34848,7 +34848,7 @@
         <v>14755</v>
       </c>
       <c r="R649">
-        <v>456086</v>
+        <v>454948</v>
       </c>
     </row>
     <row r="650">
@@ -34904,7 +34904,7 @@
         <v>14781</v>
       </c>
       <c r="R650">
-        <v>449421</v>
+        <v>452349</v>
       </c>
     </row>
     <row r="651">
@@ -34960,7 +34960,7 @@
         <v>14826</v>
       </c>
       <c r="R651">
-        <v>460527</v>
+        <v>462292</v>
       </c>
     </row>
     <row r="652">
@@ -35016,7 +35016,7 @@
         <v>14894</v>
       </c>
       <c r="R652">
-        <v>455814</v>
+        <v>456620</v>
       </c>
     </row>
     <row r="653">
@@ -35072,7 +35072,7 @@
         <v>14884</v>
       </c>
       <c r="R653">
-        <v>460896</v>
+        <v>464740</v>
       </c>
     </row>
     <row r="654">
@@ -35128,7 +35128,7 @@
         <v>14909</v>
       </c>
       <c r="R654">
-        <v>458902</v>
+        <v>465158</v>
       </c>
     </row>
     <row r="655">
@@ -35184,7 +35184,7 @@
         <v>14911</v>
       </c>
       <c r="R655">
-        <v>454153</v>
+        <v>462504</v>
       </c>
     </row>
     <row r="656">
@@ -35192,7 +35192,7 @@
         <v>45504</v>
       </c>
       <c r="B656">
-        <v>1065311</v>
+        <v>1064801</v>
       </c>
       <c r="C656">
         <v>1901</v>
@@ -35240,7 +35240,7 @@
         <v>14950</v>
       </c>
       <c r="R656">
-        <v>464102</v>
+        <v>473058</v>
       </c>
     </row>
     <row r="657">
@@ -35248,7 +35248,7 @@
         <v>45535</v>
       </c>
       <c r="B657">
-        <v>847941</v>
+        <v>847217</v>
       </c>
       <c r="C657">
         <v>1817.9</v>
@@ -35296,7 +35296,7 @@
         <v>14957</v>
       </c>
       <c r="R657">
-        <v>469078</v>
+        <v>479919</v>
       </c>
     </row>
     <row r="658">
@@ -35304,7 +35304,7 @@
         <v>45565</v>
       </c>
       <c r="B658">
-        <v>791479</v>
+        <v>791246</v>
       </c>
       <c r="C658">
         <v>1615.9</v>
@@ -35352,7 +35352,7 @@
         <v>14958</v>
       </c>
       <c r="R658">
-        <v>470037</v>
+        <v>480801</v>
       </c>
     </row>
     <row r="659">
@@ -35360,7 +35360,7 @@
         <v>45596</v>
       </c>
       <c r="B659">
-        <v>976085</v>
+        <v>975851</v>
       </c>
       <c r="C659">
         <v>1620.6</v>
@@ -35408,7 +35408,7 @@
         <v>14981</v>
       </c>
       <c r="R659">
-        <v>474646</v>
+        <v>490885</v>
       </c>
     </row>
     <row r="660">
@@ -35416,7 +35416,7 @@
         <v>45626</v>
       </c>
       <c r="B660">
-        <v>939442</v>
+        <v>939447</v>
       </c>
       <c r="C660">
         <v>1681.3</v>
@@ -35464,7 +35464,7 @@
         <v>14993</v>
       </c>
       <c r="R660">
-        <v>472134</v>
+        <v>491625</v>
       </c>
     </row>
     <row r="661">
@@ -35472,7 +35472,7 @@
         <v>45657</v>
       </c>
       <c r="B661">
-        <v>1284695</v>
+        <v>1284529</v>
       </c>
       <c r="C661">
         <v>1926.7</v>
@@ -35520,7 +35520,7 @@
         <v>15005</v>
       </c>
       <c r="R661">
-        <v>466925</v>
+        <v>488364</v>
       </c>
     </row>
     <row r="662">
@@ -35576,7 +35576,7 @@
         <v>15022</v>
       </c>
       <c r="R662">
-        <v>468212</v>
+        <v>490424</v>
       </c>
     </row>
     <row r="663">
@@ -35632,7 +35632,7 @@
         <v>15037</v>
       </c>
       <c r="R663">
-        <v>467885</v>
+        <v>493130</v>
       </c>
     </row>
     <row r="664">
@@ -35688,7 +35688,7 @@
         <v>15048</v>
       </c>
       <c r="R664">
-        <v>470613</v>
+        <v>501351</v>
       </c>
     </row>
     <row r="665">
@@ -35744,7 +35744,7 @@
         <v>15070</v>
       </c>
       <c r="R665">
-        <v>475304</v>
+        <v>503004</v>
       </c>
     </row>
     <row r="666">
@@ -35800,7 +35800,7 @@
         <v>15094</v>
       </c>
       <c r="R666">
-        <v>475285</v>
+        <v>498883</v>
       </c>
     </row>
     <row r="667">
@@ -35808,28 +35808,28 @@
         <v>45838</v>
       </c>
       <c r="B667">
-        <v>1031918</v>
+        <v>1031937</v>
       </c>
       <c r="C667">
         <v>1860.9</v>
       </c>
       <c r="D667">
-        <v>456816</v>
+        <v>456634</v>
       </c>
       <c r="E667">
         <v>178825</v>
       </c>
       <c r="F667">
-        <v>8573406</v>
+        <v>8573747</v>
       </c>
       <c r="G667">
-        <v>6954221</v>
+        <v>6951107</v>
       </c>
       <c r="H667">
-        <v>3100995</v>
+        <v>3099262</v>
       </c>
       <c r="I667">
-        <v>455.28</v>
+        <v>455.23</v>
       </c>
       <c r="J667">
         <v>39.55</v>
@@ -35841,10 +35841,10 @@
         <v>459.66</v>
       </c>
       <c r="M667">
-        <v>37394781</v>
+        <v>37393048</v>
       </c>
       <c r="N667">
-        <v>5416953</v>
+        <v>5416771</v>
       </c>
       <c r="O667">
         <v>2109289</v>
@@ -35856,7 +35856,7 @@
         <v>15126</v>
       </c>
       <c r="R667">
-        <v>477452</v>
+        <v>495257</v>
       </c>
     </row>
     <row r="668">
@@ -35864,7 +35864,7 @@
         <v>45869</v>
       </c>
       <c r="B668">
-        <v>981627</v>
+        <v>981608</v>
       </c>
       <c r="C668">
         <v>2004.2</v>
@@ -35876,7 +35876,7 @@
         <v>182609</v>
       </c>
       <c r="F668">
-        <v>8421960</v>
+        <v>8421828</v>
       </c>
       <c r="G668">
         <v>7300670</v>
@@ -35897,10 +35897,10 @@
         <v>461.56</v>
       </c>
       <c r="M668">
-        <v>37520143</v>
+        <v>37518410</v>
       </c>
       <c r="N668">
-        <v>5404377</v>
+        <v>5404195</v>
       </c>
       <c r="O668">
         <v>2110068</v>
@@ -35912,7 +35912,7 @@
         <v>15146</v>
       </c>
       <c r="R668">
-        <v>480190</v>
+        <v>493350</v>
       </c>
     </row>
     <row r="669">
@@ -35950,13 +35950,13 @@
         <v>15.42</v>
       </c>
       <c r="L669">
-        <v>462.78</v>
+        <v>462.77</v>
       </c>
       <c r="M669">
-        <v>37815262</v>
+        <v>37813529</v>
       </c>
       <c r="N669">
-        <v>5401436</v>
+        <v>5401254</v>
       </c>
       <c r="O669">
         <v>2123315</v>
@@ -35968,7 +35968,7 @@
         <v>15132</v>
       </c>
       <c r="R669">
-        <v>481748</v>
+        <v>493596</v>
       </c>
     </row>
     <row r="670">
@@ -35976,7 +35976,7 @@
         <v>45930</v>
       </c>
       <c r="B670">
-        <v>852721</v>
+        <v>852695</v>
       </c>
       <c r="C670">
         <v>1709.7</v>
@@ -35988,7 +35988,7 @@
         <v>178888</v>
       </c>
       <c r="F670">
-        <v>7502566</v>
+        <v>7502398</v>
       </c>
       <c r="G670">
         <v>6621126</v>
@@ -36009,10 +36009,10 @@
         <v>464.18</v>
       </c>
       <c r="M670">
-        <v>38099795</v>
+        <v>38098062</v>
       </c>
       <c r="N670">
-        <v>5419776</v>
+        <v>5419594</v>
       </c>
       <c r="O670">
         <v>2132676</v>
@@ -36024,7 +36024,7 @@
         <v>15132</v>
       </c>
       <c r="R670">
-        <v>487347</v>
+        <v>500858</v>
       </c>
     </row>
     <row r="671">
@@ -36032,7 +36032,7 @@
         <v>45961</v>
       </c>
       <c r="B671">
-        <v>924025</v>
+        <v>924050</v>
       </c>
       <c r="C671">
         <v>1689.4</v>
@@ -36044,7 +36044,7 @@
         <v>170543</v>
       </c>
       <c r="F671">
-        <v>6979391</v>
+        <v>6979559</v>
       </c>
       <c r="G671">
         <v>5980439</v>
@@ -36062,13 +36062,13 @@
         <v>15.49</v>
       </c>
       <c r="L671">
-        <v>466.09</v>
+        <v>466.08</v>
       </c>
       <c r="M671">
-        <v>38270545</v>
+        <v>38268812</v>
       </c>
       <c r="N671">
-        <v>5406862</v>
+        <v>5406680</v>
       </c>
       <c r="O671">
         <v>2137949</v>
@@ -36080,7 +36080,7 @@
         <v>15149</v>
       </c>
       <c r="R671">
-        <v>487527</v>
+        <v>502123</v>
       </c>
     </row>
     <row r="672">
@@ -36118,13 +36118,13 @@
         <v>15.53</v>
       </c>
       <c r="L672">
-        <v>467.95</v>
+        <v>467.94</v>
       </c>
       <c r="M672">
-        <v>38592155</v>
+        <v>38590422</v>
       </c>
       <c r="N672">
-        <v>5420574</v>
+        <v>5420392</v>
       </c>
       <c r="O672">
         <v>2152036</v>
@@ -36136,7 +36136,7 @@
         <v>15145</v>
       </c>
       <c r="R672">
-        <v>488821</v>
+        <v>500197</v>
       </c>
     </row>
     <row r="673">
@@ -36177,10 +36177,10 @@
         <v>471.05</v>
       </c>
       <c r="M673">
-        <v>38871643</v>
+        <v>38869910</v>
       </c>
       <c r="N673">
-        <v>5425647</v>
+        <v>5425465</v>
       </c>
       <c r="O673">
         <v>2149953</v>
@@ -36192,7 +36192,7 @@
         <v>15151</v>
       </c>
       <c r="R673">
-        <v>488132</v>
+        <v>493913</v>
       </c>
     </row>
     <row r="674">
@@ -36200,7 +36200,7 @@
         <v>46053</v>
       </c>
       <c r="B674">
-        <v>1152536</v>
+        <v>1151845</v>
       </c>
       <c r="C674">
         <v>2105.6</v>
@@ -36218,10 +36218,10 @@
         <v>7637367</v>
       </c>
       <c r="H674">
-        <v>3737129</v>
+        <v>3737031</v>
       </c>
       <c r="I674">
-        <v>500.63</v>
+        <v>500.62</v>
       </c>
       <c r="J674">
         <v>39.77</v>
@@ -36233,10 +36233,10 @@
         <v>473.91</v>
       </c>
       <c r="M674">
-        <v>38955015</v>
+        <v>38953183</v>
       </c>
       <c r="N674">
-        <v>5374186</v>
+        <v>5374004</v>
       </c>
       <c r="O674">
         <v>2149095</v>
@@ -36248,7 +36248,7 @@
         <v>15165</v>
       </c>
       <c r="R674">
-        <v>490223</v>
+        <v>494196</v>
       </c>
     </row>
     <row r="675">
@@ -36256,46 +36256,46 @@
         <v>46081</v>
       </c>
       <c r="B675">
-        <v>869311</v>
+        <v>863711</v>
       </c>
       <c r="C675">
         <v>2112.7</v>
       </c>
       <c r="D675">
-        <v>500092</v>
+        <v>496960</v>
       </c>
       <c r="E675">
-        <v>166311</v>
+        <v>164736</v>
       </c>
       <c r="F675">
-        <v>8661433</v>
+        <v>8593072</v>
       </c>
       <c r="G675">
-        <v>7505641</v>
+        <v>7447659</v>
       </c>
       <c r="H675">
-        <v>3462193</v>
+        <v>3449507</v>
       </c>
       <c r="I675">
-        <v>505.07</v>
+        <v>507.24</v>
       </c>
       <c r="J675">
-        <v>39.8</v>
+        <v>39.77</v>
       </c>
       <c r="K675">
         <v>15.57</v>
       </c>
       <c r="L675">
-        <v>476.92</v>
+        <v>477.09</v>
       </c>
       <c r="M675">
-        <v>38937011</v>
+        <v>38922493</v>
       </c>
       <c r="N675">
-        <v>5390978</v>
+        <v>5387664</v>
       </c>
       <c r="O675">
-        <v>2149888</v>
+        <v>2148313</v>
       </c>
       <c r="P675">
         <v>5473</v>
@@ -36304,7 +36304,7 @@
         <v>15159</v>
       </c>
       <c r="R675">
-        <v>491753</v>
+        <v>494593</v>
       </c>
     </row>
     <row r="676">
@@ -36312,46 +36312,46 @@
         <v>46112</v>
       </c>
       <c r="B676">
-        <v>862825</v>
+        <v>857415</v>
       </c>
       <c r="C676">
         <v>2009.6</v>
       </c>
       <c r="D676">
-        <v>423396</v>
+        <v>420746</v>
       </c>
       <c r="E676">
-        <v>192723</v>
+        <v>190896</v>
       </c>
       <c r="F676">
-        <v>9689666</v>
+        <v>9619903</v>
       </c>
       <c r="G676">
-        <v>8462498</v>
+        <v>8404131</v>
       </c>
       <c r="H676">
-        <v>4170006</v>
+        <v>4157267</v>
       </c>
       <c r="I676">
-        <v>503.96</v>
+        <v>505.89</v>
       </c>
       <c r="J676">
-        <v>39.74</v>
+        <v>39.68</v>
       </c>
       <c r="K676">
         <v>15.65</v>
       </c>
       <c r="L676">
-        <v>480.53</v>
+        <v>480.87</v>
       </c>
       <c r="M676">
-        <v>39363478</v>
+        <v>39336221</v>
       </c>
       <c r="N676">
-        <v>5383207</v>
+        <v>5377243</v>
       </c>
       <c r="O676">
-        <v>2153827</v>
+        <v>2150425</v>
       </c>
       <c r="P676">
         <v>5469</v>
@@ -36360,7 +36360,7 @@
         <v>15182</v>
       </c>
       <c r="R676">
-        <v>492834</v>
+        <v>495792</v>
       </c>
     </row>
     <row r="677">
@@ -36368,66 +36368,164 @@
         <v>46142</v>
       </c>
       <c r="B677">
-        <v>850091</v>
+        <v>849408</v>
       </c>
       <c r="C677">
         <v>1750.1</v>
       </c>
       <c r="D677">
-        <v>358829</v>
+        <v>358960</v>
       </c>
       <c r="E677">
-        <v>176044</v>
+        <v>176059</v>
       </c>
       <c r="F677">
-        <v>7445078</v>
+        <v>7445346</v>
       </c>
       <c r="G677">
-        <v>6575681</v>
+        <v>6576521</v>
       </c>
       <c r="H677">
-        <v>3235588</v>
+        <v>3235745</v>
       </c>
       <c r="I677">
-        <v>504.74</v>
+        <v>504.69</v>
       </c>
       <c r="J677">
-        <v>39.59</v>
+        <v>39.53</v>
       </c>
       <c r="K677">
         <v>15.7</v>
       </c>
       <c r="L677">
-        <v>483.42</v>
+        <v>483.77</v>
       </c>
       <c r="M677">
-        <v>39394198</v>
+        <v>39367098</v>
       </c>
       <c r="N677">
-        <v>5341310</v>
+        <v>5335477</v>
       </c>
       <c r="O677">
-        <v>2140562</v>
+        <v>2137175</v>
       </c>
       <c r="P677">
-        <v>5471</v>
+        <v>5469</v>
       </c>
       <c r="Q677">
-        <v>15188</v>
+        <v>15181</v>
       </c>
       <c r="R677">
-        <v>493202</v>
+        <v>498096</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" s="2">
         <v>46173</v>
       </c>
+      <c r="B678">
+        <v>808345</v>
+      </c>
+      <c r="C678">
+        <v>1640</v>
+      </c>
+      <c r="D678">
+        <v>343270</v>
+      </c>
+      <c r="E678">
+        <v>176513</v>
+      </c>
+      <c r="F678">
+        <v>7307913</v>
+      </c>
+      <c r="G678">
+        <v>5951716</v>
+      </c>
+      <c r="H678">
+        <v>2897631</v>
+      </c>
+      <c r="I678">
+        <v>498.66</v>
+      </c>
+      <c r="J678">
+        <v>39.47</v>
+      </c>
+      <c r="K678">
+        <v>15.74</v>
+      </c>
+      <c r="L678">
+        <v>486.19</v>
+      </c>
+      <c r="M678">
+        <v>39466543</v>
+      </c>
+      <c r="N678">
+        <v>5307782</v>
+      </c>
+      <c r="O678">
+        <v>2139474</v>
+      </c>
       <c r="P678">
-        <v>5467</v>
+        <v>5465</v>
       </c>
       <c r="Q678">
-        <v>15243</v>
+        <v>15214</v>
+      </c>
+      <c r="R678">
+        <v>500238</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="2">
+        <v>46203</v>
+      </c>
+      <c r="B679">
+        <v>960900</v>
+      </c>
+      <c r="C679">
+        <v>1702.4</v>
+      </c>
+      <c r="D679">
+        <v>438262</v>
+      </c>
+      <c r="E679">
+        <v>169533</v>
+      </c>
+      <c r="F679">
+        <v>7479758</v>
+      </c>
+      <c r="G679">
+        <v>6615773</v>
+      </c>
+      <c r="H679">
+        <v>3189612</v>
+      </c>
+      <c r="I679">
+        <v>493.93</v>
+      </c>
+      <c r="J679">
+        <v>39.26</v>
+      </c>
+      <c r="K679">
+        <v>15.74</v>
+      </c>
+      <c r="L679">
+        <v>489.4</v>
+      </c>
+      <c r="M679">
+        <v>39556893</v>
+      </c>
+      <c r="N679">
+        <v>5289410</v>
+      </c>
+      <c r="O679">
+        <v>2130182</v>
+      </c>
+      <c r="P679">
+        <v>5469</v>
+      </c>
+      <c r="Q679">
+        <v>15216</v>
       </c>
     </row>
   </sheetData>

--- a/data/monthly_state_ui.xlsx
+++ b/data/monthly_state_ui.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R679"/>
+  <dimension ref="A1:R680"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -34520,7 +34520,7 @@
         <v>45138</v>
       </c>
       <c r="B644">
-        <v>1058538</v>
+        <v>1057719</v>
       </c>
       <c r="C644">
         <v>1820.7</v>
@@ -34576,7 +34576,7 @@
         <v>45169</v>
       </c>
       <c r="B645">
-        <v>938430</v>
+        <v>937428</v>
       </c>
       <c r="C645">
         <v>1793.4</v>
@@ -34632,7 +34632,7 @@
         <v>45199</v>
       </c>
       <c r="B646">
-        <v>753224</v>
+        <v>753504</v>
       </c>
       <c r="C646">
         <v>1567.9</v>
@@ -34688,7 +34688,7 @@
         <v>45230</v>
       </c>
       <c r="B647">
-        <v>886919</v>
+        <v>888510</v>
       </c>
       <c r="C647">
         <v>1567.9</v>
@@ -34744,7 +34744,7 @@
         <v>45260</v>
       </c>
       <c r="B648">
-        <v>1025076</v>
+        <v>1026265</v>
       </c>
       <c r="C648">
         <v>1553.7</v>
@@ -34800,7 +34800,7 @@
         <v>45291</v>
       </c>
       <c r="B649">
-        <v>1158324</v>
+        <v>1159605</v>
       </c>
       <c r="C649">
         <v>1818.4</v>
@@ -34856,7 +34856,7 @@
         <v>45322</v>
       </c>
       <c r="B650">
-        <v>1249509</v>
+        <v>1252366</v>
       </c>
       <c r="C650">
         <v>2050.7</v>
@@ -34912,7 +34912,7 @@
         <v>45351</v>
       </c>
       <c r="B651">
-        <v>880875</v>
+        <v>881127</v>
       </c>
       <c r="C651">
         <v>2059.2</v>
@@ -34968,7 +34968,7 @@
         <v>45382</v>
       </c>
       <c r="B652">
-        <v>844296</v>
+        <v>844647</v>
       </c>
       <c r="C652">
         <v>2000.4</v>
@@ -35024,7 +35024,7 @@
         <v>45412</v>
       </c>
       <c r="B653">
-        <v>901545</v>
+        <v>903333</v>
       </c>
       <c r="C653">
         <v>1807.6</v>
@@ -35080,7 +35080,7 @@
         <v>45443</v>
       </c>
       <c r="B654">
-        <v>879370</v>
+        <v>879154</v>
       </c>
       <c r="C654">
         <v>1650</v>
@@ -35136,7 +35136,7 @@
         <v>45473</v>
       </c>
       <c r="B655">
-        <v>968522</v>
+        <v>968428</v>
       </c>
       <c r="C655">
         <v>1736.8</v>
@@ -35528,7 +35528,7 @@
         <v>45688</v>
       </c>
       <c r="B662">
-        <v>1229141</v>
+        <v>1228181</v>
       </c>
       <c r="C662">
         <v>2144.7</v>
@@ -35584,7 +35584,7 @@
         <v>45716</v>
       </c>
       <c r="B663">
-        <v>903900</v>
+        <v>902921</v>
       </c>
       <c r="C663">
         <v>2141</v>
@@ -35640,7 +35640,7 @@
         <v>45747</v>
       </c>
       <c r="B664">
-        <v>889680</v>
+        <v>889029</v>
       </c>
       <c r="C664">
         <v>2065.1</v>
@@ -35696,7 +35696,7 @@
         <v>45777</v>
       </c>
       <c r="B665">
-        <v>942976</v>
+        <v>942605</v>
       </c>
       <c r="C665">
         <v>1877</v>
@@ -35752,7 +35752,7 @@
         <v>45808</v>
       </c>
       <c r="B666">
-        <v>894858</v>
+        <v>894589</v>
       </c>
       <c r="C666">
         <v>1760.6</v>
@@ -35808,7 +35808,7 @@
         <v>45838</v>
       </c>
       <c r="B667">
-        <v>1031937</v>
+        <v>1031627</v>
       </c>
       <c r="C667">
         <v>1860.9</v>
@@ -35864,7 +35864,7 @@
         <v>45869</v>
       </c>
       <c r="B668">
-        <v>981608</v>
+        <v>980968</v>
       </c>
       <c r="C668">
         <v>2004.2</v>
@@ -35920,7 +35920,7 @@
         <v>45900</v>
       </c>
       <c r="B669">
-        <v>837602</v>
+        <v>836866</v>
       </c>
       <c r="C669">
         <v>1906.9</v>
@@ -35976,7 +35976,7 @@
         <v>45930</v>
       </c>
       <c r="B670">
-        <v>852695</v>
+        <v>852311</v>
       </c>
       <c r="C670">
         <v>1709.7</v>
@@ -36200,46 +36200,46 @@
         <v>46053</v>
       </c>
       <c r="B674">
-        <v>1151845</v>
+        <v>1158049</v>
       </c>
       <c r="C674">
         <v>2105.6</v>
       </c>
       <c r="D674">
-        <v>637251</v>
+        <v>641555</v>
       </c>
       <c r="E674">
-        <v>180638</v>
+        <v>182843</v>
       </c>
       <c r="F674">
-        <v>8916656</v>
+        <v>8992689</v>
       </c>
       <c r="G674">
-        <v>7637367</v>
+        <v>7700328</v>
       </c>
       <c r="H674">
-        <v>3737031</v>
+        <v>3750764</v>
       </c>
       <c r="I674">
-        <v>500.62</v>
+        <v>498.35</v>
       </c>
       <c r="J674">
-        <v>39.77</v>
+        <v>39.81</v>
       </c>
       <c r="K674">
         <v>15.62</v>
       </c>
       <c r="L674">
-        <v>473.91</v>
+        <v>473.72</v>
       </c>
       <c r="M674">
-        <v>38953183</v>
+        <v>38966916</v>
       </c>
       <c r="N674">
-        <v>5374004</v>
+        <v>5378308</v>
       </c>
       <c r="O674">
-        <v>2149095</v>
+        <v>2151300</v>
       </c>
       <c r="P674">
         <v>5479</v>
@@ -36256,46 +36256,46 @@
         <v>46081</v>
       </c>
       <c r="B675">
-        <v>863711</v>
+        <v>868360</v>
       </c>
       <c r="C675">
         <v>2112.7</v>
       </c>
       <c r="D675">
-        <v>496960</v>
+        <v>500159</v>
       </c>
       <c r="E675">
-        <v>164736</v>
+        <v>166485</v>
       </c>
       <c r="F675">
-        <v>8593072</v>
+        <v>8650288</v>
       </c>
       <c r="G675">
-        <v>7447659</v>
+        <v>7502047</v>
       </c>
       <c r="H675">
-        <v>3449507</v>
+        <v>3461413</v>
       </c>
       <c r="I675">
-        <v>507.24</v>
+        <v>505.18</v>
       </c>
       <c r="J675">
-        <v>39.77</v>
+        <v>39.85</v>
       </c>
       <c r="K675">
         <v>15.57</v>
       </c>
       <c r="L675">
-        <v>477.09</v>
+        <v>476.73</v>
       </c>
       <c r="M675">
-        <v>38922493</v>
+        <v>38948132</v>
       </c>
       <c r="N675">
-        <v>5387664</v>
+        <v>5395167</v>
       </c>
       <c r="O675">
-        <v>2148313</v>
+        <v>2152267</v>
       </c>
       <c r="P675">
         <v>5473</v>
@@ -36312,46 +36312,46 @@
         <v>46112</v>
       </c>
       <c r="B676">
-        <v>857415</v>
+        <v>861633</v>
       </c>
       <c r="C676">
         <v>2009.6</v>
       </c>
       <c r="D676">
-        <v>420746</v>
+        <v>423606</v>
       </c>
       <c r="E676">
-        <v>190896</v>
+        <v>192674</v>
       </c>
       <c r="F676">
-        <v>9619903</v>
+        <v>9688036</v>
       </c>
       <c r="G676">
-        <v>8404131</v>
+        <v>8467385</v>
       </c>
       <c r="H676">
-        <v>4157267</v>
+        <v>4171201</v>
       </c>
       <c r="I676">
-        <v>505.89</v>
+        <v>503.77</v>
       </c>
       <c r="J676">
-        <v>39.68</v>
+        <v>39.78</v>
       </c>
       <c r="K676">
         <v>15.65</v>
       </c>
       <c r="L676">
-        <v>480.87</v>
+        <v>480.32</v>
       </c>
       <c r="M676">
-        <v>39336221</v>
+        <v>39375794</v>
       </c>
       <c r="N676">
-        <v>5377243</v>
+        <v>5387606</v>
       </c>
       <c r="O676">
-        <v>2150425</v>
+        <v>2156157</v>
       </c>
       <c r="P676">
         <v>5469</v>
@@ -36368,46 +36368,46 @@
         <v>46142</v>
       </c>
       <c r="B677">
-        <v>849408</v>
+        <v>849594</v>
       </c>
       <c r="C677">
         <v>1750.1</v>
       </c>
       <c r="D677">
-        <v>358960</v>
+        <v>358747</v>
       </c>
       <c r="E677">
-        <v>176059</v>
+        <v>175582</v>
       </c>
       <c r="F677">
-        <v>7445346</v>
+        <v>7443594</v>
       </c>
       <c r="G677">
-        <v>6576521</v>
+        <v>6573847</v>
       </c>
       <c r="H677">
-        <v>3235745</v>
+        <v>3235247</v>
       </c>
       <c r="I677">
-        <v>504.69</v>
+        <v>504.02</v>
       </c>
       <c r="J677">
-        <v>39.53</v>
+        <v>39.63</v>
       </c>
       <c r="K677">
         <v>15.7</v>
       </c>
       <c r="L677">
-        <v>483.77</v>
+        <v>483.15</v>
       </c>
       <c r="M677">
-        <v>39367098</v>
+        <v>39406174</v>
       </c>
       <c r="N677">
-        <v>5335477</v>
+        <v>5345627</v>
       </c>
       <c r="O677">
-        <v>2137175</v>
+        <v>2142430</v>
       </c>
       <c r="P677">
         <v>5469</v>
@@ -36416,7 +36416,7 @@
         <v>15181</v>
       </c>
       <c r="R677">
-        <v>498096</v>
+        <v>499775</v>
       </c>
     </row>
     <row r="678">
@@ -36424,55 +36424,55 @@
         <v>46173</v>
       </c>
       <c r="B678">
-        <v>808345</v>
+        <v>808326</v>
       </c>
       <c r="C678">
         <v>1640</v>
       </c>
       <c r="D678">
-        <v>343270</v>
+        <v>342567</v>
       </c>
       <c r="E678">
-        <v>176513</v>
+        <v>176316</v>
       </c>
       <c r="F678">
-        <v>7307913</v>
+        <v>7303006</v>
       </c>
       <c r="G678">
-        <v>5951716</v>
+        <v>5941902</v>
       </c>
       <c r="H678">
-        <v>2897631</v>
+        <v>2895531</v>
       </c>
       <c r="I678">
-        <v>498.66</v>
+        <v>499.07</v>
       </c>
       <c r="J678">
-        <v>39.47</v>
+        <v>39.56</v>
       </c>
       <c r="K678">
-        <v>15.74</v>
+        <v>15.75</v>
       </c>
       <c r="L678">
-        <v>486.19</v>
+        <v>485.6</v>
       </c>
       <c r="M678">
-        <v>39466543</v>
+        <v>39503518</v>
       </c>
       <c r="N678">
-        <v>5307782</v>
+        <v>5317229</v>
       </c>
       <c r="O678">
-        <v>2139474</v>
+        <v>2144532</v>
       </c>
       <c r="P678">
-        <v>5465</v>
+        <v>5467</v>
       </c>
       <c r="Q678">
-        <v>15214</v>
+        <v>15181</v>
       </c>
       <c r="R678">
-        <v>500238</v>
+        <v>501948</v>
       </c>
     </row>
     <row r="679">
@@ -36480,52 +36480,108 @@
         <v>46203</v>
       </c>
       <c r="B679">
-        <v>960900</v>
+        <v>961399</v>
       </c>
       <c r="C679">
         <v>1702.4</v>
       </c>
       <c r="D679">
-        <v>438262</v>
+        <v>438099</v>
       </c>
       <c r="E679">
-        <v>169533</v>
+        <v>169553</v>
       </c>
       <c r="F679">
-        <v>7479758</v>
+        <v>7477470</v>
       </c>
       <c r="G679">
-        <v>6615773</v>
+        <v>6613638</v>
       </c>
       <c r="H679">
-        <v>3189612</v>
+        <v>3189438</v>
       </c>
       <c r="I679">
-        <v>493.93</v>
+        <v>494.08</v>
       </c>
       <c r="J679">
-        <v>39.26</v>
+        <v>39.36</v>
       </c>
       <c r="K679">
         <v>15.74</v>
       </c>
       <c r="L679">
-        <v>489.4</v>
+        <v>488.81</v>
       </c>
       <c r="M679">
-        <v>39556893</v>
+        <v>39593695</v>
       </c>
       <c r="N679">
-        <v>5289410</v>
+        <v>5298694</v>
       </c>
       <c r="O679">
-        <v>2130182</v>
+        <v>2135260</v>
       </c>
       <c r="P679">
-        <v>5469</v>
+        <v>5464</v>
       </c>
       <c r="Q679">
-        <v>15216</v>
+        <v>15173</v>
+      </c>
+      <c r="R679">
+        <v>502034</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="2">
+        <v>46234</v>
+      </c>
+      <c r="B680">
+        <v>904125</v>
+      </c>
+      <c r="C680">
+        <v>1798.5</v>
+      </c>
+      <c r="D680">
+        <v>471790</v>
+      </c>
+      <c r="E680">
+        <v>173460</v>
+      </c>
+      <c r="F680">
+        <v>7806998</v>
+      </c>
+      <c r="G680">
+        <v>6699816</v>
+      </c>
+      <c r="H680">
+        <v>3156635</v>
+      </c>
+      <c r="I680">
+        <v>482.86</v>
+      </c>
+      <c r="J680">
+        <v>39.53</v>
+      </c>
+      <c r="K680">
+        <v>15.74</v>
+      </c>
+      <c r="L680">
+        <v>490.91</v>
+      </c>
+      <c r="M680">
+        <v>39460143</v>
+      </c>
+      <c r="N680">
+        <v>5260934</v>
+      </c>
+      <c r="O680">
+        <v>2126111</v>
+      </c>
+      <c r="P680">
+        <v>5471</v>
+      </c>
+      <c r="Q680">
+        <v>15116</v>
       </c>
     </row>
   </sheetData>
